--- a/muban_clean/dizhuan.xlsx
+++ b/muban_clean/dizhuan.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="2019报价" sheetId="15" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2019报价'!$A$1:$I$176</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1278,6 +1281,13 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1286,13 +1296,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1585,21 +1588,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1607,6 +1599,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1966,7 +1965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2027,7 +2026,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2036,35 +2035,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="J2" s="30"/>
       <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
+      <c r="L2" s="31"/>
       <c r="M2"/>
       <c r="N2"/>
       <c r="O2"/>
@@ -3105,7 +3105,7 @@
       <c r="I3" s="28"/>
       <c r="J3" s="28"/>
       <c r="K3" s="28"/>
-      <c r="L3" s="30"/>
+      <c r="L3" s="31"/>
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
@@ -3265,3352 +3265,3352 @@
       <c r="FM3"/>
     </row>
     <row r="4" ht="9.75" customHeight="1" spans="1:169">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="32" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="31" t="s">
+      <c r="H4" s="34"/>
+      <c r="I4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
     </row>
     <row r="5" ht="9.75" customHeight="1" spans="1:169">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="36"/>
       <c r="F5" s="37"/>
       <c r="G5" s="36"/>
       <c r="H5" s="37"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
     </row>
     <row r="6" ht="8.25" customHeight="1" spans="1:169">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="31" t="s">
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
     </row>
     <row r="7" ht="8.25" customHeight="1" spans="1:169">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:169">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:169">
-      <c r="A9" s="43">
+      <c r="A9" s="44">
         <v>1</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="42">
         <v>70</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <f t="shared" ref="F9:F24" si="0">C9*E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <v>25</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="42">
         <f t="shared" ref="H9:H11" si="1">SUM(G9*C9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="46" t="s">
+      <c r="I9" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:169">
-      <c r="A10" s="43">
+      <c r="A10" s="44">
         <v>2</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="41" t="s">
+      <c r="C10" s="44"/>
+      <c r="D10" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <v>95</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <v>55</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="42">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:169">
-      <c r="A11" s="43">
+      <c r="A11" s="44">
         <v>3</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="50"/>
+      <c r="D11" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="51">
         <v>125</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="51">
         <v>65</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="51" t="s">
+      <c r="I11" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="52"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53" t="s">
+      <c r="J11" s="53"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:169">
-      <c r="A12" s="43">
+      <c r="A12" s="44">
         <v>4</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <v>38</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="42">
         <v>22</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="42">
         <f>C12*G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A13" s="43">
+      <c r="A13" s="44">
         <v>5</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="43" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="44">
         <v>14</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="44">
         <v>8</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="42">
         <f>C13*G13</f>
         <v>0</v>
       </c>
-      <c r="I13" s="55" t="s">
+      <c r="I13" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="56"/>
+      <c r="J13" s="57"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A14" s="43">
+      <c r="A14" s="44">
         <v>6</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="43" t="s">
+      <c r="C14" s="42"/>
+      <c r="D14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="44">
         <v>16</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="44">
         <v>10</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="42">
         <f>C14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="55" t="s">
+      <c r="I14" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="56"/>
+      <c r="J14" s="57"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A15" s="43">
+      <c r="A15" s="44">
         <v>7</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="43" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="44">
         <v>4</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="44">
         <v>6.5</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="42">
         <f>C15*G15</f>
         <v>0</v>
       </c>
-      <c r="I15" s="55" t="s">
+      <c r="I15" s="56" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" s="6" customFormat="1" ht="25" customHeight="1" spans="1:169">
-      <c r="A16" s="43">
+      <c r="A16" s="44">
         <v>8</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="51">
         <v>28</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="51">
         <v>48</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="51">
         <f>C16*G16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="59"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A17" s="43">
+      <c r="A17" s="44">
         <v>9</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="41">
-        <v>0</v>
-      </c>
-      <c r="F17" s="41">
+      <c r="E17" s="42">
+        <v>0</v>
+      </c>
+      <c r="F17" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="42">
         <v>2.5</v>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="42">
         <f>SUM(G17*C17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="42" t="s">
+      <c r="I17" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A18" s="43">
+      <c r="A18" s="44">
         <v>10</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43" t="s">
+      <c r="C18" s="44"/>
+      <c r="D18" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="44">
         <v>135</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>95</v>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="42">
         <f>SUM(G18*C18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="55" t="s">
+      <c r="I18" s="56" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A19" s="43">
+      <c r="A19" s="44">
         <v>11</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="43" t="s">
+      <c r="C19" s="42"/>
+      <c r="D19" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="42">
         <v>2</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="42">
         <v>4</v>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="42">
         <f t="shared" ref="H19:H24" si="2">SUM(G19*C19)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
     </row>
     <row r="20" ht="27" customHeight="1" spans="1:12">
-      <c r="A20" s="43">
+      <c r="A20" s="44">
         <v>12</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41" t="s">
+      <c r="C20" s="42"/>
+      <c r="D20" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="42">
         <v>19</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="42">
         <v>13</v>
       </c>
-      <c r="H20" s="41">
+      <c r="H20" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="42" t="s">
+      <c r="I20" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
     </row>
     <row r="21" ht="27" customHeight="1" spans="1:12">
-      <c r="A21" s="43">
+      <c r="A21" s="44">
         <v>13</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41" t="s">
+      <c r="C21" s="42"/>
+      <c r="D21" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="42">
         <v>12</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="42">
         <v>7</v>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="42" t="s">
+      <c r="I21" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
     </row>
     <row r="22" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A22" s="43">
+      <c r="A22" s="44">
         <v>14</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41" t="s">
+      <c r="C22" s="42"/>
+      <c r="D22" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="42">
         <v>160</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="42">
         <v>360</v>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I22" s="42" t="s">
+      <c r="I22" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:12">
-      <c r="A23" s="43">
+      <c r="A23" s="44">
         <v>15</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="42">
         <v>25</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="42">
         <v>10</v>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:12">
-      <c r="A24" s="43">
+      <c r="A24" s="44">
         <v>16</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="42">
         <v>12</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="42">
         <v>5</v>
       </c>
-      <c r="H24" s="41">
+      <c r="H24" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I24" s="42" t="s">
+      <c r="I24" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
     </row>
     <row r="25" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A25" s="61"/>
-      <c r="B25" s="62" t="s">
+      <c r="A25" s="62"/>
+      <c r="B25" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61">
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62">
         <f>SUM(F9:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61">
+      <c r="G25" s="62"/>
+      <c r="H25" s="62">
         <f>SUM(H9:H24)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="63"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:12">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="65" t="s">
+      <c r="B26" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
     </row>
     <row r="27" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A27" s="50">
+      <c r="A27" s="51">
         <v>1</v>
       </c>
-      <c r="B27" s="66" t="s">
+      <c r="B27" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50" t="s">
+      <c r="C27" s="51"/>
+      <c r="D27" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="51">
         <v>28</v>
       </c>
-      <c r="F27" s="50">
+      <c r="F27" s="51">
         <f t="shared" ref="F27:F32" si="3">C27*E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="50">
+      <c r="G27" s="51">
         <v>32</v>
       </c>
-      <c r="H27" s="50">
+      <c r="H27" s="51">
         <f t="shared" ref="H27:H32" si="4">SUM(G27*C27)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
     </row>
     <row r="28" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A28" s="50">
+      <c r="A28" s="51">
         <v>2</v>
       </c>
-      <c r="B28" s="66" t="s">
+      <c r="B28" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50" t="s">
+      <c r="C28" s="51"/>
+      <c r="D28" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="51">
         <v>28</v>
       </c>
-      <c r="F28" s="50">
+      <c r="F28" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G28" s="50">
+      <c r="G28" s="51">
         <v>40</v>
       </c>
-      <c r="H28" s="50">
+      <c r="H28" s="51">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:12">
-      <c r="A29" s="50">
+      <c r="A29" s="51">
         <v>3</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="B29" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41" t="s">
+      <c r="C29" s="42"/>
+      <c r="D29" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="41">
-        <v>0</v>
-      </c>
-      <c r="F29" s="41">
+      <c r="E29" s="42">
+        <v>0</v>
+      </c>
+      <c r="F29" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="42">
         <v>9</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I29" s="42" t="s">
+      <c r="I29" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
     </row>
     <row r="30" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A30" s="50">
+      <c r="A30" s="51">
         <v>4</v>
       </c>
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41" t="s">
+      <c r="C30" s="42"/>
+      <c r="D30" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <v>8</v>
       </c>
-      <c r="F30" s="41">
+      <c r="F30" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="42">
         <v>20</v>
       </c>
-      <c r="H30" s="41">
+      <c r="H30" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="42" t="s">
+      <c r="I30" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:12">
-      <c r="A31" s="50">
+      <c r="A31" s="51">
         <v>5</v>
       </c>
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41" t="s">
+      <c r="C31" s="42"/>
+      <c r="D31" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="41">
-        <v>0</v>
-      </c>
-      <c r="F31" s="41">
+      <c r="E31" s="42">
+        <v>0</v>
+      </c>
+      <c r="F31" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="42">
         <v>2.5</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I31" s="42" t="s">
+      <c r="I31" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:12">
-      <c r="A32" s="50">
+      <c r="A32" s="51">
         <v>6</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="42">
         <v>45</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="42">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G32" s="41">
+      <c r="G32" s="42">
         <v>20</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I32" s="42" t="s">
+      <c r="I32" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:12">
-      <c r="A33" s="50">
+      <c r="A33" s="51">
         <v>7</v>
       </c>
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="42">
         <v>12</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="42">
         <f t="shared" ref="F33:F44" si="5">C33*E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="42">
         <v>5</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="42">
         <f t="shared" ref="H33:H44" si="6">SUM(G33*C33)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="42" t="s">
+      <c r="I33" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
     </row>
     <row r="34" s="9" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A34" s="69"/>
-      <c r="B34" s="70" t="s">
+      <c r="A34" s="70"/>
+      <c r="B34" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="72">
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="73">
         <f>SUM(F27:F33)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="69"/>
-      <c r="H34" s="72">
+      <c r="G34" s="70"/>
+      <c r="H34" s="73">
         <f>SUM(H27:H33)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="73"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="75"/>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="65" t="s">
+      <c r="B35" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
     </row>
     <row r="36" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A36" s="50">
+      <c r="A36" s="51">
         <v>1</v>
       </c>
-      <c r="B36" s="66" t="s">
+      <c r="B36" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50" t="s">
+      <c r="C36" s="51"/>
+      <c r="D36" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="50">
+      <c r="E36" s="51">
         <v>28</v>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="51">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G36" s="50">
+      <c r="G36" s="51">
         <v>32</v>
       </c>
-      <c r="H36" s="50">
+      <c r="H36" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I36" s="51" t="s">
+      <c r="I36" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="59"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
     </row>
     <row r="37" s="6" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A37" s="50">
+      <c r="A37" s="51">
         <v>2</v>
       </c>
-      <c r="B37" s="66" t="s">
+      <c r="B37" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50" t="s">
+      <c r="C37" s="51"/>
+      <c r="D37" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="51">
         <v>28</v>
       </c>
-      <c r="F37" s="50">
+      <c r="F37" s="51">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G37" s="50">
+      <c r="G37" s="51">
         <v>40</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I37" s="51" t="s">
+      <c r="I37" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:12">
-      <c r="A38" s="50">
+      <c r="A38" s="51">
         <v>3</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41" t="s">
+      <c r="C38" s="42"/>
+      <c r="D38" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="41">
-        <v>0</v>
-      </c>
-      <c r="F38" s="41">
+      <c r="E38" s="42">
+        <v>0</v>
+      </c>
+      <c r="F38" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G38" s="41">
+      <c r="G38" s="42">
         <v>9</v>
       </c>
-      <c r="H38" s="41">
+      <c r="H38" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I38" s="42" t="s">
+      <c r="I38" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
     </row>
     <row r="39" s="8" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A39" s="50">
+      <c r="A39" s="51">
         <v>4</v>
       </c>
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41" t="s">
+      <c r="C39" s="42"/>
+      <c r="D39" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="42">
         <v>8</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="42">
         <v>20</v>
       </c>
-      <c r="H39" s="41">
+      <c r="H39" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I39" s="42" t="s">
+      <c r="I39" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="69"/>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:12">
-      <c r="A40" s="50">
+      <c r="A40" s="51">
         <v>5</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41" t="s">
+      <c r="C40" s="42"/>
+      <c r="D40" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41">
+      <c r="E40" s="42"/>
+      <c r="F40" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="42">
         <v>2.5</v>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I40" s="42" t="s">
+      <c r="I40" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:12">
-      <c r="A41" s="50">
+      <c r="A41" s="51">
         <v>6</v>
       </c>
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41" t="s">
+      <c r="C41" s="42"/>
+      <c r="D41" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="41">
+      <c r="E41" s="42">
         <v>45</v>
       </c>
-      <c r="F41" s="41">
+      <c r="F41" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="42">
         <v>20</v>
       </c>
-      <c r="H41" s="41">
+      <c r="H41" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I41" s="42" t="s">
+      <c r="I41" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A42" s="50">
+      <c r="A42" s="51">
         <v>7</v>
       </c>
-      <c r="B42" s="44" t="s">
+      <c r="B42" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41" t="s">
+      <c r="C42" s="42"/>
+      <c r="D42" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="41">
+      <c r="E42" s="42">
         <v>22</v>
       </c>
-      <c r="F42" s="41">
+      <c r="F42" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G42" s="41">
+      <c r="G42" s="42">
         <v>12</v>
       </c>
-      <c r="H42" s="41">
+      <c r="H42" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I42" s="42" t="s">
+      <c r="I42" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:12">
-      <c r="A43" s="50">
+      <c r="A43" s="51">
         <v>8</v>
       </c>
-      <c r="B43" s="44" t="s">
+      <c r="B43" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41" t="s">
+      <c r="C43" s="42"/>
+      <c r="D43" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="42">
         <v>45</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="42">
         <v>20</v>
       </c>
-      <c r="H43" s="41">
+      <c r="H43" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I43" s="42" t="s">
+      <c r="I43" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:12">
-      <c r="A44" s="50">
+      <c r="A44" s="51">
         <v>9</v>
       </c>
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41" t="s">
+      <c r="C44" s="42"/>
+      <c r="D44" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="41">
+      <c r="E44" s="42">
         <v>12</v>
       </c>
-      <c r="F44" s="41">
+      <c r="F44" s="42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="42">
         <v>5</v>
       </c>
-      <c r="H44" s="41">
+      <c r="H44" s="42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I44" s="42" t="s">
+      <c r="I44" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A45" s="61"/>
-      <c r="B45" s="62" t="s">
+      <c r="A45" s="62"/>
+      <c r="B45" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61">
+      <c r="C45" s="62"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="62"/>
+      <c r="F45" s="62">
         <f>SUM(F36:F44)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61">
+      <c r="G45" s="62"/>
+      <c r="H45" s="62">
         <f>SUM(H36:H44)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="63"/>
-      <c r="J45" s="64"/>
-      <c r="K45" s="64"/>
-      <c r="L45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="65"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="65"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:12">
-      <c r="A46" s="39" t="s">
+      <c r="A46" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="75" t="s">
+      <c r="B46" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
     </row>
     <row r="47" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A47" s="50">
+      <c r="A47" s="51">
         <v>1</v>
       </c>
-      <c r="B47" s="66" t="s">
+      <c r="B47" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="50"/>
-      <c r="D47" s="50" t="s">
+      <c r="C47" s="51"/>
+      <c r="D47" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="50">
+      <c r="E47" s="51">
         <v>28</v>
       </c>
-      <c r="F47" s="50">
+      <c r="F47" s="51">
         <f>C47*E47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="50">
+      <c r="G47" s="51">
         <v>32</v>
       </c>
-      <c r="H47" s="50">
+      <c r="H47" s="51">
         <f>SUM(G47*C47)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="51" t="s">
+      <c r="I47" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J47" s="59"/>
-      <c r="K47" s="59"/>
-      <c r="L47" s="59"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="60"/>
     </row>
     <row r="48" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A48" s="50">
+      <c r="A48" s="51">
         <v>2</v>
       </c>
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41" t="s">
+      <c r="C48" s="42"/>
+      <c r="D48" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41">
+      <c r="E48" s="42"/>
+      <c r="F48" s="42">
         <f t="shared" ref="F48:F53" si="7">C48*E48</f>
         <v>0</v>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="42">
         <v>2.5</v>
       </c>
-      <c r="H48" s="41">
+      <c r="H48" s="42">
         <f t="shared" ref="H48:H53" si="8">SUM(G48*C48)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="42" t="s">
+      <c r="I48" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
     </row>
     <row r="49" ht="17" customHeight="1" spans="1:12">
-      <c r="A49" s="50">
+      <c r="A49" s="51">
         <v>3</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="41" t="s">
+      <c r="C49" s="44"/>
+      <c r="D49" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="44">
         <v>95</v>
       </c>
-      <c r="F49" s="41">
+      <c r="F49" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G49" s="43">
+      <c r="G49" s="44">
         <v>55</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I49" s="42" t="s">
+      <c r="I49" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A50" s="50">
+      <c r="A50" s="51">
         <v>4</v>
       </c>
-      <c r="B50" s="44" t="s">
+      <c r="B50" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="41"/>
-      <c r="D50" s="43" t="s">
+      <c r="C50" s="42"/>
+      <c r="D50" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E50" s="41">
+      <c r="E50" s="42">
         <v>2</v>
       </c>
-      <c r="F50" s="41">
+      <c r="F50" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="42">
         <v>4</v>
       </c>
-      <c r="H50" s="41">
+      <c r="H50" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I50" s="42" t="s">
+      <c r="I50" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
     </row>
     <row r="51" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A51" s="50">
+      <c r="A51" s="51">
         <v>5</v>
       </c>
-      <c r="B51" s="44" t="s">
+      <c r="B51" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41" t="s">
+      <c r="C51" s="42"/>
+      <c r="D51" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E51" s="41">
+      <c r="E51" s="42">
         <v>19</v>
       </c>
-      <c r="F51" s="41">
+      <c r="F51" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G51" s="41">
+      <c r="G51" s="42">
         <v>13</v>
       </c>
-      <c r="H51" s="41">
+      <c r="H51" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I51" s="42" t="s">
+      <c r="I51" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
     </row>
     <row r="52" ht="27" customHeight="1" spans="1:12">
-      <c r="A52" s="50">
+      <c r="A52" s="51">
         <v>6</v>
       </c>
-      <c r="B52" s="44" t="s">
+      <c r="B52" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41" t="s">
+      <c r="C52" s="42"/>
+      <c r="D52" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E52" s="41">
+      <c r="E52" s="42">
         <v>12</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G52" s="41">
+      <c r="G52" s="42">
         <v>7</v>
       </c>
-      <c r="H52" s="41">
+      <c r="H52" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I52" s="42" t="s">
+      <c r="I52" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:12">
-      <c r="A53" s="50">
+      <c r="A53" s="51">
         <v>7</v>
       </c>
-      <c r="B53" s="44" t="s">
+      <c r="B53" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41" t="s">
+      <c r="C53" s="42"/>
+      <c r="D53" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="41">
+      <c r="E53" s="42">
         <v>12</v>
       </c>
-      <c r="F53" s="41">
+      <c r="F53" s="42">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G53" s="41">
+      <c r="G53" s="42">
         <v>5</v>
       </c>
-      <c r="H53" s="41">
+      <c r="H53" s="42">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I53" s="42" t="s">
+      <c r="I53" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J53" s="34"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
     </row>
     <row r="54" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A54" s="61"/>
-      <c r="B54" s="62" t="s">
+      <c r="A54" s="62"/>
+      <c r="B54" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61">
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62">
         <f>SUM(F47:F53)</f>
         <v>0</v>
       </c>
-      <c r="G54" s="61"/>
-      <c r="H54" s="61">
+      <c r="G54" s="62"/>
+      <c r="H54" s="62">
         <f>SUM(H47:H53)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="63"/>
-      <c r="J54" s="64"/>
-      <c r="K54" s="64"/>
-      <c r="L54" s="64"/>
+      <c r="I54" s="64"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="65"/>
+      <c r="L54" s="65"/>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:12">
-      <c r="A55" s="39" t="s">
+      <c r="A55" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="40" t="s">
+      <c r="B55" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
     </row>
     <row r="56" s="6" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A56" s="50">
+      <c r="A56" s="51">
         <v>1</v>
       </c>
-      <c r="B56" s="66" t="s">
+      <c r="B56" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50" t="s">
+      <c r="C56" s="51"/>
+      <c r="D56" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="50">
+      <c r="E56" s="51">
         <v>28</v>
       </c>
-      <c r="F56" s="50">
+      <c r="F56" s="51">
         <f t="shared" ref="F56:F58" si="9">C56*E56</f>
         <v>0</v>
       </c>
-      <c r="G56" s="50">
+      <c r="G56" s="51">
         <v>32</v>
       </c>
-      <c r="H56" s="50">
+      <c r="H56" s="51">
         <f t="shared" ref="H56:H58" si="10">SUM(G56*C56)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="51" t="s">
+      <c r="I56" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J56" s="59"/>
-      <c r="K56" s="59"/>
-      <c r="L56" s="59"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="60"/>
+      <c r="L56" s="60"/>
     </row>
     <row r="57" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A57" s="50">
+      <c r="A57" s="51">
         <v>2</v>
       </c>
-      <c r="B57" s="66" t="s">
+      <c r="B57" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50" t="s">
+      <c r="C57" s="51"/>
+      <c r="D57" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="50">
+      <c r="E57" s="51">
         <v>28</v>
       </c>
-      <c r="F57" s="50">
+      <c r="F57" s="51">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G57" s="50">
+      <c r="G57" s="51">
         <v>40</v>
       </c>
-      <c r="H57" s="50">
+      <c r="H57" s="51">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I57" s="51" t="s">
+      <c r="I57" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="J57" s="59"/>
-      <c r="K57" s="59"/>
-      <c r="L57" s="59"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="60"/>
+      <c r="L57" s="60"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="1:12">
-      <c r="A58" s="50">
+      <c r="A58" s="51">
         <v>3</v>
       </c>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41" t="s">
+      <c r="C58" s="42"/>
+      <c r="D58" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E58" s="41">
-        <v>0</v>
-      </c>
-      <c r="F58" s="41">
+      <c r="E58" s="42">
+        <v>0</v>
+      </c>
+      <c r="F58" s="42">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G58" s="41">
+      <c r="G58" s="42">
         <v>9</v>
       </c>
-      <c r="H58" s="41">
+      <c r="H58" s="42">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I58" s="42" t="s">
+      <c r="I58" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="34"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
     </row>
     <row r="59" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A59" s="50">
+      <c r="A59" s="51">
         <v>4</v>
       </c>
-      <c r="B59" s="46" t="s">
+      <c r="B59" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41" t="s">
+      <c r="C59" s="42"/>
+      <c r="D59" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E59" s="41">
+      <c r="E59" s="42">
         <v>8</v>
       </c>
-      <c r="F59" s="41">
+      <c r="F59" s="42">
         <f t="shared" ref="F59:F64" si="11">C59*E59</f>
         <v>0</v>
       </c>
-      <c r="G59" s="41">
+      <c r="G59" s="42">
         <v>20</v>
       </c>
-      <c r="H59" s="41">
+      <c r="H59" s="42">
         <f t="shared" ref="H59:H64" si="12">SUM(G59*C59)</f>
         <v>0</v>
       </c>
-      <c r="I59" s="42" t="s">
+      <c r="I59" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="68"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
+      <c r="L59" s="69"/>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:12">
-      <c r="A60" s="50">
+      <c r="A60" s="51">
         <v>5</v>
       </c>
-      <c r="B60" s="44" t="s">
+      <c r="B60" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41" t="s">
+      <c r="C60" s="42"/>
+      <c r="D60" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41">
+      <c r="E60" s="42"/>
+      <c r="F60" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G60" s="41">
+      <c r="G60" s="42">
         <v>2.5</v>
       </c>
-      <c r="H60" s="41">
+      <c r="H60" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I60" s="42" t="s">
+      <c r="I60" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:12">
-      <c r="A61" s="50">
+      <c r="A61" s="51">
         <v>6</v>
       </c>
-      <c r="B61" s="44" t="s">
+      <c r="B61" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41" t="s">
+      <c r="C61" s="42"/>
+      <c r="D61" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E61" s="41">
+      <c r="E61" s="42">
         <v>45</v>
       </c>
-      <c r="F61" s="41">
+      <c r="F61" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G61" s="41">
+      <c r="G61" s="42">
         <v>20</v>
       </c>
-      <c r="H61" s="41">
+      <c r="H61" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I61" s="42" t="s">
+      <c r="I61" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+      <c r="L61" s="35"/>
     </row>
     <row r="62" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A62" s="50">
+      <c r="A62" s="51">
         <v>7</v>
       </c>
-      <c r="B62" s="44" t="s">
+      <c r="B62" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41" t="s">
+      <c r="C62" s="42"/>
+      <c r="D62" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="41">
+      <c r="E62" s="42">
         <v>22</v>
       </c>
-      <c r="F62" s="41">
+      <c r="F62" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G62" s="41">
+      <c r="G62" s="42">
         <v>12</v>
       </c>
-      <c r="H62" s="41">
+      <c r="H62" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I62" s="42" t="s">
+      <c r="I62" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="35"/>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:12">
-      <c r="A63" s="50">
+      <c r="A63" s="51">
         <v>8</v>
       </c>
-      <c r="B63" s="44" t="s">
+      <c r="B63" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41" t="s">
+      <c r="C63" s="42"/>
+      <c r="D63" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E63" s="41">
+      <c r="E63" s="42">
         <v>45</v>
       </c>
-      <c r="F63" s="41">
+      <c r="F63" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G63" s="41">
+      <c r="G63" s="42">
         <v>20</v>
       </c>
-      <c r="H63" s="41">
+      <c r="H63" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I63" s="42" t="s">
+      <c r="I63" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J63" s="34"/>
-      <c r="K63" s="34"/>
-      <c r="L63" s="34"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:12">
-      <c r="A64" s="50">
+      <c r="A64" s="51">
         <v>9</v>
       </c>
-      <c r="B64" s="44" t="s">
+      <c r="B64" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41" t="s">
+      <c r="C64" s="42"/>
+      <c r="D64" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E64" s="41">
+      <c r="E64" s="42">
         <v>12</v>
       </c>
-      <c r="F64" s="41">
+      <c r="F64" s="42">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G64" s="41">
+      <c r="G64" s="42">
         <v>5</v>
       </c>
-      <c r="H64" s="41">
+      <c r="H64" s="42">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I64" s="42" t="s">
+      <c r="I64" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J64" s="34"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="34"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35"/>
     </row>
     <row r="65" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A65" s="61"/>
-      <c r="B65" s="62" t="s">
+      <c r="A65" s="62"/>
+      <c r="B65" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C65" s="61"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61">
+      <c r="C65" s="62"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="62">
         <f>SUM(F56:F64)</f>
         <v>0</v>
       </c>
-      <c r="G65" s="61"/>
-      <c r="H65" s="61">
+      <c r="G65" s="62"/>
+      <c r="H65" s="62">
         <f>SUM(H56:H64)</f>
         <v>0</v>
       </c>
-      <c r="I65" s="63"/>
-      <c r="J65" s="64"/>
-      <c r="K65" s="64"/>
-      <c r="L65" s="64"/>
+      <c r="I65" s="64"/>
+      <c r="J65" s="65"/>
+      <c r="K65" s="65"/>
+      <c r="L65" s="65"/>
     </row>
     <row r="66" ht="18" customHeight="1" spans="1:12">
-      <c r="A66" s="39" t="s">
+      <c r="A66" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
-      <c r="L66" s="34"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
+      <c r="L66" s="35"/>
     </row>
     <row r="67" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A67" s="50">
+      <c r="A67" s="51">
         <v>1</v>
       </c>
-      <c r="B67" s="66" t="s">
+      <c r="B67" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="50"/>
-      <c r="D67" s="50" t="s">
+      <c r="C67" s="51"/>
+      <c r="D67" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E67" s="50">
+      <c r="E67" s="51">
         <v>28</v>
       </c>
-      <c r="F67" s="50">
+      <c r="F67" s="51">
         <f t="shared" ref="F67:F70" si="13">C67*E67</f>
         <v>0</v>
       </c>
-      <c r="G67" s="50">
+      <c r="G67" s="51">
         <v>32</v>
       </c>
-      <c r="H67" s="50">
+      <c r="H67" s="51">
         <f t="shared" ref="H67:H73" si="14">SUM(G67*C67)</f>
         <v>0</v>
       </c>
-      <c r="I67" s="51" t="s">
+      <c r="I67" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J67" s="59"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="59"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="60"/>
+      <c r="L67" s="60"/>
     </row>
     <row r="68" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A68" s="50">
+      <c r="A68" s="51">
         <v>2</v>
       </c>
-      <c r="B68" s="44" t="s">
+      <c r="B68" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C68" s="41"/>
-      <c r="D68" s="41" t="s">
+      <c r="C68" s="42"/>
+      <c r="D68" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41">
+      <c r="E68" s="42"/>
+      <c r="F68" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G68" s="41">
+      <c r="G68" s="42">
         <v>2.5</v>
       </c>
-      <c r="H68" s="41">
+      <c r="H68" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I68" s="42" t="s">
+      <c r="I68" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J68" s="34"/>
-      <c r="K68" s="34"/>
-      <c r="L68" s="34"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="35"/>
     </row>
     <row r="69" ht="18" customHeight="1" spans="1:12">
-      <c r="A69" s="50">
+      <c r="A69" s="51">
         <v>3</v>
       </c>
-      <c r="B69" s="47" t="s">
+      <c r="B69" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="41" t="s">
+      <c r="C69" s="44"/>
+      <c r="D69" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E69" s="43">
+      <c r="E69" s="44">
         <v>95</v>
       </c>
-      <c r="F69" s="41">
+      <c r="F69" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G69" s="43">
+      <c r="G69" s="44">
         <v>55</v>
       </c>
-      <c r="H69" s="41">
+      <c r="H69" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I69" s="42" t="s">
+      <c r="I69" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A70" s="50">
+      <c r="A70" s="51">
         <v>4</v>
       </c>
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="41"/>
-      <c r="D70" s="41" t="s">
+      <c r="C70" s="42"/>
+      <c r="D70" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="41">
+      <c r="E70" s="42">
         <v>65</v>
       </c>
-      <c r="F70" s="41">
+      <c r="F70" s="42">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G70" s="41">
+      <c r="G70" s="42">
         <v>85</v>
       </c>
-      <c r="H70" s="41">
+      <c r="H70" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I70" s="42" t="s">
+      <c r="I70" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="35"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A71" s="50">
+      <c r="A71" s="51">
         <v>5</v>
       </c>
-      <c r="B71" s="44" t="s">
+      <c r="B71" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C71" s="41"/>
-      <c r="D71" s="43" t="s">
+      <c r="C71" s="42"/>
+      <c r="D71" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E71" s="41">
+      <c r="E71" s="42">
         <v>2</v>
       </c>
-      <c r="F71" s="41">
+      <c r="F71" s="42">
         <f t="shared" ref="F71:F74" si="15">C71*E71</f>
         <v>0</v>
       </c>
-      <c r="G71" s="41">
+      <c r="G71" s="42">
         <v>4</v>
       </c>
-      <c r="H71" s="41">
+      <c r="H71" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I71" s="42" t="s">
+      <c r="I71" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J71" s="34"/>
-      <c r="K71" s="34"/>
-      <c r="L71" s="34"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="35"/>
     </row>
     <row r="72" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A72" s="50">
+      <c r="A72" s="51">
         <v>6</v>
       </c>
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C72" s="41"/>
-      <c r="D72" s="41" t="s">
+      <c r="C72" s="42"/>
+      <c r="D72" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E72" s="41">
+      <c r="E72" s="42">
         <v>19</v>
       </c>
-      <c r="F72" s="41">
+      <c r="F72" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G72" s="41">
+      <c r="G72" s="42">
         <v>13</v>
       </c>
-      <c r="H72" s="41">
+      <c r="H72" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I72" s="42" t="s">
+      <c r="I72" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="34"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="35"/>
+      <c r="L72" s="35"/>
     </row>
     <row r="73" ht="27" customHeight="1" spans="1:12">
-      <c r="A73" s="50">
+      <c r="A73" s="51">
         <v>7</v>
       </c>
-      <c r="B73" s="44" t="s">
+      <c r="B73" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41" t="s">
+      <c r="C73" s="42"/>
+      <c r="D73" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E73" s="41">
+      <c r="E73" s="42">
         <v>12</v>
       </c>
-      <c r="F73" s="41">
+      <c r="F73" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G73" s="41">
+      <c r="G73" s="42">
         <v>7</v>
       </c>
-      <c r="H73" s="41">
+      <c r="H73" s="42">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I73" s="42" t="s">
+      <c r="I73" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J73" s="34"/>
-      <c r="K73" s="34"/>
-      <c r="L73" s="34"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
+      <c r="L73" s="35"/>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:12">
-      <c r="A74" s="50">
+      <c r="A74" s="51">
         <v>8</v>
       </c>
-      <c r="B74" s="44" t="s">
+      <c r="B74" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="41"/>
-      <c r="D74" s="41" t="s">
+      <c r="C74" s="42"/>
+      <c r="D74" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="41">
+      <c r="E74" s="42">
         <v>12</v>
       </c>
-      <c r="F74" s="41">
+      <c r="F74" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G74" s="41">
+      <c r="G74" s="42">
         <v>5</v>
       </c>
-      <c r="H74" s="41">
+      <c r="H74" s="42">
         <f t="shared" ref="H74:H83" si="16">SUM(G74*C74)</f>
         <v>0</v>
       </c>
-      <c r="I74" s="42" t="s">
+      <c r="I74" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J74" s="34"/>
-      <c r="K74" s="34"/>
-      <c r="L74" s="34"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="35"/>
+      <c r="L74" s="35"/>
     </row>
     <row r="75" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A75" s="61"/>
-      <c r="B75" s="62" t="s">
+      <c r="A75" s="62"/>
+      <c r="B75" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61">
+      <c r="C75" s="62"/>
+      <c r="D75" s="62"/>
+      <c r="E75" s="62"/>
+      <c r="F75" s="62">
         <f>SUM(F67:F74)</f>
         <v>0</v>
       </c>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61">
+      <c r="G75" s="62"/>
+      <c r="H75" s="62">
         <f>SUM(H67:H74)</f>
         <v>0</v>
       </c>
-      <c r="I75" s="63"/>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="64"/>
+      <c r="I75" s="64"/>
+      <c r="J75" s="65"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
     </row>
     <row r="76" ht="18" customHeight="1" spans="1:12">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C76" s="41"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="41"/>
-      <c r="I76" s="42"/>
-      <c r="J76" s="34"/>
-      <c r="K76" s="34"/>
-      <c r="L76" s="34"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="43"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="35"/>
     </row>
     <row r="77" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A77" s="50">
+      <c r="A77" s="51">
         <v>1</v>
       </c>
-      <c r="B77" s="66" t="s">
+      <c r="B77" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C77" s="50"/>
-      <c r="D77" s="50" t="s">
+      <c r="C77" s="51"/>
+      <c r="D77" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E77" s="50">
+      <c r="E77" s="51">
         <v>28</v>
       </c>
-      <c r="F77" s="50">
+      <c r="F77" s="51">
         <f t="shared" ref="F77:F83" si="17">C77*E77</f>
         <v>0</v>
       </c>
-      <c r="G77" s="50">
+      <c r="G77" s="51">
         <v>32</v>
       </c>
-      <c r="H77" s="50">
+      <c r="H77" s="51">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I77" s="51" t="s">
+      <c r="I77" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J77" s="59"/>
-      <c r="K77" s="59"/>
-      <c r="L77" s="59"/>
+      <c r="J77" s="60"/>
+      <c r="K77" s="60"/>
+      <c r="L77" s="60"/>
     </row>
     <row r="78" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A78" s="50">
+      <c r="A78" s="51">
         <v>2</v>
       </c>
-      <c r="B78" s="44" t="s">
+      <c r="B78" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="41"/>
-      <c r="D78" s="41" t="s">
+      <c r="C78" s="42"/>
+      <c r="D78" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="41"/>
-      <c r="F78" s="41">
+      <c r="E78" s="42"/>
+      <c r="F78" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G78" s="41">
+      <c r="G78" s="42">
         <v>2.5</v>
       </c>
-      <c r="H78" s="41">
+      <c r="H78" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I78" s="42" t="s">
+      <c r="I78" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="J78" s="34"/>
-      <c r="K78" s="34"/>
-      <c r="L78" s="34"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="35"/>
+      <c r="L78" s="35"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A79" s="50">
+      <c r="A79" s="51">
         <v>3</v>
       </c>
-      <c r="B79" s="44" t="s">
+      <c r="B79" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41" t="s">
+      <c r="C79" s="42"/>
+      <c r="D79" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E79" s="41">
+      <c r="E79" s="42">
         <v>65</v>
       </c>
-      <c r="F79" s="41">
+      <c r="F79" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G79" s="41">
+      <c r="G79" s="42">
         <v>85</v>
       </c>
-      <c r="H79" s="41">
+      <c r="H79" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I79" s="42" t="s">
+      <c r="I79" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="J79" s="34"/>
-      <c r="K79" s="34"/>
-      <c r="L79" s="34"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="35"/>
+      <c r="L79" s="35"/>
     </row>
     <row r="80" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A80" s="50">
+      <c r="A80" s="51">
         <v>4</v>
       </c>
-      <c r="B80" s="44" t="s">
+      <c r="B80" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C80" s="41"/>
-      <c r="D80" s="43" t="s">
+      <c r="C80" s="42"/>
+      <c r="D80" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E80" s="41">
+      <c r="E80" s="42">
         <v>2</v>
       </c>
-      <c r="F80" s="41">
+      <c r="F80" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G80" s="41">
+      <c r="G80" s="42">
         <v>4</v>
       </c>
-      <c r="H80" s="41">
+      <c r="H80" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I80" s="42" t="s">
+      <c r="I80" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="J80" s="34"/>
-      <c r="K80" s="34"/>
-      <c r="L80" s="34"/>
+      <c r="J80" s="35"/>
+      <c r="K80" s="35"/>
+      <c r="L80" s="35"/>
     </row>
     <row r="81" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A81" s="50">
+      <c r="A81" s="51">
         <v>5</v>
       </c>
-      <c r="B81" s="44" t="s">
+      <c r="B81" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="C81" s="41"/>
-      <c r="D81" s="41" t="s">
+      <c r="C81" s="42"/>
+      <c r="D81" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E81" s="41">
+      <c r="E81" s="42">
         <v>19</v>
       </c>
-      <c r="F81" s="41">
+      <c r="F81" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G81" s="41">
+      <c r="G81" s="42">
         <v>13</v>
       </c>
-      <c r="H81" s="41">
+      <c r="H81" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I81" s="42" t="s">
+      <c r="I81" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J81" s="34"/>
-      <c r="K81" s="34"/>
-      <c r="L81" s="34"/>
+      <c r="J81" s="35"/>
+      <c r="K81" s="35"/>
+      <c r="L81" s="35"/>
     </row>
     <row r="82" ht="27" customHeight="1" spans="1:12">
-      <c r="A82" s="50">
+      <c r="A82" s="51">
         <v>6</v>
       </c>
-      <c r="B82" s="44" t="s">
+      <c r="B82" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="41"/>
-      <c r="D82" s="41" t="s">
+      <c r="C82" s="42"/>
+      <c r="D82" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E82" s="41">
+      <c r="E82" s="42">
         <v>12</v>
       </c>
-      <c r="F82" s="41">
+      <c r="F82" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G82" s="41">
+      <c r="G82" s="42">
         <v>7</v>
       </c>
-      <c r="H82" s="41">
+      <c r="H82" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I82" s="42" t="s">
+      <c r="I82" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="J82" s="34"/>
-      <c r="K82" s="34"/>
-      <c r="L82" s="34"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="35"/>
+      <c r="L82" s="35"/>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:12">
-      <c r="A83" s="50">
+      <c r="A83" s="51">
         <v>7</v>
       </c>
-      <c r="B83" s="44" t="s">
+      <c r="B83" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41" t="s">
+      <c r="C83" s="42"/>
+      <c r="D83" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E83" s="41">
+      <c r="E83" s="42">
         <v>12</v>
       </c>
-      <c r="F83" s="41">
+      <c r="F83" s="42">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G83" s="41">
+      <c r="G83" s="42">
         <v>5</v>
       </c>
-      <c r="H83" s="41">
+      <c r="H83" s="42">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I83" s="42" t="s">
+      <c r="I83" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="J83" s="34"/>
-      <c r="K83" s="34"/>
-      <c r="L83" s="34"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="35"/>
+      <c r="L83" s="35"/>
     </row>
     <row r="84" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A84" s="61"/>
-      <c r="B84" s="62" t="s">
+      <c r="A84" s="62"/>
+      <c r="B84" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61">
+      <c r="C84" s="62"/>
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62">
         <f>SUM(F77:F83)</f>
         <v>0</v>
       </c>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61">
+      <c r="G84" s="62"/>
+      <c r="H84" s="62">
         <f>SUM(H77:H83)</f>
         <v>0</v>
       </c>
-      <c r="I84" s="63"/>
-      <c r="J84" s="64"/>
-      <c r="K84" s="64"/>
-      <c r="L84" s="64"/>
+      <c r="I84" s="64"/>
+      <c r="J84" s="65"/>
+      <c r="K84" s="65"/>
+      <c r="L84" s="65"/>
     </row>
     <row r="85" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A85" s="39" t="s">
+      <c r="A85" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="40" t="s">
+      <c r="B85" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="42"/>
-      <c r="J85" s="34"/>
-      <c r="K85" s="34"/>
-      <c r="L85" s="34"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="43"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35"/>
     </row>
     <row r="86" ht="18" customHeight="1" spans="1:12">
-      <c r="A86" s="41" t="s">
+      <c r="A86" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="78" t="s">
+      <c r="B86" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="80"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="34"/>
-      <c r="K86" s="34"/>
-      <c r="L86" s="34"/>
+      <c r="C86" s="80"/>
+      <c r="D86" s="80"/>
+      <c r="E86" s="81"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="43"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="35"/>
+      <c r="L86" s="35"/>
     </row>
     <row r="87" s="6" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A87" s="50">
+      <c r="A87" s="51">
         <v>1</v>
       </c>
-      <c r="B87" s="66" t="s">
+      <c r="B87" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="50"/>
-      <c r="D87" s="50" t="s">
+      <c r="C87" s="51"/>
+      <c r="D87" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E87" s="50">
+      <c r="E87" s="51">
         <v>14</v>
       </c>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50">
+      <c r="F87" s="51"/>
+      <c r="G87" s="51">
         <v>12</v>
       </c>
-      <c r="H87" s="50"/>
-      <c r="I87" s="51" t="s">
+      <c r="H87" s="51"/>
+      <c r="I87" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
+      <c r="J87" s="60"/>
+      <c r="K87" s="60"/>
+      <c r="L87" s="60"/>
     </row>
     <row r="88" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A88" s="50">
+      <c r="A88" s="51">
         <v>2</v>
       </c>
-      <c r="B88" s="66" t="s">
+      <c r="B88" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C88" s="50"/>
-      <c r="D88" s="50" t="s">
+      <c r="C88" s="51"/>
+      <c r="D88" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E88" s="50">
+      <c r="E88" s="51">
         <v>6</v>
       </c>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50">
+      <c r="F88" s="51"/>
+      <c r="G88" s="51">
         <v>11</v>
       </c>
-      <c r="H88" s="50"/>
-      <c r="I88" s="51" t="s">
+      <c r="H88" s="51"/>
+      <c r="I88" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
+      <c r="J88" s="60"/>
+      <c r="K88" s="60"/>
+      <c r="L88" s="60"/>
     </row>
     <row r="89" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A89" s="50">
+      <c r="A89" s="51">
         <v>3</v>
       </c>
-      <c r="B89" s="66" t="s">
+      <c r="B89" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C89" s="50"/>
-      <c r="D89" s="50" t="s">
+      <c r="C89" s="51"/>
+      <c r="D89" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E89" s="50">
+      <c r="E89" s="51">
         <v>6</v>
       </c>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50">
+      <c r="F89" s="51"/>
+      <c r="G89" s="51">
         <v>11</v>
       </c>
-      <c r="H89" s="50"/>
-      <c r="I89" s="51" t="s">
+      <c r="H89" s="51"/>
+      <c r="I89" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
+      <c r="J89" s="60"/>
+      <c r="K89" s="60"/>
+      <c r="L89" s="60"/>
     </row>
     <row r="90" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A90" s="50">
+      <c r="A90" s="51">
         <v>4</v>
       </c>
-      <c r="B90" s="66" t="s">
+      <c r="B90" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="50"/>
-      <c r="D90" s="50" t="s">
+      <c r="C90" s="51"/>
+      <c r="D90" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E90" s="50">
+      <c r="E90" s="51">
         <v>6</v>
       </c>
-      <c r="F90" s="50"/>
-      <c r="G90" s="50">
+      <c r="F90" s="51"/>
+      <c r="G90" s="51">
         <v>11</v>
       </c>
-      <c r="H90" s="50"/>
-      <c r="I90" s="51" t="s">
+      <c r="H90" s="51"/>
+      <c r="I90" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
+      <c r="J90" s="60"/>
+      <c r="K90" s="60"/>
+      <c r="L90" s="60"/>
     </row>
     <row r="91" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A91" s="50">
+      <c r="A91" s="51">
         <v>5</v>
       </c>
-      <c r="B91" s="66" t="s">
+      <c r="B91" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C91" s="50"/>
-      <c r="D91" s="50" t="s">
+      <c r="C91" s="51"/>
+      <c r="D91" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E91" s="50">
+      <c r="E91" s="51">
         <v>6</v>
       </c>
-      <c r="F91" s="50"/>
-      <c r="G91" s="50">
+      <c r="F91" s="51"/>
+      <c r="G91" s="51">
         <v>11</v>
       </c>
-      <c r="H91" s="50"/>
-      <c r="I91" s="51" t="s">
+      <c r="H91" s="51"/>
+      <c r="I91" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
+      <c r="J91" s="60"/>
+      <c r="K91" s="60"/>
+      <c r="L91" s="60"/>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:12">
-      <c r="A92" s="41">
+      <c r="A92" s="42">
         <v>6</v>
       </c>
-      <c r="B92" s="44" t="s">
+      <c r="B92" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41" t="s">
+      <c r="C92" s="42"/>
+      <c r="D92" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E92" s="41">
+      <c r="E92" s="42">
         <v>10</v>
       </c>
-      <c r="F92" s="41"/>
-      <c r="G92" s="41">
+      <c r="F92" s="42"/>
+      <c r="G92" s="42">
         <v>6</v>
       </c>
-      <c r="H92" s="41"/>
-      <c r="I92" s="42" t="s">
+      <c r="H92" s="42"/>
+      <c r="I92" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="J92" s="34"/>
-      <c r="K92" s="34"/>
-      <c r="L92" s="34"/>
+      <c r="J92" s="35"/>
+      <c r="K92" s="35"/>
+      <c r="L92" s="35"/>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:12">
-      <c r="A93" s="41">
+      <c r="A93" s="42">
         <v>7</v>
       </c>
-      <c r="B93" s="44" t="s">
+      <c r="B93" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="C93" s="41"/>
-      <c r="D93" s="41" t="s">
+      <c r="C93" s="42"/>
+      <c r="D93" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="41">
+      <c r="E93" s="42">
         <v>75</v>
       </c>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41">
+      <c r="F93" s="42"/>
+      <c r="G93" s="42">
         <v>45</v>
       </c>
-      <c r="H93" s="45"/>
-      <c r="I93" s="42" t="s">
+      <c r="H93" s="46"/>
+      <c r="I93" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="J93" s="34"/>
-      <c r="K93" s="34"/>
-      <c r="L93" s="34"/>
+      <c r="J93" s="35"/>
+      <c r="K93" s="35"/>
+      <c r="L93" s="35"/>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:12">
-      <c r="A94" s="41">
+      <c r="A94" s="42">
         <v>8</v>
       </c>
-      <c r="B94" s="44" t="s">
+      <c r="B94" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41" t="s">
+      <c r="C94" s="42"/>
+      <c r="D94" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="41">
+      <c r="E94" s="42">
         <v>2</v>
       </c>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41">
+      <c r="F94" s="42"/>
+      <c r="G94" s="42">
         <v>4</v>
       </c>
-      <c r="H94" s="41"/>
-      <c r="I94" s="42" t="s">
+      <c r="H94" s="42"/>
+      <c r="I94" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="J94" s="34"/>
-      <c r="K94" s="34"/>
-      <c r="L94" s="34"/>
+      <c r="J94" s="35"/>
+      <c r="K94" s="35"/>
+      <c r="L94" s="35"/>
     </row>
     <row r="95" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A95" s="50">
+      <c r="A95" s="51">
         <v>9</v>
       </c>
-      <c r="B95" s="66" t="s">
+      <c r="B95" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="C95" s="50"/>
-      <c r="D95" s="50" t="s">
+      <c r="C95" s="51"/>
+      <c r="D95" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="50">
+      <c r="E95" s="51">
         <v>18</v>
       </c>
-      <c r="F95" s="50"/>
-      <c r="G95" s="50">
+      <c r="F95" s="51"/>
+      <c r="G95" s="51">
         <v>13</v>
       </c>
-      <c r="H95" s="50"/>
-      <c r="I95" s="81" t="s">
+      <c r="H95" s="51"/>
+      <c r="I95" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="J95" s="59"/>
-      <c r="K95" s="59"/>
-      <c r="L95" s="59"/>
+      <c r="J95" s="60"/>
+      <c r="K95" s="60"/>
+      <c r="L95" s="60"/>
     </row>
     <row r="96" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A96" s="50">
+      <c r="A96" s="51">
         <v>10</v>
       </c>
-      <c r="B96" s="66" t="s">
+      <c r="B96" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="C96" s="50"/>
-      <c r="D96" s="50" t="s">
+      <c r="C96" s="51"/>
+      <c r="D96" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E96" s="50">
+      <c r="E96" s="51">
         <v>25</v>
       </c>
-      <c r="F96" s="50"/>
-      <c r="G96" s="50">
+      <c r="F96" s="51"/>
+      <c r="G96" s="51">
         <v>15</v>
       </c>
-      <c r="H96" s="82"/>
-      <c r="I96" s="81" t="s">
+      <c r="H96" s="83"/>
+      <c r="I96" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="J96" s="59"/>
-      <c r="K96" s="59"/>
-      <c r="L96" s="59"/>
+      <c r="J96" s="60"/>
+      <c r="K96" s="60"/>
+      <c r="L96" s="60"/>
     </row>
     <row r="97" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A97" s="50">
+      <c r="A97" s="51">
         <v>11</v>
       </c>
-      <c r="B97" s="66" t="s">
+      <c r="B97" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="C97" s="50"/>
-      <c r="D97" s="50" t="s">
+      <c r="C97" s="51"/>
+      <c r="D97" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E97" s="50">
+      <c r="E97" s="51">
         <v>55</v>
       </c>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50">
+      <c r="F97" s="51"/>
+      <c r="G97" s="51">
         <v>20</v>
       </c>
-      <c r="H97" s="82"/>
-      <c r="I97" s="81" t="s">
+      <c r="H97" s="83"/>
+      <c r="I97" s="82" t="s">
         <v>107</v>
       </c>
-      <c r="J97" s="59"/>
-      <c r="K97" s="59"/>
-      <c r="L97" s="59"/>
+      <c r="J97" s="60"/>
+      <c r="K97" s="60"/>
+      <c r="L97" s="60"/>
     </row>
     <row r="98" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A98" s="41">
+      <c r="A98" s="42">
         <v>12</v>
       </c>
-      <c r="B98" s="44" t="s">
+      <c r="B98" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="C98" s="41"/>
-      <c r="D98" s="41" t="s">
+      <c r="C98" s="42"/>
+      <c r="D98" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E98" s="41">
+      <c r="E98" s="42">
         <v>150</v>
       </c>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41">
+      <c r="F98" s="42"/>
+      <c r="G98" s="42">
         <v>180</v>
       </c>
-      <c r="H98" s="41"/>
-      <c r="I98" s="42" t="s">
+      <c r="H98" s="42"/>
+      <c r="I98" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="J98" s="34"/>
-      <c r="K98" s="34"/>
-      <c r="L98" s="34"/>
+      <c r="J98" s="35"/>
+      <c r="K98" s="35"/>
+      <c r="L98" s="35"/>
     </row>
     <row r="99" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A99" s="41">
+      <c r="A99" s="42">
         <v>13</v>
       </c>
-      <c r="B99" s="44" t="s">
+      <c r="B99" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C99" s="41"/>
-      <c r="D99" s="41" t="s">
+      <c r="C99" s="42"/>
+      <c r="D99" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E99" s="41">
+      <c r="E99" s="42">
         <v>240</v>
       </c>
-      <c r="F99" s="41"/>
-      <c r="G99" s="41">
+      <c r="F99" s="42"/>
+      <c r="G99" s="42">
         <v>160</v>
       </c>
-      <c r="H99" s="41"/>
-      <c r="I99" s="42" t="s">
+      <c r="H99" s="42"/>
+      <c r="I99" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="J99" s="34"/>
-      <c r="K99" s="34"/>
-      <c r="L99" s="34"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="35"/>
+      <c r="L99" s="35"/>
     </row>
     <row r="100" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A100" s="41">
+      <c r="A100" s="42">
         <v>14</v>
       </c>
-      <c r="B100" s="44" t="s">
+      <c r="B100" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="C100" s="41"/>
-      <c r="D100" s="41" t="s">
+      <c r="C100" s="42"/>
+      <c r="D100" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E100" s="41">
+      <c r="E100" s="42">
         <v>120</v>
       </c>
-      <c r="F100" s="41"/>
-      <c r="G100" s="41">
+      <c r="F100" s="42"/>
+      <c r="G100" s="42">
         <v>380</v>
       </c>
-      <c r="H100" s="41"/>
-      <c r="I100" s="42" t="s">
+      <c r="H100" s="42"/>
+      <c r="I100" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="J100" s="34"/>
-      <c r="K100" s="34"/>
-      <c r="L100" s="34"/>
+      <c r="J100" s="35"/>
+      <c r="K100" s="35"/>
+      <c r="L100" s="35"/>
     </row>
     <row r="101" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A101" s="41">
+      <c r="A101" s="42">
         <v>15</v>
       </c>
-      <c r="B101" s="67" t="s">
+      <c r="B101" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="C101" s="83"/>
-      <c r="D101" s="41" t="s">
+      <c r="C101" s="84"/>
+      <c r="D101" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E101" s="83"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41">
+      <c r="E101" s="84"/>
+      <c r="F101" s="42"/>
+      <c r="G101" s="42">
         <v>5</v>
       </c>
-      <c r="H101" s="45"/>
-      <c r="I101" s="84" t="s">
+      <c r="H101" s="46"/>
+      <c r="I101" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="J101" s="34"/>
-      <c r="K101" s="85"/>
-      <c r="L101" s="85"/>
+      <c r="J101" s="35"/>
+      <c r="K101" s="86"/>
+      <c r="L101" s="86"/>
     </row>
     <row r="102" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A102" s="61"/>
-      <c r="B102" s="62" t="s">
+      <c r="A102" s="62"/>
+      <c r="B102" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C102" s="61"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61"/>
-      <c r="I102" s="63"/>
-      <c r="J102" s="64"/>
-      <c r="K102" s="64"/>
-      <c r="L102" s="64"/>
+      <c r="C102" s="62"/>
+      <c r="D102" s="62"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="62"/>
+      <c r="H102" s="62"/>
+      <c r="I102" s="64"/>
+      <c r="J102" s="65"/>
+      <c r="K102" s="65"/>
+      <c r="L102" s="65"/>
     </row>
     <row r="103" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A103" s="41" t="s">
+      <c r="A103" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="B103" s="75" t="s">
+      <c r="B103" s="76" t="s">
         <v>116</v>
       </c>
-      <c r="C103" s="76"/>
-      <c r="D103" s="76"/>
-      <c r="E103" s="77"/>
-      <c r="F103" s="41"/>
-      <c r="G103" s="41"/>
-      <c r="H103" s="41"/>
-      <c r="I103" s="42"/>
-      <c r="J103" s="34"/>
-      <c r="K103" s="34"/>
-      <c r="L103" s="34"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
+      <c r="E103" s="78"/>
+      <c r="F103" s="42"/>
+      <c r="G103" s="42"/>
+      <c r="H103" s="42"/>
+      <c r="I103" s="43"/>
+      <c r="J103" s="35"/>
+      <c r="K103" s="35"/>
+      <c r="L103" s="35"/>
     </row>
     <row r="104" s="6" customFormat="1" ht="24.75" customHeight="1" spans="1:12">
-      <c r="A104" s="50">
+      <c r="A104" s="51">
         <v>1</v>
       </c>
-      <c r="B104" s="66" t="s">
+      <c r="B104" s="67" t="s">
         <v>117</v>
       </c>
-      <c r="C104" s="50"/>
-      <c r="D104" s="50" t="s">
+      <c r="C104" s="51"/>
+      <c r="D104" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="50">
+      <c r="E104" s="51">
         <v>36</v>
       </c>
-      <c r="F104" s="50"/>
-      <c r="G104" s="50">
+      <c r="F104" s="51"/>
+      <c r="G104" s="51">
         <v>33</v>
       </c>
-      <c r="H104" s="50"/>
-      <c r="I104" s="51" t="s">
+      <c r="H104" s="51"/>
+      <c r="I104" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="J104" s="59"/>
-      <c r="K104" s="59"/>
-      <c r="L104" s="59"/>
+      <c r="J104" s="60"/>
+      <c r="K104" s="60"/>
+      <c r="L104" s="60"/>
     </row>
     <row r="105" ht="25.5" customHeight="1" spans="1:12">
-      <c r="A105" s="41">
+      <c r="A105" s="42">
         <v>2</v>
       </c>
-      <c r="B105" s="44" t="s">
+      <c r="B105" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="C105" s="41"/>
-      <c r="D105" s="41" t="s">
+      <c r="C105" s="42"/>
+      <c r="D105" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="41">
+      <c r="E105" s="42">
         <v>38</v>
       </c>
-      <c r="F105" s="41"/>
-      <c r="G105" s="41">
+      <c r="F105" s="42"/>
+      <c r="G105" s="42">
         <v>40</v>
       </c>
-      <c r="H105" s="41"/>
-      <c r="I105" s="42" t="s">
+      <c r="H105" s="42"/>
+      <c r="I105" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="J105" s="34"/>
-      <c r="K105" s="34"/>
-      <c r="L105" s="34"/>
+      <c r="J105" s="35"/>
+      <c r="K105" s="35"/>
+      <c r="L105" s="35"/>
     </row>
     <row r="106" ht="24.5" customHeight="1" spans="1:12">
-      <c r="A106" s="41">
+      <c r="A106" s="42">
         <v>3</v>
       </c>
-      <c r="B106" s="44" t="s">
+      <c r="B106" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="C106" s="41"/>
-      <c r="D106" s="41" t="s">
+      <c r="C106" s="42"/>
+      <c r="D106" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="41">
+      <c r="E106" s="42">
         <v>48</v>
       </c>
-      <c r="F106" s="41"/>
-      <c r="G106" s="41">
+      <c r="F106" s="42"/>
+      <c r="G106" s="42">
         <v>70</v>
       </c>
-      <c r="H106" s="41"/>
-      <c r="I106" s="42" t="s">
+      <c r="H106" s="42"/>
+      <c r="I106" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="J106" s="34"/>
-      <c r="K106" s="34"/>
-      <c r="L106" s="34"/>
+      <c r="J106" s="35"/>
+      <c r="K106" s="35"/>
+      <c r="L106" s="35"/>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:12">
-      <c r="A107" s="41">
+      <c r="A107" s="42">
         <v>4</v>
       </c>
-      <c r="B107" s="44" t="s">
+      <c r="B107" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="C107" s="41"/>
-      <c r="D107" s="41" t="s">
+      <c r="C107" s="42"/>
+      <c r="D107" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E107" s="41">
+      <c r="E107" s="42">
         <v>20</v>
       </c>
-      <c r="F107" s="41"/>
-      <c r="G107" s="41">
+      <c r="F107" s="42"/>
+      <c r="G107" s="42">
         <v>15</v>
       </c>
-      <c r="H107" s="41"/>
-      <c r="I107" s="42" t="s">
+      <c r="H107" s="42"/>
+      <c r="I107" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="J107" s="34"/>
-      <c r="K107" s="34"/>
-      <c r="L107" s="34"/>
+      <c r="J107" s="35"/>
+      <c r="K107" s="35"/>
+      <c r="L107" s="35"/>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:12">
-      <c r="A108" s="41">
+      <c r="A108" s="42">
         <v>5</v>
       </c>
-      <c r="B108" s="44" t="s">
+      <c r="B108" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="C108" s="41"/>
-      <c r="D108" s="41" t="s">
+      <c r="C108" s="42"/>
+      <c r="D108" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="E108" s="41">
+      <c r="E108" s="42">
         <v>135</v>
       </c>
-      <c r="F108" s="41"/>
-      <c r="G108" s="41">
+      <c r="F108" s="42"/>
+      <c r="G108" s="42">
         <v>35</v>
       </c>
-      <c r="H108" s="41"/>
-      <c r="I108" s="42" t="s">
+      <c r="H108" s="42"/>
+      <c r="I108" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="J108" s="34"/>
-      <c r="K108" s="34"/>
-      <c r="L108" s="34"/>
+      <c r="J108" s="35"/>
+      <c r="K108" s="35"/>
+      <c r="L108" s="35"/>
     </row>
     <row r="109" s="7" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A109" s="61"/>
-      <c r="B109" s="62" t="s">
+      <c r="A109" s="62"/>
+      <c r="B109" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C109" s="61"/>
-      <c r="D109" s="61"/>
-      <c r="E109" s="61"/>
-      <c r="F109" s="61"/>
-      <c r="G109" s="61"/>
-      <c r="H109" s="61"/>
-      <c r="I109" s="63"/>
-      <c r="J109" s="64"/>
-      <c r="K109" s="64"/>
-      <c r="L109" s="64"/>
+      <c r="C109" s="62"/>
+      <c r="D109" s="62"/>
+      <c r="E109" s="62"/>
+      <c r="F109" s="62"/>
+      <c r="G109" s="62"/>
+      <c r="H109" s="62"/>
+      <c r="I109" s="64"/>
+      <c r="J109" s="65"/>
+      <c r="K109" s="65"/>
+      <c r="L109" s="65"/>
     </row>
     <row r="110" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="B110" s="40" t="s">
+      <c r="B110" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="C110" s="41"/>
-      <c r="D110" s="41"/>
-      <c r="E110" s="41"/>
-      <c r="F110" s="41"/>
-      <c r="G110" s="41"/>
-      <c r="H110" s="41"/>
-      <c r="I110" s="42"/>
-      <c r="J110" s="34"/>
-      <c r="K110" s="34"/>
-      <c r="L110" s="34"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="42"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="42"/>
+      <c r="H110" s="42"/>
+      <c r="I110" s="43"/>
+      <c r="J110" s="35"/>
+      <c r="K110" s="35"/>
+      <c r="L110" s="35"/>
     </row>
     <row r="111" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A111" s="41">
+      <c r="A111" s="42">
         <v>1</v>
       </c>
-      <c r="B111" s="44" t="s">
+      <c r="B111" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="C111" s="41"/>
-      <c r="D111" s="41" t="s">
+      <c r="C111" s="42"/>
+      <c r="D111" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="41">
+      <c r="E111" s="42">
         <v>22</v>
       </c>
-      <c r="F111" s="41">
+      <c r="F111" s="42">
         <f>C111*E111</f>
         <v>0</v>
       </c>
-      <c r="G111" s="41">
+      <c r="G111" s="42">
         <v>25</v>
       </c>
-      <c r="H111" s="41">
+      <c r="H111" s="42">
         <f>SUM(G111*C111)</f>
         <v>0</v>
       </c>
-      <c r="I111" s="42" t="s">
+      <c r="I111" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="J111" s="34"/>
-      <c r="K111" s="34"/>
-      <c r="L111" s="34"/>
+      <c r="J111" s="35"/>
+      <c r="K111" s="35"/>
+      <c r="L111" s="35"/>
     </row>
     <row r="112" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A112" s="41">
+      <c r="A112" s="42">
         <v>2</v>
       </c>
-      <c r="B112" s="44" t="s">
+      <c r="B112" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="C112" s="41"/>
-      <c r="D112" s="41" t="s">
+      <c r="C112" s="42"/>
+      <c r="D112" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E112" s="41">
+      <c r="E112" s="42">
         <v>160</v>
       </c>
-      <c r="F112" s="41">
+      <c r="F112" s="42">
         <f t="shared" ref="F112:F131" si="18">C112*E112</f>
         <v>0</v>
       </c>
-      <c r="G112" s="41">
+      <c r="G112" s="42">
         <v>125</v>
       </c>
-      <c r="H112" s="41">
+      <c r="H112" s="42">
         <f t="shared" ref="H112:H131" si="19">SUM(G112*C112)</f>
         <v>0</v>
       </c>
-      <c r="I112" s="42" t="s">
+      <c r="I112" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="J112" s="87"/>
-      <c r="K112" s="87"/>
-      <c r="L112" s="87"/>
+      <c r="J112" s="88"/>
+      <c r="K112" s="88"/>
+      <c r="L112" s="88"/>
     </row>
     <row r="113" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A113" s="41">
+      <c r="A113" s="42">
         <v>3</v>
       </c>
-      <c r="B113" s="44" t="s">
+      <c r="B113" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41" t="s">
+      <c r="C113" s="42"/>
+      <c r="D113" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E113" s="41">
+      <c r="E113" s="42">
         <v>95</v>
       </c>
-      <c r="F113" s="41">
+      <c r="F113" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G113" s="41">
+      <c r="G113" s="42">
         <v>75</v>
       </c>
-      <c r="H113" s="41">
+      <c r="H113" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I113" s="42" t="s">
+      <c r="I113" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="J113" s="34"/>
-      <c r="K113" s="34"/>
-      <c r="L113" s="34"/>
+      <c r="J113" s="35"/>
+      <c r="K113" s="35"/>
+      <c r="L113" s="35"/>
     </row>
     <row r="114" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A114" s="41">
+      <c r="A114" s="42">
         <v>4</v>
       </c>
-      <c r="B114" s="44" t="s">
+      <c r="B114" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="C114" s="41"/>
-      <c r="D114" s="41" t="s">
+      <c r="C114" s="42"/>
+      <c r="D114" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="E114" s="41">
+      <c r="E114" s="42">
         <v>120</v>
       </c>
-      <c r="F114" s="41">
+      <c r="F114" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G114" s="41">
+      <c r="G114" s="42">
         <v>90</v>
       </c>
-      <c r="H114" s="41">
+      <c r="H114" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I114" s="42" t="s">
+      <c r="I114" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="J114" s="34"/>
-      <c r="K114" s="34"/>
-      <c r="L114" s="34"/>
+      <c r="J114" s="35"/>
+      <c r="K114" s="35"/>
+      <c r="L114" s="35"/>
     </row>
     <row r="115" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A115" s="41">
+      <c r="A115" s="42">
         <v>5</v>
       </c>
-      <c r="B115" s="44" t="s">
+      <c r="B115" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="C115" s="41"/>
-      <c r="D115" s="41" t="s">
+      <c r="C115" s="42"/>
+      <c r="D115" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="E115" s="41">
+      <c r="E115" s="42">
         <v>150</v>
       </c>
-      <c r="F115" s="41">
+      <c r="F115" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G115" s="41">
+      <c r="G115" s="42">
         <v>100</v>
       </c>
-      <c r="H115" s="41">
+      <c r="H115" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I115" s="42" t="s">
+      <c r="I115" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="J115" s="34"/>
-      <c r="K115" s="34"/>
-      <c r="L115" s="34"/>
+      <c r="J115" s="35"/>
+      <c r="K115" s="35"/>
+      <c r="L115" s="35"/>
     </row>
     <row r="116" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A116" s="41">
+      <c r="A116" s="42">
         <v>6</v>
       </c>
-      <c r="B116" s="44" t="s">
+      <c r="B116" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="C116" s="41"/>
-      <c r="D116" s="41" t="s">
+      <c r="C116" s="42"/>
+      <c r="D116" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E116" s="41">
+      <c r="E116" s="42">
         <v>120</v>
       </c>
-      <c r="F116" s="41">
+      <c r="F116" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G116" s="41">
+      <c r="G116" s="42">
         <v>320</v>
       </c>
-      <c r="H116" s="41">
+      <c r="H116" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I116" s="42" t="s">
+      <c r="I116" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="J116" s="34"/>
-      <c r="K116" s="34"/>
-      <c r="L116" s="34"/>
+      <c r="J116" s="35"/>
+      <c r="K116" s="35"/>
+      <c r="L116" s="35"/>
     </row>
     <row r="117" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A117" s="41">
+      <c r="A117" s="42">
         <v>7</v>
       </c>
-      <c r="B117" s="44" t="s">
+      <c r="B117" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41" t="s">
+      <c r="C117" s="42"/>
+      <c r="D117" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E117" s="41">
+      <c r="E117" s="42">
         <v>10</v>
       </c>
-      <c r="F117" s="41">
+      <c r="F117" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G117" s="41">
+      <c r="G117" s="42">
         <v>15</v>
       </c>
-      <c r="H117" s="41">
+      <c r="H117" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I117" s="42" t="s">
+      <c r="I117" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="J117" s="34"/>
-      <c r="K117" s="34"/>
-      <c r="L117" s="34"/>
+      <c r="J117" s="35"/>
+      <c r="K117" s="35"/>
+      <c r="L117" s="35"/>
     </row>
     <row r="118" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A118" s="41">
+      <c r="A118" s="42">
         <v>8</v>
       </c>
-      <c r="B118" s="44" t="s">
+      <c r="B118" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="C118" s="41"/>
-      <c r="D118" s="41" t="s">
+      <c r="C118" s="42"/>
+      <c r="D118" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E118" s="41">
+      <c r="E118" s="42">
         <v>280</v>
       </c>
-      <c r="F118" s="41">
+      <c r="F118" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G118" s="41">
+      <c r="G118" s="42">
         <v>380</v>
       </c>
-      <c r="H118" s="41">
+      <c r="H118" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I118" s="42" t="s">
+      <c r="I118" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="J118" s="88"/>
-      <c r="K118" s="88"/>
-      <c r="L118" s="88"/>
+      <c r="J118" s="89"/>
+      <c r="K118" s="89"/>
+      <c r="L118" s="89"/>
     </row>
     <row r="119" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A119" s="41">
+      <c r="A119" s="42">
         <v>9</v>
       </c>
-      <c r="B119" s="44" t="s">
+      <c r="B119" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="41"/>
-      <c r="D119" s="41" t="s">
+      <c r="C119" s="42"/>
+      <c r="D119" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E119" s="41">
+      <c r="E119" s="42">
         <v>105</v>
       </c>
-      <c r="F119" s="41">
+      <c r="F119" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G119" s="41">
+      <c r="G119" s="42">
         <v>70</v>
       </c>
-      <c r="H119" s="41">
+      <c r="H119" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I119" s="42" t="s">
+      <c r="I119" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="J119" s="88"/>
-      <c r="K119" s="88"/>
-      <c r="L119" s="88"/>
+      <c r="J119" s="89"/>
+      <c r="K119" s="89"/>
+      <c r="L119" s="89"/>
     </row>
     <row r="120" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A120" s="41">
+      <c r="A120" s="42">
         <v>10</v>
       </c>
-      <c r="B120" s="44" t="s">
+      <c r="B120" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C120" s="50"/>
-      <c r="D120" s="50" t="s">
+      <c r="C120" s="51"/>
+      <c r="D120" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E120" s="41">
+      <c r="E120" s="42">
         <v>25</v>
       </c>
-      <c r="F120" s="41">
+      <c r="F120" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G120" s="82">
+      <c r="G120" s="83">
         <v>45</v>
       </c>
-      <c r="H120" s="41">
+      <c r="H120" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I120" s="42" t="s">
+      <c r="I120" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="J120" s="59"/>
-      <c r="K120" s="59"/>
-      <c r="L120" s="59"/>
+      <c r="J120" s="60"/>
+      <c r="K120" s="60"/>
+      <c r="L120" s="60"/>
     </row>
     <row r="121" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A121" s="41">
+      <c r="A121" s="42">
         <v>11</v>
       </c>
-      <c r="B121" s="44" t="s">
+      <c r="B121" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="C121" s="41"/>
-      <c r="D121" s="41" t="s">
+      <c r="C121" s="42"/>
+      <c r="D121" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E121" s="41">
+      <c r="E121" s="42">
         <v>45</v>
       </c>
-      <c r="F121" s="41">
+      <c r="F121" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G121" s="41">
+      <c r="G121" s="42">
         <v>90</v>
       </c>
-      <c r="H121" s="41">
+      <c r="H121" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I121" s="42" t="s">
+      <c r="I121" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="J121" s="34"/>
-      <c r="K121" s="34"/>
-      <c r="L121" s="34"/>
+      <c r="J121" s="35"/>
+      <c r="K121" s="35"/>
+      <c r="L121" s="35"/>
     </row>
     <row r="122" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A122" s="41">
+      <c r="A122" s="42">
         <v>12</v>
       </c>
-      <c r="B122" s="44" t="s">
+      <c r="B122" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="C122" s="41"/>
-      <c r="D122" s="50" t="s">
+      <c r="C122" s="42"/>
+      <c r="D122" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E122" s="41">
+      <c r="E122" s="42">
         <v>65</v>
       </c>
-      <c r="F122" s="41">
+      <c r="F122" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G122" s="41">
+      <c r="G122" s="42">
         <v>100</v>
       </c>
-      <c r="H122" s="41">
+      <c r="H122" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I122" s="42" t="s">
+      <c r="I122" s="43" t="s">
         <v>151</v>
       </c>
       <c r="J122"/>
@@ -6618,883 +6618,883 @@
       <c r="L122"/>
     </row>
     <row r="123" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A123" s="41">
+      <c r="A123" s="42">
         <v>13</v>
       </c>
-      <c r="B123" s="44" t="s">
+      <c r="B123" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="C123" s="41"/>
-      <c r="D123" s="50" t="s">
+      <c r="C123" s="42"/>
+      <c r="D123" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E123" s="41">
+      <c r="E123" s="42">
         <v>180</v>
       </c>
-      <c r="F123" s="41">
+      <c r="F123" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G123" s="41">
+      <c r="G123" s="42">
         <v>320</v>
       </c>
-      <c r="H123" s="41">
+      <c r="H123" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I123" s="42" t="s">
+      <c r="I123" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="J123" s="34"/>
-      <c r="K123" s="34"/>
-      <c r="L123" s="34"/>
+      <c r="J123" s="35"/>
+      <c r="K123" s="35"/>
+      <c r="L123" s="35"/>
     </row>
     <row r="124" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A124" s="41">
+      <c r="A124" s="42">
         <v>14</v>
       </c>
-      <c r="B124" s="44" t="s">
+      <c r="B124" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="C124" s="41"/>
-      <c r="D124" s="50" t="s">
+      <c r="C124" s="42"/>
+      <c r="D124" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="E124" s="41">
+      <c r="E124" s="42">
         <v>4</v>
       </c>
-      <c r="F124" s="41">
+      <c r="F124" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G124" s="41">
+      <c r="G124" s="42">
         <v>2.5</v>
       </c>
-      <c r="H124" s="41">
+      <c r="H124" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I124" s="42" t="s">
+      <c r="I124" s="43" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="125" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A125" s="41">
+      <c r="A125" s="42">
         <v>15</v>
       </c>
-      <c r="B125" s="44" t="s">
+      <c r="B125" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="C125" s="41"/>
-      <c r="D125" s="50" t="s">
+      <c r="C125" s="42"/>
+      <c r="D125" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="41">
+      <c r="E125" s="42">
         <v>25</v>
       </c>
-      <c r="F125" s="41">
+      <c r="F125" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G125" s="41">
+      <c r="G125" s="42">
         <v>48</v>
       </c>
-      <c r="H125" s="41">
+      <c r="H125" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I125" s="42" t="s">
+      <c r="I125" s="43" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="126" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A126" s="41">
+      <c r="A126" s="42">
         <v>16</v>
       </c>
-      <c r="B126" s="44" t="s">
+      <c r="B126" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C126" s="41"/>
-      <c r="D126" s="41" t="s">
+      <c r="C126" s="42"/>
+      <c r="D126" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E126" s="41">
+      <c r="E126" s="42">
         <v>160</v>
       </c>
-      <c r="F126" s="41">
+      <c r="F126" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G126" s="41">
+      <c r="G126" s="42">
         <v>125</v>
       </c>
-      <c r="H126" s="41">
+      <c r="H126" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I126" s="42" t="s">
+      <c r="I126" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="J126" s="34"/>
-      <c r="K126" s="34"/>
-      <c r="L126" s="34"/>
+      <c r="J126" s="35"/>
+      <c r="K126" s="35"/>
+      <c r="L126" s="35"/>
     </row>
     <row r="127" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A127" s="41">
+      <c r="A127" s="42">
         <v>17</v>
       </c>
-      <c r="B127" s="44" t="s">
+      <c r="B127" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="C127" s="41"/>
-      <c r="D127" s="41" t="s">
+      <c r="C127" s="42"/>
+      <c r="D127" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E127" s="41">
-        <v>0</v>
-      </c>
-      <c r="F127" s="41">
+      <c r="E127" s="42">
+        <v>0</v>
+      </c>
+      <c r="F127" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G127" s="41">
+      <c r="G127" s="42">
         <v>75</v>
       </c>
-      <c r="H127" s="41">
+      <c r="H127" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I127" s="42" t="s">
+      <c r="I127" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="J127" s="34"/>
-      <c r="K127" s="34"/>
-      <c r="L127" s="34"/>
+      <c r="J127" s="35"/>
+      <c r="K127" s="35"/>
+      <c r="L127" s="35"/>
     </row>
     <row r="128" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A128" s="41">
+      <c r="A128" s="42">
         <v>18</v>
       </c>
-      <c r="B128" s="44" t="s">
+      <c r="B128" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="C128" s="41"/>
-      <c r="D128" s="41" t="s">
+      <c r="C128" s="42"/>
+      <c r="D128" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E128" s="41"/>
-      <c r="F128" s="41">
+      <c r="E128" s="42"/>
+      <c r="F128" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G128" s="41">
+      <c r="G128" s="42">
         <v>5</v>
       </c>
-      <c r="H128" s="41">
+      <c r="H128" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I128" s="42" t="s">
+      <c r="I128" s="43" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="129" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A129" s="41">
+      <c r="A129" s="42">
         <v>19</v>
       </c>
-      <c r="B129" s="44" t="s">
+      <c r="B129" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="C129" s="41"/>
-      <c r="D129" s="41" t="s">
+      <c r="C129" s="42"/>
+      <c r="D129" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E129" s="41">
+      <c r="E129" s="42">
         <v>80</v>
       </c>
-      <c r="F129" s="41">
+      <c r="F129" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G129" s="41">
+      <c r="G129" s="42">
         <v>75</v>
       </c>
-      <c r="H129" s="41">
+      <c r="H129" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I129" s="42" t="s">
+      <c r="I129" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="J129" s="34"/>
-      <c r="K129" s="34"/>
-      <c r="L129" s="34"/>
+      <c r="J129" s="35"/>
+      <c r="K129" s="35"/>
+      <c r="L129" s="35"/>
     </row>
     <row r="130" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A130" s="41">
+      <c r="A130" s="42">
         <v>20</v>
       </c>
-      <c r="B130" s="44" t="s">
+      <c r="B130" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="C130" s="41"/>
-      <c r="D130" s="41" t="s">
+      <c r="C130" s="42"/>
+      <c r="D130" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E130" s="41">
+      <c r="E130" s="42">
         <v>15</v>
       </c>
-      <c r="F130" s="41">
+      <c r="F130" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G130" s="41">
+      <c r="G130" s="42">
         <v>13</v>
       </c>
-      <c r="H130" s="41">
+      <c r="H130" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I130" s="42" t="s">
+      <c r="I130" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="J130" s="34"/>
-      <c r="K130" s="34"/>
-      <c r="L130" s="34"/>
+      <c r="J130" s="35"/>
+      <c r="K130" s="35"/>
+      <c r="L130" s="35"/>
     </row>
     <row r="131" s="8" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A131" s="41">
+      <c r="A131" s="42">
         <v>21</v>
       </c>
-      <c r="B131" s="44" t="s">
+      <c r="B131" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="C131" s="41"/>
-      <c r="D131" s="41" t="s">
+      <c r="C131" s="42"/>
+      <c r="D131" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E131" s="41">
+      <c r="E131" s="42">
         <v>2</v>
       </c>
-      <c r="F131" s="41">
+      <c r="F131" s="42">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="G131" s="41">
+      <c r="G131" s="42">
         <v>6</v>
       </c>
-      <c r="H131" s="41">
+      <c r="H131" s="42">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="I131" s="42" t="s">
+      <c r="I131" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="J131" s="68"/>
-      <c r="K131" s="68"/>
-      <c r="L131" s="68"/>
+      <c r="J131" s="69"/>
+      <c r="K131" s="69"/>
+      <c r="L131" s="69"/>
     </row>
     <row r="132" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A132" s="61"/>
-      <c r="B132" s="62" t="s">
+      <c r="A132" s="62"/>
+      <c r="B132" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C132" s="61"/>
-      <c r="D132" s="61"/>
-      <c r="E132" s="61"/>
-      <c r="F132" s="61">
+      <c r="C132" s="62"/>
+      <c r="D132" s="62"/>
+      <c r="E132" s="62"/>
+      <c r="F132" s="62">
         <f>SUM(F111:F131)</f>
         <v>0</v>
       </c>
-      <c r="G132" s="61"/>
-      <c r="H132" s="61">
+      <c r="G132" s="62"/>
+      <c r="H132" s="62">
         <f>SUM(H111:H131)</f>
         <v>0</v>
       </c>
-      <c r="I132" s="63"/>
-      <c r="J132" s="64"/>
-      <c r="K132" s="64"/>
-      <c r="L132" s="64"/>
+      <c r="I132" s="64"/>
+      <c r="J132" s="65"/>
+      <c r="K132" s="65"/>
+      <c r="L132" s="65"/>
     </row>
     <row r="133" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A133" s="41"/>
-      <c r="B133" s="65" t="s">
+      <c r="A133" s="42"/>
+      <c r="B133" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="C133" s="41"/>
-      <c r="D133" s="41"/>
-      <c r="E133" s="41"/>
-      <c r="F133" s="89">
+      <c r="C133" s="42"/>
+      <c r="D133" s="42"/>
+      <c r="E133" s="42"/>
+      <c r="F133" s="90">
         <f>F132+F84+F75+F65+F54+F45+F34+F25</f>
         <v>0</v>
       </c>
-      <c r="G133" s="89"/>
-      <c r="H133" s="89">
+      <c r="G133" s="90"/>
+      <c r="H133" s="90">
         <f>H132+H84+H75+H65+H54+H45+H34+H25</f>
         <v>0</v>
       </c>
-      <c r="I133" s="42"/>
-      <c r="J133" s="34"/>
-      <c r="K133" s="34"/>
-      <c r="L133" s="34"/>
+      <c r="I133" s="43"/>
+      <c r="J133" s="35"/>
+      <c r="K133" s="35"/>
+      <c r="L133" s="35"/>
     </row>
     <row r="134" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A134" s="61"/>
-      <c r="B134" s="62" t="s">
+      <c r="A134" s="62"/>
+      <c r="B134" s="63" t="s">
         <v>172</v>
       </c>
-      <c r="C134" s="61"/>
-      <c r="D134" s="61"/>
-      <c r="E134" s="61"/>
-      <c r="F134" s="61"/>
-      <c r="G134" s="61"/>
-      <c r="H134" s="90">
+      <c r="C134" s="62"/>
+      <c r="D134" s="62"/>
+      <c r="E134" s="62"/>
+      <c r="F134" s="62"/>
+      <c r="G134" s="62"/>
+      <c r="H134" s="91">
         <f>F133+H133</f>
         <v>0</v>
       </c>
-      <c r="I134" s="91"/>
-      <c r="J134" s="64"/>
-      <c r="K134" s="64"/>
-      <c r="L134" s="64"/>
+      <c r="I134" s="92"/>
+      <c r="J134" s="65"/>
+      <c r="K134" s="65"/>
+      <c r="L134" s="65"/>
     </row>
     <row r="135" s="15" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A135" s="92"/>
-      <c r="B135" s="93" t="s">
+      <c r="A135" s="93"/>
+      <c r="B135" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="C135" s="94"/>
-      <c r="D135" s="94"/>
-      <c r="E135" s="94"/>
-      <c r="F135" s="94"/>
-      <c r="G135" s="94"/>
-      <c r="H135" s="94"/>
-      <c r="I135" s="95"/>
-      <c r="J135" s="96"/>
-      <c r="K135" s="96"/>
-      <c r="L135" s="96"/>
+      <c r="C135" s="95"/>
+      <c r="D135" s="95"/>
+      <c r="E135" s="95"/>
+      <c r="F135" s="95"/>
+      <c r="G135" s="95"/>
+      <c r="H135" s="95"/>
+      <c r="I135" s="96"/>
+      <c r="J135" s="97"/>
+      <c r="K135" s="97"/>
+      <c r="L135" s="97"/>
     </row>
     <row r="136" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A136" s="41"/>
-      <c r="B136" s="97" t="s">
+      <c r="A136" s="42"/>
+      <c r="B136" s="98" t="s">
         <v>174</v>
       </c>
-      <c r="C136" s="41"/>
-      <c r="D136" s="41"/>
-      <c r="E136" s="41"/>
-      <c r="F136" s="41"/>
-      <c r="G136" s="98"/>
-      <c r="H136" s="89">
+      <c r="C136" s="42"/>
+      <c r="D136" s="42"/>
+      <c r="E136" s="42"/>
+      <c r="F136" s="42"/>
+      <c r="G136" s="99"/>
+      <c r="H136" s="90">
         <f>H134*3.5%</f>
         <v>0</v>
       </c>
-      <c r="I136" s="42" t="s">
+      <c r="I136" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="J136" s="34"/>
-      <c r="K136" s="34"/>
-      <c r="L136" s="34"/>
+      <c r="J136" s="35"/>
+      <c r="K136" s="35"/>
+      <c r="L136" s="35"/>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:12">
-      <c r="A137" s="41"/>
-      <c r="B137" s="65" t="s">
+      <c r="A137" s="42"/>
+      <c r="B137" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="C137" s="41"/>
-      <c r="D137" s="41"/>
-      <c r="E137" s="41"/>
-      <c r="F137" s="41"/>
-      <c r="G137" s="98"/>
-      <c r="H137" s="89">
+      <c r="C137" s="42"/>
+      <c r="D137" s="42"/>
+      <c r="E137" s="42"/>
+      <c r="F137" s="42"/>
+      <c r="G137" s="99"/>
+      <c r="H137" s="90">
         <f>H134*3%</f>
         <v>0</v>
       </c>
-      <c r="I137" s="42" t="s">
+      <c r="I137" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="J137" s="34"/>
-      <c r="K137" s="34"/>
-      <c r="L137" s="34"/>
+      <c r="J137" s="35"/>
+      <c r="K137" s="35"/>
+      <c r="L137" s="35"/>
     </row>
     <row r="138" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A138" s="41"/>
-      <c r="B138" s="65" t="s">
+      <c r="A138" s="42"/>
+      <c r="B138" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="41"/>
-      <c r="D138" s="41"/>
-      <c r="E138" s="41"/>
-      <c r="F138" s="99"/>
-      <c r="G138" s="41"/>
-      <c r="H138" s="89">
+      <c r="C138" s="42"/>
+      <c r="D138" s="42"/>
+      <c r="E138" s="42"/>
+      <c r="F138" s="100"/>
+      <c r="G138" s="42"/>
+      <c r="H138" s="90">
         <f>H134*8%</f>
         <v>0</v>
       </c>
-      <c r="I138" s="42" t="s">
+      <c r="I138" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="J138" s="100"/>
-      <c r="K138" s="101"/>
-      <c r="L138" s="101"/>
+      <c r="J138" s="101"/>
+      <c r="K138" s="102"/>
+      <c r="L138" s="102"/>
     </row>
     <row r="139" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A139" s="41"/>
-      <c r="B139" s="65" t="s">
+      <c r="A139" s="42"/>
+      <c r="B139" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="C139" s="41"/>
-      <c r="D139" s="41"/>
-      <c r="E139" s="41"/>
-      <c r="F139" s="99"/>
-      <c r="G139" s="41"/>
-      <c r="H139" s="89">
+      <c r="C139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="100"/>
+      <c r="G139" s="42"/>
+      <c r="H139" s="90">
         <f>H134*5%</f>
         <v>0</v>
       </c>
-      <c r="I139" s="42" t="s">
+      <c r="I139" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="J139" s="100"/>
-      <c r="K139" s="101"/>
-      <c r="L139" s="101"/>
+      <c r="J139" s="101"/>
+      <c r="K139" s="102"/>
+      <c r="L139" s="102"/>
     </row>
     <row r="140" s="16" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A140" s="92"/>
-      <c r="B140" s="102" t="s">
+      <c r="A140" s="93"/>
+      <c r="B140" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="C140" s="92"/>
-      <c r="D140" s="92"/>
-      <c r="E140" s="92"/>
-      <c r="F140" s="103"/>
-      <c r="G140" s="92"/>
-      <c r="H140" s="104">
+      <c r="C140" s="93"/>
+      <c r="D140" s="93"/>
+      <c r="E140" s="93"/>
+      <c r="F140" s="104"/>
+      <c r="G140" s="93"/>
+      <c r="H140" s="105">
         <f>H139+H138+H137+H136+H134</f>
         <v>0</v>
       </c>
-      <c r="I140" s="105"/>
-      <c r="J140" s="106"/>
-      <c r="K140" s="107"/>
-      <c r="L140" s="107"/>
+      <c r="I140" s="106"/>
+      <c r="J140" s="107"/>
+      <c r="K140" s="108"/>
+      <c r="L140" s="108"/>
     </row>
     <row r="141" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A141" s="41"/>
-      <c r="B141" s="108" t="s">
+      <c r="A141" s="42"/>
+      <c r="B141" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="C141" s="109"/>
-      <c r="D141" s="109"/>
-      <c r="E141" s="109"/>
-      <c r="F141" s="109"/>
-      <c r="G141" s="109"/>
-      <c r="H141" s="110"/>
-      <c r="I141" s="111" t="s">
+      <c r="C141" s="110"/>
+      <c r="D141" s="110"/>
+      <c r="E141" s="110"/>
+      <c r="F141" s="110"/>
+      <c r="G141" s="110"/>
+      <c r="H141" s="111"/>
+      <c r="I141" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="J141" s="100"/>
-      <c r="K141" s="101"/>
-      <c r="L141" s="101"/>
+      <c r="J141" s="101"/>
+      <c r="K141" s="102"/>
+      <c r="L141" s="102"/>
     </row>
     <row r="142" s="16" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A142" s="92" t="s">
+      <c r="A142" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="B142" s="102" t="s">
+      <c r="B142" s="103" t="s">
         <v>185</v>
       </c>
-      <c r="C142" s="92"/>
-      <c r="D142" s="92"/>
-      <c r="E142" s="92"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="92"/>
-      <c r="H142" s="103"/>
-      <c r="J142" s="106"/>
-      <c r="K142" s="107"/>
-      <c r="L142" s="107"/>
+      <c r="C142" s="93"/>
+      <c r="D142" s="93"/>
+      <c r="E142" s="93"/>
+      <c r="F142" s="104"/>
+      <c r="G142" s="93"/>
+      <c r="H142" s="104"/>
+      <c r="J142" s="107"/>
+      <c r="K142" s="108"/>
+      <c r="L142" s="108"/>
     </row>
     <row r="143" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A143" s="41">
+      <c r="A143" s="42">
         <v>1</v>
       </c>
-      <c r="B143" s="44" t="s">
+      <c r="B143" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="C143" s="41"/>
-      <c r="D143" s="41" t="s">
+      <c r="C143" s="42"/>
+      <c r="D143" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="E143" s="45">
+      <c r="E143" s="46">
         <v>95</v>
       </c>
-      <c r="F143" s="41"/>
-      <c r="G143" s="45">
+      <c r="F143" s="42"/>
+      <c r="G143" s="46">
         <v>45</v>
       </c>
-      <c r="H143" s="45"/>
-      <c r="I143" s="42" t="s">
+      <c r="H143" s="46"/>
+      <c r="I143" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="J143" s="100"/>
-      <c r="K143" s="101"/>
-      <c r="L143" s="101"/>
+      <c r="J143" s="101"/>
+      <c r="K143" s="102"/>
+      <c r="L143" s="102"/>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:12">
-      <c r="A144" s="41">
+      <c r="A144" s="42">
         <v>2</v>
       </c>
-      <c r="B144" s="44" t="s">
+      <c r="B144" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="C144" s="41"/>
-      <c r="D144" s="41" t="s">
+      <c r="C144" s="42"/>
+      <c r="D144" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E144" s="45">
+      <c r="E144" s="46">
         <v>2</v>
       </c>
-      <c r="F144" s="41"/>
-      <c r="G144" s="45">
+      <c r="F144" s="42"/>
+      <c r="G144" s="46">
         <v>6</v>
       </c>
-      <c r="H144" s="41"/>
-      <c r="I144" s="42" t="s">
+      <c r="H144" s="42"/>
+      <c r="I144" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="J144" s="34"/>
-      <c r="K144" s="34"/>
-      <c r="L144" s="34"/>
+      <c r="J144" s="35"/>
+      <c r="K144" s="35"/>
+      <c r="L144" s="35"/>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:12">
-      <c r="A145" s="41">
+      <c r="A145" s="42">
         <v>3</v>
       </c>
-      <c r="B145" s="44" t="s">
+      <c r="B145" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="C145" s="41"/>
-      <c r="D145" s="41" t="s">
+      <c r="C145" s="42"/>
+      <c r="D145" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E145" s="45">
+      <c r="E145" s="46">
         <v>20</v>
       </c>
-      <c r="F145" s="41"/>
-      <c r="G145" s="45">
+      <c r="F145" s="42"/>
+      <c r="G145" s="46">
         <v>45</v>
       </c>
-      <c r="H145" s="41"/>
-      <c r="I145" s="112" t="s">
+      <c r="H145" s="42"/>
+      <c r="I145" s="113" t="s">
         <v>192</v>
       </c>
-      <c r="J145" s="34"/>
-      <c r="K145" s="34"/>
-      <c r="L145" s="34"/>
+      <c r="J145" s="35"/>
+      <c r="K145" s="35"/>
+      <c r="L145" s="35"/>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:12">
-      <c r="A146" s="41">
+      <c r="A146" s="42">
         <v>4</v>
       </c>
-      <c r="B146" s="44" t="s">
+      <c r="B146" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="C146" s="41"/>
-      <c r="D146" s="41" t="s">
+      <c r="C146" s="42"/>
+      <c r="D146" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E146" s="45">
+      <c r="E146" s="46">
         <v>20</v>
       </c>
-      <c r="F146" s="41"/>
-      <c r="G146" s="45">
+      <c r="F146" s="42"/>
+      <c r="G146" s="46">
         <v>60</v>
       </c>
-      <c r="H146" s="41"/>
-      <c r="I146" s="112" t="s">
+      <c r="H146" s="42"/>
+      <c r="I146" s="113" t="s">
         <v>194</v>
       </c>
-      <c r="J146" s="34"/>
-      <c r="K146" s="34"/>
-      <c r="L146" s="34"/>
+      <c r="J146" s="35"/>
+      <c r="K146" s="35"/>
+      <c r="L146" s="35"/>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:12">
-      <c r="A147" s="41">
+      <c r="A147" s="42">
         <v>5</v>
       </c>
-      <c r="B147" s="44" t="s">
+      <c r="B147" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="C147" s="41"/>
-      <c r="D147" s="41" t="s">
+      <c r="C147" s="42"/>
+      <c r="D147" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E147" s="45">
+      <c r="E147" s="46">
         <v>20</v>
       </c>
-      <c r="F147" s="41"/>
-      <c r="G147" s="45">
+      <c r="F147" s="42"/>
+      <c r="G147" s="46">
         <v>85</v>
       </c>
-      <c r="H147" s="41"/>
-      <c r="I147" s="112" t="s">
+      <c r="H147" s="42"/>
+      <c r="I147" s="113" t="s">
         <v>196</v>
       </c>
-      <c r="J147" s="34"/>
-      <c r="K147" s="34"/>
-      <c r="L147" s="34"/>
+      <c r="J147" s="35"/>
+      <c r="K147" s="35"/>
+      <c r="L147" s="35"/>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:12">
-      <c r="A148" s="41">
+      <c r="A148" s="42">
         <v>6</v>
       </c>
-      <c r="B148" s="44" t="s">
+      <c r="B148" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="C148" s="41"/>
-      <c r="D148" s="41" t="s">
+      <c r="C148" s="42"/>
+      <c r="D148" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E148" s="45">
+      <c r="E148" s="46">
         <v>45</v>
       </c>
-      <c r="F148" s="41"/>
-      <c r="G148" s="45">
+      <c r="F148" s="42"/>
+      <c r="G148" s="46">
         <v>90</v>
       </c>
-      <c r="H148" s="41"/>
-      <c r="I148" s="112" t="s">
+      <c r="H148" s="42"/>
+      <c r="I148" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="J148" s="34"/>
-      <c r="K148" s="34"/>
-      <c r="L148" s="34"/>
+      <c r="J148" s="35"/>
+      <c r="K148" s="35"/>
+      <c r="L148" s="35"/>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:12">
-      <c r="A149" s="41">
+      <c r="A149" s="42">
         <v>7</v>
       </c>
-      <c r="B149" s="44" t="s">
+      <c r="B149" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="C149" s="41"/>
-      <c r="D149" s="41" t="s">
+      <c r="C149" s="42"/>
+      <c r="D149" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E149" s="45">
+      <c r="E149" s="46">
         <v>180</v>
       </c>
-      <c r="F149" s="41"/>
-      <c r="G149" s="45">
+      <c r="F149" s="42"/>
+      <c r="G149" s="46">
         <v>120</v>
       </c>
-      <c r="H149" s="45"/>
-      <c r="I149" s="46" t="s">
+      <c r="H149" s="46"/>
+      <c r="I149" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="J149" s="34"/>
-      <c r="K149" s="34"/>
-      <c r="L149" s="34"/>
+      <c r="J149" s="35"/>
+      <c r="K149" s="35"/>
+      <c r="L149" s="35"/>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:12">
-      <c r="A150" s="41">
+      <c r="A150" s="42">
         <v>8</v>
       </c>
-      <c r="B150" s="44" t="s">
+      <c r="B150" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C150" s="41"/>
-      <c r="D150" s="41" t="s">
+      <c r="C150" s="42"/>
+      <c r="D150" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="45">
+      <c r="E150" s="46">
         <v>70</v>
       </c>
-      <c r="F150" s="41"/>
-      <c r="G150" s="45">
+      <c r="F150" s="42"/>
+      <c r="G150" s="46">
         <v>25</v>
       </c>
-      <c r="H150" s="45"/>
-      <c r="I150" s="46" t="s">
+      <c r="H150" s="46"/>
+      <c r="I150" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="J150" s="34"/>
-      <c r="K150" s="34"/>
-      <c r="L150" s="34"/>
+      <c r="J150" s="35"/>
+      <c r="K150" s="35"/>
+      <c r="L150" s="35"/>
     </row>
     <row r="151" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A151" s="41">
+      <c r="A151" s="42">
         <v>9</v>
       </c>
-      <c r="B151" s="67" t="s">
+      <c r="B151" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="C151" s="41"/>
-      <c r="D151" s="41" t="s">
+      <c r="C151" s="42"/>
+      <c r="D151" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E151" s="83">
-        <v>0</v>
-      </c>
-      <c r="F151" s="41"/>
-      <c r="G151" s="41">
+      <c r="E151" s="84">
+        <v>0</v>
+      </c>
+      <c r="F151" s="42"/>
+      <c r="G151" s="42">
         <v>50</v>
       </c>
-      <c r="H151" s="41"/>
-      <c r="I151" s="113" t="s">
+      <c r="H151" s="42"/>
+      <c r="I151" s="114" t="s">
         <v>200</v>
       </c>
-      <c r="J151" s="88"/>
-      <c r="K151" s="88"/>
-      <c r="L151" s="88"/>
+      <c r="J151" s="89"/>
+      <c r="K151" s="89"/>
+      <c r="L151" s="89"/>
     </row>
     <row r="152" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A152" s="41">
+      <c r="A152" s="42">
         <v>10</v>
       </c>
-      <c r="B152" s="67" t="s">
+      <c r="B152" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="C152" s="41"/>
-      <c r="D152" s="41" t="s">
+      <c r="C152" s="42"/>
+      <c r="D152" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E152" s="83">
+      <c r="E152" s="84">
         <v>50</v>
       </c>
-      <c r="F152" s="41"/>
-      <c r="G152" s="41">
+      <c r="F152" s="42"/>
+      <c r="G152" s="42">
         <v>100</v>
       </c>
-      <c r="H152" s="41"/>
-      <c r="I152" s="113" t="s">
+      <c r="H152" s="42"/>
+      <c r="I152" s="114" t="s">
         <v>202</v>
       </c>
-      <c r="J152" s="88"/>
-      <c r="K152" s="88"/>
-      <c r="L152" s="88"/>
+      <c r="J152" s="89"/>
+      <c r="K152" s="89"/>
+      <c r="L152" s="89"/>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:12">
-      <c r="A153" s="41">
+      <c r="A153" s="42">
         <v>11</v>
       </c>
-      <c r="B153" s="114" t="s">
+      <c r="B153" s="115" t="s">
         <v>203</v>
       </c>
-      <c r="C153" s="41"/>
-      <c r="D153" s="41" t="s">
+      <c r="C153" s="42"/>
+      <c r="D153" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E153" s="45">
+      <c r="E153" s="46">
         <v>120</v>
       </c>
-      <c r="F153" s="41"/>
-      <c r="G153" s="45">
+      <c r="F153" s="42"/>
+      <c r="G153" s="46">
         <v>160</v>
       </c>
-      <c r="H153" s="45"/>
-      <c r="I153" s="46" t="s">
+      <c r="H153" s="46"/>
+      <c r="I153" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="J153" s="34"/>
-      <c r="K153" s="34"/>
-      <c r="L153" s="34"/>
+      <c r="J153" s="35"/>
+      <c r="K153" s="35"/>
+      <c r="L153" s="35"/>
     </row>
     <row r="154" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A154" s="41">
+      <c r="A154" s="42">
         <v>12</v>
       </c>
-      <c r="B154" s="115" t="s">
+      <c r="B154" s="116" t="s">
         <v>146</v>
       </c>
-      <c r="C154" s="50"/>
-      <c r="D154" s="50" t="s">
+      <c r="C154" s="51"/>
+      <c r="D154" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E154" s="82">
+      <c r="E154" s="83">
         <v>25</v>
       </c>
-      <c r="F154" s="50"/>
-      <c r="G154" s="82">
+      <c r="F154" s="51"/>
+      <c r="G154" s="83">
         <v>45</v>
       </c>
-      <c r="H154" s="82"/>
-      <c r="I154" s="58" t="s">
+      <c r="H154" s="83"/>
+      <c r="I154" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="J154" s="59"/>
-      <c r="K154" s="59"/>
-      <c r="L154" s="59"/>
+      <c r="J154" s="60"/>
+      <c r="K154" s="60"/>
+      <c r="L154" s="60"/>
     </row>
     <row r="155" s="17" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A155" s="41">
+      <c r="A155" s="42">
         <v>13</v>
       </c>
-      <c r="B155" s="58" t="s">
+      <c r="B155" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C155" s="50"/>
-      <c r="D155" s="50" t="s">
+      <c r="C155" s="51"/>
+      <c r="D155" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E155" s="82">
+      <c r="E155" s="83">
         <v>23</v>
       </c>
-      <c r="F155" s="50"/>
-      <c r="G155" s="82">
+      <c r="F155" s="51"/>
+      <c r="G155" s="83">
         <v>16</v>
       </c>
-      <c r="H155" s="50"/>
-      <c r="I155" s="51" t="s">
+      <c r="H155" s="51"/>
+      <c r="I155" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="J155" s="116"/>
-      <c r="K155" s="116"/>
-      <c r="L155" s="116"/>
+      <c r="J155" s="117"/>
+      <c r="K155" s="117"/>
+      <c r="L155" s="117"/>
     </row>
     <row r="156" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A156" s="41">
+      <c r="A156" s="42">
         <v>14</v>
       </c>
-      <c r="B156" s="46" t="s">
+      <c r="B156" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="C156" s="41"/>
-      <c r="D156" s="41" t="s">
+      <c r="C156" s="42"/>
+      <c r="D156" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E156" s="45">
+      <c r="E156" s="46">
         <v>120</v>
       </c>
-      <c r="F156" s="41"/>
-      <c r="G156" s="45">
+      <c r="F156" s="42"/>
+      <c r="G156" s="46">
         <v>180</v>
       </c>
-      <c r="H156" s="41"/>
-      <c r="I156" s="42" t="s">
+      <c r="H156" s="42"/>
+      <c r="I156" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="J156" s="68"/>
-      <c r="K156" s="68"/>
-      <c r="L156" s="68"/>
+      <c r="J156" s="69"/>
+      <c r="K156" s="69"/>
+      <c r="L156" s="69"/>
     </row>
     <row r="157" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A157" s="41">
+      <c r="A157" s="42">
         <v>15</v>
       </c>
-      <c r="B157" s="117" t="s">
+      <c r="B157" s="118" t="s">
         <v>150</v>
       </c>
-      <c r="C157" s="118"/>
-      <c r="D157" s="118" t="s">
+      <c r="C157" s="119"/>
+      <c r="D157" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="E157" s="119">
+      <c r="E157" s="120">
         <v>65</v>
       </c>
-      <c r="F157" s="41"/>
-      <c r="G157" s="119">
+      <c r="F157" s="42"/>
+      <c r="G157" s="120">
         <v>100</v>
       </c>
-      <c r="H157" s="41"/>
-      <c r="I157" s="120" t="s">
+      <c r="H157" s="42"/>
+      <c r="I157" s="121" t="s">
         <v>151</v>
       </c>
       <c r="J157"/>
@@ -7502,399 +7502,399 @@
       <c r="L157"/>
     </row>
     <row r="158" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A158" s="41">
+      <c r="A158" s="42">
         <v>16</v>
       </c>
-      <c r="B158" s="121" t="s">
+      <c r="B158" s="122" t="s">
         <v>163</v>
       </c>
-      <c r="C158" s="41"/>
-      <c r="D158" s="41" t="s">
+      <c r="C158" s="42"/>
+      <c r="D158" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E158" s="122"/>
-      <c r="F158" s="41"/>
-      <c r="G158" s="122">
+      <c r="E158" s="123"/>
+      <c r="F158" s="42"/>
+      <c r="G158" s="123">
         <v>5</v>
       </c>
-      <c r="H158" s="41"/>
-      <c r="I158" s="123" t="s">
+      <c r="H158" s="42"/>
+      <c r="I158" s="124" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:12">
-      <c r="A159" s="41">
+      <c r="A159" s="42">
         <v>17</v>
       </c>
-      <c r="B159" s="44" t="s">
+      <c r="B159" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="C159" s="41"/>
-      <c r="D159" s="41" t="s">
+      <c r="C159" s="42"/>
+      <c r="D159" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E159" s="45">
+      <c r="E159" s="46">
         <v>180</v>
       </c>
-      <c r="F159" s="41"/>
-      <c r="G159" s="45">
+      <c r="F159" s="42"/>
+      <c r="G159" s="46">
         <v>320</v>
       </c>
-      <c r="H159" s="41"/>
-      <c r="I159" s="42" t="s">
+      <c r="H159" s="42"/>
+      <c r="I159" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="J159" s="34"/>
-      <c r="K159" s="34"/>
-      <c r="L159" s="34"/>
+      <c r="J159" s="35"/>
+      <c r="K159" s="35"/>
+      <c r="L159" s="35"/>
     </row>
     <row r="160" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A160" s="41">
+      <c r="A160" s="42">
         <v>18</v>
       </c>
-      <c r="B160" s="44" t="s">
+      <c r="B160" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="C160" s="41"/>
-      <c r="D160" s="41" t="s">
+      <c r="C160" s="42"/>
+      <c r="D160" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E160" s="45">
+      <c r="E160" s="46">
         <v>200</v>
       </c>
-      <c r="F160" s="41"/>
-      <c r="G160" s="45">
+      <c r="F160" s="42"/>
+      <c r="G160" s="46">
         <v>150</v>
       </c>
-      <c r="H160" s="41"/>
-      <c r="I160" s="42" t="s">
+      <c r="H160" s="42"/>
+      <c r="I160" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="J160" s="34"/>
-      <c r="K160" s="34"/>
-      <c r="L160" s="34"/>
+      <c r="J160" s="35"/>
+      <c r="K160" s="35"/>
+      <c r="L160" s="35"/>
     </row>
     <row r="161" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A161" s="41">
+      <c r="A161" s="42">
         <v>19</v>
       </c>
-      <c r="B161" s="44" t="s">
+      <c r="B161" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="C161" s="41"/>
-      <c r="D161" s="41" t="s">
+      <c r="C161" s="42"/>
+      <c r="D161" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E161" s="45">
+      <c r="E161" s="46">
         <v>130</v>
       </c>
-      <c r="F161" s="41"/>
-      <c r="G161" s="45">
+      <c r="F161" s="42"/>
+      <c r="G161" s="46">
         <v>70</v>
       </c>
-      <c r="H161" s="41"/>
-      <c r="I161" s="42" t="s">
+      <c r="H161" s="42"/>
+      <c r="I161" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="J161" s="34"/>
-      <c r="K161" s="34"/>
-      <c r="L161" s="34"/>
+      <c r="J161" s="35"/>
+      <c r="K161" s="35"/>
+      <c r="L161" s="35"/>
     </row>
     <row r="162" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A162" s="41">
+      <c r="A162" s="42">
         <v>20</v>
       </c>
-      <c r="B162" s="124" t="s">
+      <c r="B162" s="125" t="s">
         <v>154</v>
       </c>
-      <c r="C162" s="41"/>
-      <c r="D162" s="118" t="s">
+      <c r="C162" s="42"/>
+      <c r="D162" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="E162" s="119">
+      <c r="E162" s="120">
         <v>4</v>
       </c>
-      <c r="F162" s="118"/>
-      <c r="G162" s="119">
+      <c r="F162" s="119"/>
+      <c r="G162" s="120">
         <v>2.5</v>
       </c>
-      <c r="H162" s="41"/>
-      <c r="I162" s="120" t="s">
+      <c r="H162" s="42"/>
+      <c r="I162" s="121" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="163" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A163" s="41">
+      <c r="A163" s="42">
         <v>21</v>
       </c>
-      <c r="B163" s="117" t="s">
+      <c r="B163" s="118" t="s">
         <v>157</v>
       </c>
-      <c r="C163" s="41"/>
-      <c r="D163" s="118" t="s">
+      <c r="C163" s="42"/>
+      <c r="D163" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="E163" s="119">
+      <c r="E163" s="120">
         <v>25</v>
       </c>
-      <c r="F163" s="41"/>
-      <c r="G163" s="119">
+      <c r="F163" s="42"/>
+      <c r="G163" s="120">
         <v>48</v>
       </c>
-      <c r="H163" s="41"/>
-      <c r="I163" s="120" t="s">
+      <c r="H163" s="42"/>
+      <c r="I163" s="121" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:12">
-      <c r="A164" s="41">
+      <c r="A164" s="42">
         <v>22</v>
       </c>
-      <c r="B164" s="114" t="s">
+      <c r="B164" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="C164" s="41"/>
-      <c r="D164" s="41" t="s">
+      <c r="C164" s="42"/>
+      <c r="D164" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E164" s="45">
+      <c r="E164" s="46">
         <v>160</v>
       </c>
-      <c r="F164" s="41"/>
-      <c r="G164" s="45">
+      <c r="F164" s="42"/>
+      <c r="G164" s="46">
         <v>125</v>
       </c>
-      <c r="H164" s="41"/>
-      <c r="I164" s="42" t="s">
+      <c r="H164" s="42"/>
+      <c r="I164" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="J164" s="34"/>
-      <c r="K164" s="34"/>
-      <c r="L164" s="34"/>
+      <c r="J164" s="35"/>
+      <c r="K164" s="35"/>
+      <c r="L164" s="35"/>
     </row>
     <row r="165" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A165" s="41">
+      <c r="A165" s="42">
         <v>23</v>
       </c>
-      <c r="B165" s="117" t="s">
+      <c r="B165" s="118" t="s">
         <v>212</v>
       </c>
-      <c r="C165" s="118"/>
-      <c r="D165" s="118" t="s">
+      <c r="C165" s="119"/>
+      <c r="D165" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="119"/>
-      <c r="F165" s="41">
+      <c r="E165" s="120"/>
+      <c r="F165" s="42">
         <f>C165*E165</f>
         <v>0</v>
       </c>
-      <c r="G165" s="119">
+      <c r="G165" s="120">
         <v>85</v>
       </c>
-      <c r="H165" s="41">
+      <c r="H165" s="42">
         <f>SUM(G165*C165)</f>
         <v>0</v>
       </c>
-      <c r="I165" s="42" t="s">
+      <c r="I165" s="43" t="s">
         <v>213</v>
       </c>
       <c r="J165"/>
     </row>
     <row r="166" s="5" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A166" s="41" t="s">
+      <c r="A166" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B166" s="65" t="s">
+      <c r="B166" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="C166" s="125"/>
-      <c r="D166" s="125"/>
-      <c r="E166" s="125"/>
-      <c r="F166" s="125"/>
-      <c r="G166" s="125"/>
-      <c r="H166" s="125"/>
-      <c r="I166" s="125"/>
-      <c r="J166" s="100"/>
-      <c r="K166" s="101"/>
-      <c r="L166" s="101"/>
+      <c r="C166" s="126"/>
+      <c r="D166" s="126"/>
+      <c r="E166" s="126"/>
+      <c r="F166" s="126"/>
+      <c r="G166" s="126"/>
+      <c r="H166" s="126"/>
+      <c r="I166" s="126"/>
+      <c r="J166" s="101"/>
+      <c r="K166" s="102"/>
+      <c r="L166" s="102"/>
     </row>
     <row r="167" s="5" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A167" s="41">
+      <c r="A167" s="42">
         <v>1</v>
       </c>
-      <c r="B167" s="126" t="s">
+      <c r="B167" s="127" t="s">
         <v>215</v>
       </c>
-      <c r="C167" s="126"/>
-      <c r="D167" s="126"/>
-      <c r="E167" s="126"/>
-      <c r="F167" s="126"/>
-      <c r="G167" s="126"/>
-      <c r="H167" s="126"/>
-      <c r="I167" s="126"/>
-      <c r="J167" s="100"/>
-      <c r="K167" s="101"/>
-      <c r="L167" s="101"/>
+      <c r="C167" s="127"/>
+      <c r="D167" s="127"/>
+      <c r="E167" s="127"/>
+      <c r="F167" s="127"/>
+      <c r="G167" s="127"/>
+      <c r="H167" s="127"/>
+      <c r="I167" s="127"/>
+      <c r="J167" s="101"/>
+      <c r="K167" s="102"/>
+      <c r="L167" s="102"/>
     </row>
     <row r="168" s="5" customFormat="1" ht="29" customHeight="1" spans="1:12">
-      <c r="A168" s="41">
+      <c r="A168" s="42">
         <v>2</v>
       </c>
-      <c r="B168" s="44" t="s">
+      <c r="B168" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="C168" s="44"/>
-      <c r="D168" s="44"/>
-      <c r="E168" s="44"/>
-      <c r="F168" s="44"/>
-      <c r="G168" s="44"/>
-      <c r="H168" s="44"/>
-      <c r="I168" s="44"/>
-      <c r="J168" s="100"/>
-      <c r="K168" s="101"/>
-      <c r="L168" s="101"/>
+      <c r="C168" s="45"/>
+      <c r="D168" s="45"/>
+      <c r="E168" s="45"/>
+      <c r="F168" s="45"/>
+      <c r="G168" s="45"/>
+      <c r="H168" s="45"/>
+      <c r="I168" s="45"/>
+      <c r="J168" s="101"/>
+      <c r="K168" s="102"/>
+      <c r="L168" s="102"/>
     </row>
     <row r="169" s="5" customFormat="1" ht="29.25" customHeight="1" spans="1:12">
-      <c r="A169" s="41">
+      <c r="A169" s="42">
         <v>3</v>
       </c>
-      <c r="B169" s="126" t="s">
+      <c r="B169" s="127" t="s">
         <v>217</v>
       </c>
-      <c r="C169" s="126"/>
-      <c r="D169" s="126"/>
-      <c r="E169" s="126"/>
-      <c r="F169" s="126"/>
-      <c r="G169" s="126"/>
-      <c r="H169" s="126"/>
-      <c r="I169" s="126"/>
-      <c r="J169" s="100"/>
-      <c r="K169" s="101"/>
-      <c r="L169" s="101"/>
+      <c r="C169" s="127"/>
+      <c r="D169" s="127"/>
+      <c r="E169" s="127"/>
+      <c r="F169" s="127"/>
+      <c r="G169" s="127"/>
+      <c r="H169" s="127"/>
+      <c r="I169" s="127"/>
+      <c r="J169" s="101"/>
+      <c r="K169" s="102"/>
+      <c r="L169" s="102"/>
     </row>
     <row r="170" s="5" customFormat="1" ht="27.75" customHeight="1" spans="1:12">
-      <c r="A170" s="41">
+      <c r="A170" s="42">
         <v>4</v>
       </c>
-      <c r="B170" s="126" t="s">
+      <c r="B170" s="127" t="s">
         <v>218</v>
       </c>
-      <c r="C170" s="126"/>
-      <c r="D170" s="126"/>
-      <c r="E170" s="126"/>
-      <c r="F170" s="126"/>
-      <c r="G170" s="126"/>
-      <c r="H170" s="126"/>
-      <c r="I170" s="126"/>
-      <c r="J170" s="100"/>
-      <c r="K170" s="101"/>
-      <c r="L170" s="101"/>
+      <c r="C170" s="127"/>
+      <c r="D170" s="127"/>
+      <c r="E170" s="127"/>
+      <c r="F170" s="127"/>
+      <c r="G170" s="127"/>
+      <c r="H170" s="127"/>
+      <c r="I170" s="127"/>
+      <c r="J170" s="101"/>
+      <c r="K170" s="102"/>
+      <c r="L170" s="102"/>
     </row>
     <row r="171" s="5" customFormat="1" ht="58" customHeight="1" spans="1:12">
-      <c r="A171" s="41">
+      <c r="A171" s="42">
         <v>5</v>
       </c>
-      <c r="B171" s="126" t="s">
+      <c r="B171" s="127" t="s">
         <v>219</v>
       </c>
-      <c r="C171" s="126"/>
-      <c r="D171" s="126"/>
-      <c r="E171" s="126"/>
-      <c r="F171" s="126"/>
-      <c r="G171" s="126"/>
-      <c r="H171" s="126"/>
-      <c r="I171" s="126"/>
-      <c r="J171" s="100"/>
-      <c r="K171" s="101"/>
-      <c r="L171" s="101"/>
+      <c r="C171" s="127"/>
+      <c r="D171" s="127"/>
+      <c r="E171" s="127"/>
+      <c r="F171" s="127"/>
+      <c r="G171" s="127"/>
+      <c r="H171" s="127"/>
+      <c r="I171" s="127"/>
+      <c r="J171" s="101"/>
+      <c r="K171" s="102"/>
+      <c r="L171" s="102"/>
     </row>
     <row r="172" s="5" customFormat="1" ht="31.5" customHeight="1" spans="1:12">
-      <c r="A172" s="41">
+      <c r="A172" s="42">
         <v>6</v>
       </c>
-      <c r="B172" s="44" t="s">
+      <c r="B172" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="C172" s="44"/>
-      <c r="D172" s="44"/>
-      <c r="E172" s="44"/>
-      <c r="F172" s="44"/>
-      <c r="G172" s="44"/>
-      <c r="H172" s="44"/>
-      <c r="I172" s="44"/>
-      <c r="J172" s="100"/>
-      <c r="K172" s="101"/>
-      <c r="L172" s="101"/>
+      <c r="C172" s="45"/>
+      <c r="D172" s="45"/>
+      <c r="E172" s="45"/>
+      <c r="F172" s="45"/>
+      <c r="G172" s="45"/>
+      <c r="H172" s="45"/>
+      <c r="I172" s="45"/>
+      <c r="J172" s="101"/>
+      <c r="K172" s="102"/>
+      <c r="L172" s="102"/>
     </row>
     <row r="173" s="5" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A173" s="41">
+      <c r="A173" s="42">
         <v>7</v>
       </c>
-      <c r="B173" s="126" t="s">
+      <c r="B173" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="C173" s="126"/>
-      <c r="D173" s="126"/>
-      <c r="E173" s="126"/>
-      <c r="F173" s="126"/>
-      <c r="G173" s="126"/>
-      <c r="H173" s="126"/>
-      <c r="I173" s="126"/>
-      <c r="J173" s="100"/>
-      <c r="K173" s="101"/>
-      <c r="L173" s="101"/>
+      <c r="C173" s="127"/>
+      <c r="D173" s="127"/>
+      <c r="E173" s="127"/>
+      <c r="F173" s="127"/>
+      <c r="G173" s="127"/>
+      <c r="H173" s="127"/>
+      <c r="I173" s="127"/>
+      <c r="J173" s="101"/>
+      <c r="K173" s="102"/>
+      <c r="L173" s="102"/>
     </row>
     <row r="174" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
-      <c r="A174" s="41">
+      <c r="A174" s="42">
         <v>8</v>
       </c>
-      <c r="B174" s="126" t="s">
+      <c r="B174" s="127" t="s">
         <v>222</v>
       </c>
-      <c r="C174" s="126"/>
-      <c r="D174" s="126"/>
-      <c r="E174" s="126"/>
-      <c r="F174" s="126"/>
-      <c r="G174" s="126"/>
-      <c r="H174" s="126"/>
-      <c r="I174" s="126"/>
-      <c r="J174" s="100"/>
-      <c r="K174" s="101"/>
-      <c r="L174" s="101"/>
+      <c r="C174" s="127"/>
+      <c r="D174" s="127"/>
+      <c r="E174" s="127"/>
+      <c r="F174" s="127"/>
+      <c r="G174" s="127"/>
+      <c r="H174" s="127"/>
+      <c r="I174" s="127"/>
+      <c r="J174" s="101"/>
+      <c r="K174" s="102"/>
+      <c r="L174" s="102"/>
     </row>
     <row r="175" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
-      <c r="A175" s="41">
+      <c r="A175" s="42">
         <v>9</v>
       </c>
-      <c r="B175" s="126" t="s">
+      <c r="B175" s="127" t="s">
         <v>223</v>
       </c>
-      <c r="C175" s="126"/>
-      <c r="D175" s="126"/>
-      <c r="E175" s="126"/>
-      <c r="F175" s="126"/>
-      <c r="G175" s="126"/>
-      <c r="H175" s="126"/>
-      <c r="I175" s="126"/>
-      <c r="J175" s="100"/>
-      <c r="K175" s="101"/>
-      <c r="L175" s="101"/>
+      <c r="C175" s="127"/>
+      <c r="D175" s="127"/>
+      <c r="E175" s="127"/>
+      <c r="F175" s="127"/>
+      <c r="G175" s="127"/>
+      <c r="H175" s="127"/>
+      <c r="I175" s="127"/>
+      <c r="J175" s="101"/>
+      <c r="K175" s="102"/>
+      <c r="L175" s="102"/>
     </row>
     <row r="176" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A176" s="127"/>
-      <c r="B176" s="128" t="s">
+      <c r="A176" s="128"/>
+      <c r="B176" s="129" t="s">
         <v>224</v>
       </c>
-      <c r="C176" s="128"/>
-      <c r="D176" s="128"/>
-      <c r="E176" s="128"/>
-      <c r="F176" s="128"/>
-      <c r="G176" s="128"/>
-      <c r="H176" s="128"/>
-      <c r="I176" s="128"/>
-      <c r="J176" s="129"/>
-      <c r="K176" s="129"/>
-      <c r="L176" s="129"/>
+      <c r="C176" s="129"/>
+      <c r="D176" s="129"/>
+      <c r="E176" s="129"/>
+      <c r="F176" s="129"/>
+      <c r="G176" s="129"/>
+      <c r="H176" s="129"/>
+      <c r="I176" s="129"/>
+      <c r="J176" s="130"/>
+      <c r="K176" s="130"/>
+      <c r="L176" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="31">

--- a/muban_clean/dizhuan.xlsx
+++ b/muban_clean/dizhuan.xlsx
@@ -10,7 +10,7 @@
     <sheet name="2019报价" sheetId="15" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2019报价'!$A$1:$I$176</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2019报价'!$A$1:$I$183</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="225">
   <si>
     <t xml:space="preserve">                                                                                      广东帝豪装饰集团巴中分公司（工程预算单）
 </t>
@@ -1281,8 +1281,7 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="新宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1293,14 +1292,15 @@
     </font>
     <font>
       <vertAlign val="superscript"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="新宋体"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新宋体"/>
       <charset val="134"/>
     </font>
@@ -1965,7 +1965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2072,9 +2072,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2728,7 +2725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:FM176"/>
+  <dimension ref="A1:FM183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.08333333333333" style="19" customWidth="1"/>
@@ -3346,46 +3343,46 @@
       <c r="A8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="43"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="35"/>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:169">
-      <c r="A9" s="44">
+      <c r="A9" s="43">
         <v>1</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <v>70</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <f t="shared" ref="F9:F24" si="0">C9*E9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="45">
         <v>25</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="41">
         <f t="shared" ref="H9:H11" si="1">SUM(G9*C9)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="46" t="s">
         <v>16</v>
       </c>
       <c r="J9" s="35"/>
@@ -3393,94 +3390,94 @@
       <c r="L9" s="35"/>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:169">
-      <c r="A10" s="44">
+      <c r="A10" s="43">
         <v>2</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="42" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="43">
         <v>95</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="43">
         <v>55</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="41">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="43" t="s">
+      <c r="I10" s="42" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:169">
-      <c r="A11" s="44">
+      <c r="A11" s="43">
         <v>3</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="51" t="s">
+      <c r="C11" s="49"/>
+      <c r="D11" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="50">
         <v>125</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="50">
         <v>65</v>
       </c>
-      <c r="H11" s="51">
+      <c r="H11" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="53"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54" t="s">
+      <c r="J11" s="52"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:169">
-      <c r="A12" s="44">
+      <c r="A12" s="43">
         <v>4</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42" t="s">
+      <c r="C12" s="41"/>
+      <c r="D12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="41">
         <v>38</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="41">
         <v>22</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="41">
         <f>C12*G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="42" t="s">
         <v>26</v>
       </c>
       <c r="J12" s="35"/>
@@ -3488,152 +3485,152 @@
       <c r="L12" s="35"/>
     </row>
     <row r="13" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A13" s="44">
+      <c r="A13" s="43">
         <v>5</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="44" t="s">
+      <c r="C13" s="41"/>
+      <c r="D13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="43">
         <v>14</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="43">
         <v>8</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="41">
         <f>C13*G13</f>
         <v>0</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="57"/>
+      <c r="J13" s="56"/>
     </row>
     <row r="14" s="5" customFormat="1" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A14" s="44">
+      <c r="A14" s="43">
         <v>6</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="44" t="s">
+      <c r="C14" s="41"/>
+      <c r="D14" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="43">
         <v>16</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="43">
         <v>10</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="41">
         <f>C14*G14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="57"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:169">
-      <c r="A15" s="44">
+      <c r="A15" s="43">
         <v>7</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="44" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="43">
         <v>4</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="43">
         <v>6.5</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="41">
         <f>C15*G15</f>
         <v>0</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="55" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" s="6" customFormat="1" ht="25" customHeight="1" spans="1:169">
-      <c r="A16" s="44">
+      <c r="A16" s="43">
         <v>8</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51" t="s">
+      <c r="C16" s="50"/>
+      <c r="D16" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="50">
         <v>28</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="50">
         <v>48</v>
       </c>
-      <c r="H16" s="51">
+      <c r="H16" s="50">
         <f>C16*G16</f>
         <v>0</v>
       </c>
-      <c r="I16" s="52" t="s">
+      <c r="I16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A17" s="44">
+      <c r="A17" s="43">
         <v>9</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42" t="s">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="42">
-        <v>0</v>
-      </c>
-      <c r="F17" s="42">
+      <c r="E17" s="41">
+        <v>0</v>
+      </c>
+      <c r="F17" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="41">
         <v>2.5</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="41">
         <f>SUM(G17*C17)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="43" t="s">
+      <c r="I17" s="42" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="35"/>
@@ -3641,60 +3638,60 @@
       <c r="L17" s="35"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A18" s="44">
+      <c r="A18" s="43">
         <v>10</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44" t="s">
+      <c r="C18" s="43"/>
+      <c r="D18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="43">
         <v>135</v>
       </c>
-      <c r="F18" s="42">
+      <c r="F18" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>95</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="41">
         <f>SUM(G18*C18)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="56" t="s">
+      <c r="I18" s="55" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A19" s="44">
+      <c r="A19" s="43">
         <v>11</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="44" t="s">
+      <c r="C19" s="41"/>
+      <c r="D19" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="41">
         <v>2</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="41">
         <v>4</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="41">
         <f t="shared" ref="H19:H24" si="2">SUM(G19*C19)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="42" t="s">
         <v>40</v>
       </c>
       <c r="J19" s="35"/>
@@ -3702,31 +3699,31 @@
       <c r="L19" s="35"/>
     </row>
     <row r="20" ht="27" customHeight="1" spans="1:12">
-      <c r="A20" s="44">
+      <c r="A20" s="43">
         <v>12</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <v>19</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="41">
         <v>13</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="42" t="s">
         <v>42</v>
       </c>
       <c r="J20" s="35"/>
@@ -3734,31 +3731,31 @@
       <c r="L20" s="35"/>
     </row>
     <row r="21" ht="27" customHeight="1" spans="1:12">
-      <c r="A21" s="44">
+      <c r="A21" s="43">
         <v>13</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42" t="s">
+      <c r="C21" s="41"/>
+      <c r="D21" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="42">
+      <c r="E21" s="41">
         <v>12</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="41">
         <v>7</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="42" t="s">
         <v>44</v>
       </c>
       <c r="J21" s="35"/>
@@ -3766,31 +3763,31 @@
       <c r="L21" s="35"/>
     </row>
     <row r="22" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A22" s="44">
+      <c r="A22" s="43">
         <v>14</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42" t="s">
+      <c r="C22" s="41"/>
+      <c r="D22" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="41">
         <v>160</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="41">
         <v>360</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I22" s="43" t="s">
+      <c r="I22" s="42" t="s">
         <v>47</v>
       </c>
       <c r="J22" s="35"/>
@@ -3798,31 +3795,31 @@
       <c r="L22" s="35"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:12">
-      <c r="A23" s="44">
+      <c r="A23" s="43">
         <v>15</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42" t="s">
+      <c r="C23" s="41"/>
+      <c r="D23" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="41">
         <v>25</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="41">
         <v>10</v>
       </c>
-      <c r="H23" s="42">
+      <c r="H23" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="43" t="s">
+      <c r="I23" s="42" t="s">
         <v>49</v>
       </c>
       <c r="J23" s="35"/>
@@ -3830,31 +3827,31 @@
       <c r="L23" s="35"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:12">
-      <c r="A24" s="44">
+      <c r="A24" s="43">
         <v>16</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42" t="s">
+      <c r="C24" s="41"/>
+      <c r="D24" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="41">
         <v>12</v>
       </c>
-      <c r="F24" s="42">
+      <c r="F24" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="41">
         <v>5</v>
       </c>
-      <c r="H24" s="42">
+      <c r="H24" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I24" s="43" t="s">
+      <c r="I24" s="42" t="s">
         <v>51</v>
       </c>
       <c r="J24" s="35"/>
@@ -3862,135 +3859,135 @@
       <c r="L24" s="35"/>
     </row>
     <row r="25" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A25" s="62"/>
-      <c r="B25" s="63" t="s">
+      <c r="A25" s="61"/>
+      <c r="B25" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62">
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61">
         <f>SUM(F9:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62">
+      <c r="G25" s="61"/>
+      <c r="H25" s="61">
         <f>SUM(H9:H24)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="64"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:12">
       <c r="A26" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="66" t="s">
+      <c r="B26" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="43"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
       <c r="J26" s="35"/>
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
     </row>
     <row r="27" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A27" s="51">
+      <c r="A27" s="50">
         <v>1</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51" t="s">
+      <c r="C27" s="50"/>
+      <c r="D27" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="50">
         <v>28</v>
       </c>
-      <c r="F27" s="51">
+      <c r="F27" s="50">
         <f t="shared" ref="F27:F32" si="3">C27*E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="50">
         <v>32</v>
       </c>
-      <c r="H27" s="51">
+      <c r="H27" s="50">
         <f t="shared" ref="H27:H32" si="4">SUM(G27*C27)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="52" t="s">
+      <c r="I27" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
     </row>
     <row r="28" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A28" s="51">
+      <c r="A28" s="50">
         <v>2</v>
       </c>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51" t="s">
+      <c r="C28" s="50"/>
+      <c r="D28" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="50">
         <v>28</v>
       </c>
-      <c r="F28" s="51">
+      <c r="F28" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G28" s="51">
+      <c r="G28" s="50">
         <v>40</v>
       </c>
-      <c r="H28" s="51">
+      <c r="H28" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="52" t="s">
+      <c r="I28" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="1:12">
-      <c r="A29" s="51">
+      <c r="A29" s="50">
         <v>3</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42" t="s">
+      <c r="C29" s="41"/>
+      <c r="D29" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="42">
-        <v>0</v>
-      </c>
-      <c r="F29" s="42">
+      <c r="E29" s="41">
+        <v>0</v>
+      </c>
+      <c r="F29" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G29" s="42">
+      <c r="G29" s="41">
         <v>9</v>
       </c>
-      <c r="H29" s="42">
+      <c r="H29" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I29" s="43" t="s">
+      <c r="I29" s="42" t="s">
         <v>59</v>
       </c>
       <c r="J29" s="35"/>
@@ -3998,63 +3995,63 @@
       <c r="L29" s="35"/>
     </row>
     <row r="30" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A30" s="51">
+      <c r="A30" s="50">
         <v>4</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42" t="s">
+      <c r="C30" s="41"/>
+      <c r="D30" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="41">
         <v>8</v>
       </c>
-      <c r="F30" s="42">
+      <c r="F30" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="41">
         <v>20</v>
       </c>
-      <c r="H30" s="42">
+      <c r="H30" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:12">
-      <c r="A31" s="51">
+      <c r="A31" s="50">
         <v>5</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42" t="s">
+      <c r="C31" s="41"/>
+      <c r="D31" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="42">
-        <v>0</v>
-      </c>
-      <c r="F31" s="42">
+      <c r="E31" s="41">
+        <v>0</v>
+      </c>
+      <c r="F31" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G31" s="42">
+      <c r="G31" s="41">
         <v>2.5</v>
       </c>
-      <c r="H31" s="42">
+      <c r="H31" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I31" s="43" t="s">
+      <c r="I31" s="42" t="s">
         <v>62</v>
       </c>
       <c r="J31" s="35"/>
@@ -4062,31 +4059,31 @@
       <c r="L31" s="35"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:12">
-      <c r="A32" s="51">
+      <c r="A32" s="50">
         <v>6</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42" t="s">
+      <c r="C32" s="41"/>
+      <c r="D32" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="42">
+      <c r="E32" s="41">
         <v>45</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F32" s="41">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G32" s="41">
         <v>20</v>
       </c>
-      <c r="H32" s="42">
+      <c r="H32" s="41">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I32" s="43" t="s">
+      <c r="I32" s="42" t="s">
         <v>64</v>
       </c>
       <c r="J32" s="35"/>
@@ -4094,31 +4091,31 @@
       <c r="L32" s="35"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:12">
-      <c r="A33" s="51">
+      <c r="A33" s="50">
         <v>7</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="42"/>
-      <c r="D33" s="42" t="s">
+      <c r="C33" s="41"/>
+      <c r="D33" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="41">
         <v>12</v>
       </c>
-      <c r="F33" s="42">
+      <c r="F33" s="41">
         <f t="shared" ref="F33:F44" si="5">C33*E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="42">
+      <c r="G33" s="41">
         <v>5</v>
       </c>
-      <c r="H33" s="42">
+      <c r="H33" s="41">
         <f t="shared" ref="H33:H44" si="6">SUM(G33*C33)</f>
         <v>0</v>
       </c>
-      <c r="I33" s="43" t="s">
+      <c r="I33" s="42" t="s">
         <v>51</v>
       </c>
       <c r="J33" s="35"/>
@@ -4126,135 +4123,135 @@
       <c r="L33" s="35"/>
     </row>
     <row r="34" s="9" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A34" s="70"/>
-      <c r="B34" s="71" t="s">
+      <c r="A34" s="69"/>
+      <c r="B34" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="73">
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72">
         <f>SUM(F27:F33)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="70"/>
-      <c r="H34" s="73">
+      <c r="G34" s="69"/>
+      <c r="H34" s="72">
         <f>SUM(H27:H33)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="74"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="75"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="74"/>
+      <c r="L34" s="74"/>
     </row>
     <row r="35" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="43"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="42"/>
       <c r="J35" s="35"/>
       <c r="K35" s="35"/>
       <c r="L35" s="35"/>
     </row>
     <row r="36" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A36" s="51">
+      <c r="A36" s="50">
         <v>1</v>
       </c>
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51" t="s">
+      <c r="C36" s="50"/>
+      <c r="D36" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="50">
         <v>28</v>
       </c>
-      <c r="F36" s="51">
+      <c r="F36" s="50">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G36" s="51">
+      <c r="G36" s="50">
         <v>32</v>
       </c>
-      <c r="H36" s="51">
+      <c r="H36" s="50">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I36" s="52" t="s">
+      <c r="I36" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J36" s="60"/>
-      <c r="K36" s="60"/>
-      <c r="L36" s="60"/>
+      <c r="J36" s="59"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="59"/>
     </row>
     <row r="37" s="6" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A37" s="51">
+      <c r="A37" s="50">
         <v>2</v>
       </c>
-      <c r="B37" s="67" t="s">
+      <c r="B37" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51" t="s">
+      <c r="C37" s="50"/>
+      <c r="D37" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="50">
         <v>28</v>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="50">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G37" s="51">
+      <c r="G37" s="50">
         <v>40</v>
       </c>
-      <c r="H37" s="51">
+      <c r="H37" s="50">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I37" s="52" t="s">
+      <c r="I37" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J37" s="60"/>
-      <c r="K37" s="60"/>
-      <c r="L37" s="60"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="1:12">
-      <c r="A38" s="51">
+      <c r="A38" s="50">
         <v>3</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="B38" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42" t="s">
+      <c r="C38" s="41"/>
+      <c r="D38" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="42">
-        <v>0</v>
-      </c>
-      <c r="F38" s="42">
+      <c r="E38" s="41">
+        <v>0</v>
+      </c>
+      <c r="F38" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G38" s="42">
+      <c r="G38" s="41">
         <v>9</v>
       </c>
-      <c r="H38" s="42">
+      <c r="H38" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I38" s="43" t="s">
+      <c r="I38" s="42" t="s">
         <v>59</v>
       </c>
       <c r="J38" s="35"/>
@@ -4262,61 +4259,61 @@
       <c r="L38" s="35"/>
     </row>
     <row r="39" s="8" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A39" s="51">
+      <c r="A39" s="50">
         <v>4</v>
       </c>
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42" t="s">
+      <c r="C39" s="41"/>
+      <c r="D39" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="42">
+      <c r="E39" s="41">
         <v>8</v>
       </c>
-      <c r="F39" s="42">
+      <c r="F39" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G39" s="42">
+      <c r="G39" s="41">
         <v>20</v>
       </c>
-      <c r="H39" s="42">
+      <c r="H39" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I39" s="43" t="s">
+      <c r="I39" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="69"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="68"/>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:12">
-      <c r="A40" s="51">
+      <c r="A40" s="50">
         <v>5</v>
       </c>
-      <c r="B40" s="45" t="s">
+      <c r="B40" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42" t="s">
+      <c r="C40" s="41"/>
+      <c r="D40" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42">
+      <c r="E40" s="41"/>
+      <c r="F40" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G40" s="42">
+      <c r="G40" s="41">
         <v>2.5</v>
       </c>
-      <c r="H40" s="42">
+      <c r="H40" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I40" s="43" t="s">
+      <c r="I40" s="42" t="s">
         <v>62</v>
       </c>
       <c r="J40" s="35"/>
@@ -4324,31 +4321,31 @@
       <c r="L40" s="35"/>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:12">
-      <c r="A41" s="51">
+      <c r="A41" s="50">
         <v>6</v>
       </c>
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42" t="s">
+      <c r="C41" s="41"/>
+      <c r="D41" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="42">
+      <c r="E41" s="41">
         <v>45</v>
       </c>
-      <c r="F41" s="42">
+      <c r="F41" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G41" s="42">
+      <c r="G41" s="41">
         <v>20</v>
       </c>
-      <c r="H41" s="42">
+      <c r="H41" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="42" t="s">
         <v>67</v>
       </c>
       <c r="J41" s="35"/>
@@ -4356,31 +4353,31 @@
       <c r="L41" s="35"/>
     </row>
     <row r="42" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A42" s="51">
+      <c r="A42" s="50">
         <v>7</v>
       </c>
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42" t="s">
+      <c r="C42" s="41"/>
+      <c r="D42" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="42">
+      <c r="E42" s="41">
         <v>22</v>
       </c>
-      <c r="F42" s="42">
+      <c r="F42" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G42" s="42">
+      <c r="G42" s="41">
         <v>12</v>
       </c>
-      <c r="H42" s="42">
+      <c r="H42" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I42" s="43" t="s">
+      <c r="I42" s="42" t="s">
         <v>69</v>
       </c>
       <c r="J42" s="35"/>
@@ -4388,31 +4385,31 @@
       <c r="L42" s="35"/>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:12">
-      <c r="A43" s="51">
+      <c r="A43" s="50">
         <v>8</v>
       </c>
-      <c r="B43" s="45" t="s">
+      <c r="B43" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42" t="s">
+      <c r="C43" s="41"/>
+      <c r="D43" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="42">
+      <c r="E43" s="41">
         <v>45</v>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G43" s="42">
+      <c r="G43" s="41">
         <v>20</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I43" s="43" t="s">
+      <c r="I43" s="42" t="s">
         <v>71</v>
       </c>
       <c r="J43" s="35"/>
@@ -4420,31 +4417,31 @@
       <c r="L43" s="35"/>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:12">
-      <c r="A44" s="51">
+      <c r="A44" s="50">
         <v>9</v>
       </c>
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42" t="s">
+      <c r="C44" s="41"/>
+      <c r="D44" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="42">
+      <c r="E44" s="41">
         <v>12</v>
       </c>
-      <c r="F44" s="42">
+      <c r="F44" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G44" s="42">
+      <c r="G44" s="41">
         <v>5</v>
       </c>
-      <c r="H44" s="42">
+      <c r="H44" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I44" s="43" t="s">
+      <c r="I44" s="42" t="s">
         <v>51</v>
       </c>
       <c r="J44" s="35"/>
@@ -4452,3449 +4449,3679 @@
       <c r="L44" s="35"/>
     </row>
     <row r="45" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A45" s="62"/>
-      <c r="B45" s="63" t="s">
+      <c r="A45" s="61"/>
+      <c r="B45" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="62"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="62">
+      <c r="C45" s="61"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="61">
         <f>SUM(F36:F44)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="62"/>
-      <c r="H45" s="62">
+      <c r="G45" s="61"/>
+      <c r="H45" s="61">
         <f>SUM(H36:H44)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="64"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
+      <c r="L45" s="64"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:12">
       <c r="A46" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="43"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="77"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="42"/>
       <c r="J46" s="35"/>
       <c r="K46" s="35"/>
       <c r="L46" s="35"/>
     </row>
     <row r="47" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A47" s="51">
+      <c r="A47" s="50">
         <v>1</v>
       </c>
-      <c r="B47" s="67" t="s">
+      <c r="B47" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51" t="s">
+      <c r="C47" s="50"/>
+      <c r="D47" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="50">
         <v>28</v>
       </c>
-      <c r="F47" s="51">
-        <f>C47*E47</f>
-        <v>0</v>
-      </c>
-      <c r="G47" s="51">
+      <c r="F47" s="50">
+        <f t="shared" ref="F47:F55" si="7">C47*E47</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="50">
         <v>32</v>
       </c>
-      <c r="H47" s="51">
-        <f>SUM(G47*C47)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="52" t="s">
+      <c r="H47" s="50">
+        <f t="shared" ref="H47:H55" si="8">SUM(G47*C47)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J47" s="60"/>
-      <c r="K47" s="60"/>
-      <c r="L47" s="60"/>
-    </row>
-    <row r="48" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A48" s="51">
+      <c r="J47" s="59"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="59"/>
+    </row>
+    <row r="48" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A48" s="50">
         <v>2</v>
       </c>
-      <c r="B48" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42">
-        <f t="shared" ref="F48:F53" si="7">C48*E48</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="42">
-        <v>2.5</v>
-      </c>
-      <c r="H48" s="42">
-        <f t="shared" ref="H48:H53" si="8">SUM(G48*C48)</f>
-        <v>0</v>
-      </c>
-      <c r="I48" s="43" t="s">
-        <v>62</v>
+      <c r="B48" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="41">
+        <v>70</v>
+      </c>
+      <c r="F48" s="41">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="45">
+        <v>25</v>
+      </c>
+      <c r="H48" s="41">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="46" t="s">
+        <v>16</v>
       </c>
       <c r="J48" s="35"/>
       <c r="K48" s="35"/>
       <c r="L48" s="35"/>
     </row>
-    <row r="49" ht="17" customHeight="1" spans="1:12">
-      <c r="A49" s="51">
+    <row r="49" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A49" s="50">
         <v>3</v>
       </c>
       <c r="B49" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="50">
+        <v>125</v>
+      </c>
+      <c r="F49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="50">
+        <v>65</v>
+      </c>
+      <c r="H49" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="52"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1" spans="1:12">
+      <c r="A50" s="50">
+        <v>4</v>
+      </c>
+      <c r="B50" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="44"/>
-      <c r="D49" s="42" t="s">
+      <c r="C50" s="43"/>
+      <c r="D50" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="44">
+      <c r="E50" s="43">
         <v>95</v>
       </c>
-      <c r="F49" s="42">
+      <c r="F50" s="41">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G49" s="44">
+      <c r="G50" s="43">
         <v>55</v>
       </c>
-      <c r="H49" s="42">
+      <c r="H50" s="41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I49" s="43" t="s">
+      <c r="I50" s="42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A50" s="51">
-        <v>4</v>
-      </c>
-      <c r="B50" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" s="42"/>
-      <c r="D50" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E50" s="42">
-        <v>2</v>
-      </c>
-      <c r="F50" s="42">
+    <row r="51" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
+      <c r="A51" s="50">
+        <v>5</v>
+      </c>
+      <c r="B51" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G50" s="42">
-        <v>4</v>
-      </c>
-      <c r="H50" s="42">
+      <c r="G51" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H51" s="41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I50" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-    </row>
-    <row r="51" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A51" s="51">
-        <v>5</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="42">
-        <v>19</v>
-      </c>
-      <c r="F51" s="42">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="42">
-        <v>13</v>
-      </c>
-      <c r="H51" s="42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="43" t="s">
-        <v>42</v>
+      <c r="I51" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="J51" s="35"/>
       <c r="K51" s="35"/>
       <c r="L51" s="35"/>
     </row>
-    <row r="52" ht="27" customHeight="1" spans="1:12">
-      <c r="A52" s="51">
+    <row r="52" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A52" s="50">
         <v>6</v>
       </c>
-      <c r="B52" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="42">
-        <v>12</v>
-      </c>
-      <c r="F52" s="42">
+      <c r="B52" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="41"/>
+      <c r="D52" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="41">
+        <v>2</v>
+      </c>
+      <c r="F52" s="41">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G52" s="42">
-        <v>7</v>
-      </c>
-      <c r="H52" s="42">
+      <c r="G52" s="41">
+        <v>4</v>
+      </c>
+      <c r="H52" s="41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I52" s="43" t="s">
-        <v>44</v>
+      <c r="I52" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="J52" s="35"/>
       <c r="K52" s="35"/>
       <c r="L52" s="35"/>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:12">
-      <c r="A53" s="51">
+    <row r="53" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A53" s="50">
         <v>7</v>
       </c>
-      <c r="B53" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42" t="s">
+      <c r="B53" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E53" s="42">
-        <v>12</v>
-      </c>
-      <c r="F53" s="42">
+      <c r="E53" s="41">
+        <v>19</v>
+      </c>
+      <c r="F53" s="41">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G53" s="42">
-        <v>5</v>
-      </c>
-      <c r="H53" s="42">
+      <c r="G53" s="41">
+        <v>13</v>
+      </c>
+      <c r="H53" s="41">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I53" s="43" t="s">
-        <v>51</v>
+      <c r="I53" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="J53" s="35"/>
       <c r="K53" s="35"/>
       <c r="L53" s="35"/>
     </row>
-    <row r="54" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A54" s="62"/>
-      <c r="B54" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="62"/>
-      <c r="D54" s="62"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="62">
-        <f>SUM(F47:F53)</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="62"/>
-      <c r="H54" s="62">
-        <f>SUM(H47:H53)</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="64"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-    </row>
-    <row r="55" ht="18" customHeight="1" spans="1:12">
-      <c r="A55" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="43"/>
+    <row r="54" ht="27" customHeight="1" spans="1:12">
+      <c r="A54" s="50">
+        <v>8</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="41">
+        <v>12</v>
+      </c>
+      <c r="F54" s="41">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G54" s="41">
+        <v>7</v>
+      </c>
+      <c r="H54" s="41">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+    </row>
+    <row r="55" ht="14" customHeight="1" spans="1:12">
+      <c r="A55" s="50">
+        <v>9</v>
+      </c>
+      <c r="B55" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="41">
+        <v>12</v>
+      </c>
+      <c r="F55" s="41">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G55" s="41">
+        <v>5</v>
+      </c>
+      <c r="H55" s="41">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="42" t="s">
+        <v>51</v>
+      </c>
       <c r="J55" s="35"/>
       <c r="K55" s="35"/>
       <c r="L55" s="35"/>
     </row>
-    <row r="56" s="6" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A56" s="51">
+    <row r="56" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A56" s="61"/>
+      <c r="B56" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61">
+        <f>SUM(F47:F55)</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61">
+        <f>SUM(H47:H55)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="63"/>
+      <c r="J56" s="64"/>
+      <c r="K56" s="64"/>
+      <c r="L56" s="64"/>
+    </row>
+    <row r="57" ht="18" customHeight="1" spans="1:12">
+      <c r="A57" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+    </row>
+    <row r="58" s="6" customFormat="1" ht="27" customHeight="1" spans="1:12">
+      <c r="A58" s="50">
         <v>1</v>
       </c>
-      <c r="B56" s="67" t="s">
+      <c r="B58" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51" t="s">
+      <c r="C58" s="50"/>
+      <c r="D58" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="51">
+      <c r="E58" s="50">
         <v>28</v>
       </c>
-      <c r="F56" s="51">
-        <f t="shared" ref="F56:F58" si="9">C56*E56</f>
-        <v>0</v>
-      </c>
-      <c r="G56" s="51">
+      <c r="F58" s="50">
+        <f t="shared" ref="F58:F60" si="9">C58*E58</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="50">
         <v>32</v>
       </c>
-      <c r="H56" s="51">
-        <f t="shared" ref="H56:H58" si="10">SUM(G56*C56)</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="52" t="s">
+      <c r="H58" s="50">
+        <f t="shared" ref="H58:H60" si="10">SUM(G58*C58)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="J56" s="60"/>
-      <c r="K56" s="60"/>
-      <c r="L56" s="60"/>
-    </row>
-    <row r="57" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A57" s="51">
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
+      <c r="L58" s="59"/>
+    </row>
+    <row r="59" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A59" s="50">
         <v>2</v>
       </c>
-      <c r="B57" s="67" t="s">
+      <c r="B59" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51" t="s">
+      <c r="C59" s="50"/>
+      <c r="D59" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="51">
+      <c r="E59" s="50">
         <v>28</v>
       </c>
-      <c r="F57" s="51">
+      <c r="F59" s="50">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G57" s="51">
+      <c r="G59" s="50">
         <v>40</v>
       </c>
-      <c r="H57" s="51">
+      <c r="H59" s="50">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I57" s="52" t="s">
+      <c r="I59" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J57" s="60"/>
-      <c r="K57" s="60"/>
-      <c r="L57" s="60"/>
-    </row>
-    <row r="58" ht="16" customHeight="1" spans="1:12">
-      <c r="A58" s="51">
+      <c r="J59" s="59"/>
+      <c r="K59" s="59"/>
+      <c r="L59" s="59"/>
+    </row>
+    <row r="60" ht="16" customHeight="1" spans="1:12">
+      <c r="A60" s="50">
         <v>3</v>
       </c>
-      <c r="B58" s="47" t="s">
+      <c r="B60" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="42"/>
-      <c r="D58" s="42" t="s">
+      <c r="C60" s="41"/>
+      <c r="D60" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E58" s="42">
-        <v>0</v>
-      </c>
-      <c r="F58" s="42">
+      <c r="E60" s="41">
+        <v>0</v>
+      </c>
+      <c r="F60" s="41">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G58" s="42">
+      <c r="G60" s="41">
         <v>9</v>
       </c>
-      <c r="H58" s="42">
+      <c r="H60" s="41">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I58" s="43" t="s">
+      <c r="I60" s="42" t="s">
         <v>59</v>
-      </c>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-    </row>
-    <row r="59" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A59" s="51">
-        <v>4</v>
-      </c>
-      <c r="B59" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="42">
-        <v>8</v>
-      </c>
-      <c r="F59" s="42">
-        <f t="shared" ref="F59:F64" si="11">C59*E59</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="42">
-        <v>20</v>
-      </c>
-      <c r="H59" s="42">
-        <f t="shared" ref="H59:H64" si="12">SUM(G59*C59)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
-      <c r="L59" s="69"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="1:12">
-      <c r="A60" s="51">
-        <v>5</v>
-      </c>
-      <c r="B60" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G60" s="42">
-        <v>2.5</v>
-      </c>
-      <c r="H60" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="43" t="s">
-        <v>62</v>
       </c>
       <c r="J60" s="35"/>
       <c r="K60" s="35"/>
       <c r="L60" s="35"/>
     </row>
-    <row r="61" ht="15" customHeight="1" spans="1:12">
-      <c r="A61" s="51">
-        <v>6</v>
-      </c>
-      <c r="B61" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="42"/>
-      <c r="D61" s="42" t="s">
+    <row r="61" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A61" s="50">
+        <v>4</v>
+      </c>
+      <c r="B61" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="41">
+        <v>8</v>
+      </c>
+      <c r="F61" s="41">
+        <f t="shared" ref="F61:F66" si="11">C61*E61</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="41">
+        <v>20</v>
+      </c>
+      <c r="H61" s="41">
+        <f t="shared" ref="H61:H66" si="12">SUM(G61*C61)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="J61" s="68"/>
+      <c r="K61" s="68"/>
+      <c r="L61" s="68"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:12">
+      <c r="A62" s="50">
+        <v>5</v>
+      </c>
+      <c r="B62" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E61" s="42">
-        <v>45</v>
-      </c>
-      <c r="F61" s="42">
+      <c r="E62" s="41"/>
+      <c r="F62" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G61" s="42">
-        <v>20</v>
-      </c>
-      <c r="H61" s="42">
+      <c r="G62" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H62" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I61" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A62" s="51">
-        <v>7</v>
-      </c>
-      <c r="B62" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="42">
-        <v>22</v>
-      </c>
-      <c r="F62" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G62" s="42">
-        <v>12</v>
-      </c>
-      <c r="H62" s="42">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="43" t="s">
-        <v>69</v>
+      <c r="I62" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="J62" s="35"/>
       <c r="K62" s="35"/>
       <c r="L62" s="35"/>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:12">
-      <c r="A63" s="51">
-        <v>8</v>
-      </c>
-      <c r="B63" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42" t="s">
+      <c r="A63" s="50">
+        <v>6</v>
+      </c>
+      <c r="B63" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E63" s="42">
+      <c r="E63" s="41">
         <v>45</v>
       </c>
-      <c r="F63" s="42">
+      <c r="F63" s="41">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G63" s="42">
+      <c r="G63" s="41">
         <v>20</v>
       </c>
-      <c r="H63" s="42">
+      <c r="H63" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I63" s="43" t="s">
-        <v>71</v>
+      <c r="I63" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="J63" s="35"/>
       <c r="K63" s="35"/>
       <c r="L63" s="35"/>
     </row>
-    <row r="64" ht="15" customHeight="1" spans="1:12">
-      <c r="A64" s="51">
-        <v>9</v>
-      </c>
-      <c r="B64" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42" t="s">
+    <row r="64" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A64" s="50">
+        <v>7</v>
+      </c>
+      <c r="B64" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="41"/>
+      <c r="D64" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E64" s="42">
+      <c r="E64" s="41">
+        <v>22</v>
+      </c>
+      <c r="F64" s="41">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="41">
         <v>12</v>
       </c>
-      <c r="F64" s="42">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="42">
-        <v>5</v>
-      </c>
-      <c r="H64" s="42">
+      <c r="H64" s="41">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I64" s="43" t="s">
-        <v>51</v>
+      <c r="I64" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="J64" s="35"/>
       <c r="K64" s="35"/>
       <c r="L64" s="35"/>
     </row>
-    <row r="65" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A65" s="62"/>
-      <c r="B65" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C65" s="62"/>
-      <c r="D65" s="62"/>
-      <c r="E65" s="62"/>
-      <c r="F65" s="62">
-        <f>SUM(F56:F64)</f>
-        <v>0</v>
-      </c>
-      <c r="G65" s="62"/>
-      <c r="H65" s="62">
-        <f>SUM(H56:H64)</f>
-        <v>0</v>
-      </c>
-      <c r="I65" s="64"/>
-      <c r="J65" s="65"/>
-      <c r="K65" s="65"/>
-      <c r="L65" s="65"/>
-    </row>
-    <row r="66" ht="18" customHeight="1" spans="1:12">
-      <c r="A66" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="43"/>
+    <row r="65" ht="15" customHeight="1" spans="1:12">
+      <c r="A65" s="50">
+        <v>8</v>
+      </c>
+      <c r="B65" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="41">
+        <v>45</v>
+      </c>
+      <c r="F65" s="41">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="41">
+        <v>20</v>
+      </c>
+      <c r="H65" s="41">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="35"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:12">
+      <c r="A66" s="50">
+        <v>9</v>
+      </c>
+      <c r="B66" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="41"/>
+      <c r="D66" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="41">
+        <v>12</v>
+      </c>
+      <c r="F66" s="41">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G66" s="41">
+        <v>5</v>
+      </c>
+      <c r="H66" s="41">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="42" t="s">
+        <v>51</v>
+      </c>
       <c r="J66" s="35"/>
       <c r="K66" s="35"/>
       <c r="L66" s="35"/>
     </row>
-    <row r="67" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A67" s="51">
-        <v>1</v>
-      </c>
-      <c r="B67" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="51">
-        <v>28</v>
-      </c>
-      <c r="F67" s="51">
-        <f t="shared" ref="F67:F70" si="13">C67*E67</f>
-        <v>0</v>
-      </c>
-      <c r="G67" s="51">
-        <v>32</v>
-      </c>
-      <c r="H67" s="51">
-        <f t="shared" ref="H67:H73" si="14">SUM(G67*C67)</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J67" s="60"/>
-      <c r="K67" s="60"/>
-      <c r="L67" s="60"/>
-    </row>
-    <row r="68" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A68" s="51">
-        <v>2</v>
-      </c>
-      <c r="B68" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G68" s="42">
-        <v>2.5</v>
-      </c>
-      <c r="H68" s="42">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="43" t="s">
-        <v>62</v>
-      </c>
+    <row r="67" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A67" s="61"/>
+      <c r="B67" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" s="61"/>
+      <c r="D67" s="61"/>
+      <c r="E67" s="61"/>
+      <c r="F67" s="61">
+        <f>SUM(F58:F66)</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="61"/>
+      <c r="H67" s="61">
+        <f>SUM(H58:H66)</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="63"/>
+      <c r="J67" s="64"/>
+      <c r="K67" s="64"/>
+      <c r="L67" s="64"/>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:12">
+      <c r="A68" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="41"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="41"/>
+      <c r="I68" s="42"/>
       <c r="J68" s="35"/>
       <c r="K68" s="35"/>
       <c r="L68" s="35"/>
     </row>
-    <row r="69" ht="18" customHeight="1" spans="1:12">
-      <c r="A69" s="51">
-        <v>3</v>
-      </c>
-      <c r="B69" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="44"/>
-      <c r="D69" s="42" t="s">
+    <row r="69" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
+      <c r="A69" s="50">
+        <v>1</v>
+      </c>
+      <c r="B69" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69" s="50">
+        <v>28</v>
+      </c>
+      <c r="F69" s="50">
+        <f t="shared" ref="F69:F74" si="13">C69*E69</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="50">
+        <v>32</v>
+      </c>
+      <c r="H69" s="50">
+        <f t="shared" ref="H69:H76" si="14">SUM(G69*C69)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="J69" s="59"/>
+      <c r="K69" s="59"/>
+      <c r="L69" s="59"/>
+    </row>
+    <row r="70" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
+      <c r="A70" s="50">
+        <v>2</v>
+      </c>
+      <c r="B70" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E69" s="44">
-        <v>95</v>
-      </c>
-      <c r="F69" s="42">
+      <c r="E70" s="41"/>
+      <c r="F70" s="41">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G69" s="44">
-        <v>55</v>
-      </c>
-      <c r="H69" s="42">
+      <c r="G70" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H70" s="41">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I69" s="43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A70" s="51">
-        <v>4</v>
-      </c>
-      <c r="B70" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70" s="42">
-        <v>65</v>
-      </c>
-      <c r="F70" s="42">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G70" s="42">
-        <v>85</v>
-      </c>
-      <c r="H70" s="42">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="43" t="s">
-        <v>80</v>
+      <c r="I70" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="J70" s="35"/>
       <c r="K70" s="35"/>
       <c r="L70" s="35"/>
     </row>
-    <row r="71" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A71" s="51">
-        <v>5</v>
-      </c>
-      <c r="B71" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" s="42">
-        <v>2</v>
-      </c>
-      <c r="F71" s="42">
-        <f t="shared" ref="F71:F74" si="15">C71*E71</f>
-        <v>0</v>
-      </c>
-      <c r="G71" s="42">
-        <v>4</v>
-      </c>
-      <c r="H71" s="42">
+    <row r="71" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A71" s="50">
+        <v>3</v>
+      </c>
+      <c r="B71" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="41"/>
+      <c r="D71" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="41">
+        <v>70</v>
+      </c>
+      <c r="F71" s="41">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="45">
+        <v>25</v>
+      </c>
+      <c r="H71" s="41">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I71" s="43" t="s">
-        <v>40</v>
+      <c r="I71" s="46" t="s">
+        <v>16</v>
       </c>
       <c r="J71" s="35"/>
       <c r="K71" s="35"/>
       <c r="L71" s="35"/>
     </row>
-    <row r="72" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A72" s="51">
+    <row r="72" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A72" s="50">
+        <v>4</v>
+      </c>
+      <c r="B72" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="49"/>
+      <c r="D72" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="50">
+        <v>125</v>
+      </c>
+      <c r="F72" s="50">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="50">
+        <v>65</v>
+      </c>
+      <c r="H72" s="50">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" s="52"/>
+      <c r="K72" s="53"/>
+      <c r="L72" s="53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="1:12">
+      <c r="A73" s="50">
+        <v>5</v>
+      </c>
+      <c r="B73" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="43"/>
+      <c r="D73" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="43">
+        <v>95</v>
+      </c>
+      <c r="F73" s="41">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="43">
+        <v>55</v>
+      </c>
+      <c r="H73" s="41">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="42" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A74" s="50">
         <v>6</v>
       </c>
-      <c r="B72" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" s="42"/>
-      <c r="D72" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E72" s="42">
-        <v>19</v>
-      </c>
-      <c r="F72" s="42">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G72" s="42">
-        <v>13</v>
-      </c>
-      <c r="H72" s="42">
+      <c r="B74" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="41"/>
+      <c r="D74" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="41">
+        <v>65</v>
+      </c>
+      <c r="F74" s="41">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="41">
+        <v>85</v>
+      </c>
+      <c r="H74" s="41">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I72" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J72" s="35"/>
-      <c r="K72" s="35"/>
-      <c r="L72" s="35"/>
-    </row>
-    <row r="73" ht="27" customHeight="1" spans="1:12">
-      <c r="A73" s="51">
-        <v>7</v>
-      </c>
-      <c r="B73" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" s="42">
-        <v>12</v>
-      </c>
-      <c r="F73" s="42">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G73" s="42">
-        <v>7</v>
-      </c>
-      <c r="H73" s="42">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="J73" s="35"/>
-      <c r="K73" s="35"/>
-      <c r="L73" s="35"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" spans="1:12">
-      <c r="A74" s="51">
-        <v>8</v>
-      </c>
-      <c r="B74" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" s="42"/>
-      <c r="D74" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" s="42">
-        <v>12</v>
-      </c>
-      <c r="F74" s="42">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G74" s="42">
-        <v>5</v>
-      </c>
-      <c r="H74" s="42">
-        <f t="shared" ref="H74:H83" si="16">SUM(G74*C74)</f>
-        <v>0</v>
-      </c>
-      <c r="I74" s="43" t="s">
-        <v>51</v>
+      <c r="I74" s="42" t="s">
+        <v>80</v>
       </c>
       <c r="J74" s="35"/>
       <c r="K74" s="35"/>
       <c r="L74" s="35"/>
     </row>
-    <row r="75" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A75" s="62"/>
-      <c r="B75" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="62"/>
-      <c r="D75" s="62"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="62">
-        <f>SUM(F67:F74)</f>
-        <v>0</v>
-      </c>
-      <c r="G75" s="62"/>
-      <c r="H75" s="62">
-        <f>SUM(H67:H74)</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="64"/>
-      <c r="J75" s="65"/>
-      <c r="K75" s="65"/>
-      <c r="L75" s="65"/>
-    </row>
-    <row r="76" ht="18" customHeight="1" spans="1:12">
-      <c r="A76" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="42"/>
-      <c r="H76" s="42"/>
-      <c r="I76" s="43"/>
+    <row r="75" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A75" s="50">
+        <v>7</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C75" s="41"/>
+      <c r="D75" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E75" s="41">
+        <v>2</v>
+      </c>
+      <c r="F75" s="41">
+        <f t="shared" ref="F75:F78" si="15">C75*E75</f>
+        <v>0</v>
+      </c>
+      <c r="G75" s="41">
+        <v>4</v>
+      </c>
+      <c r="H75" s="41">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35"/>
+    </row>
+    <row r="76" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A76" s="50">
+        <v>8</v>
+      </c>
+      <c r="B76" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="41"/>
+      <c r="D76" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="41">
+        <v>19</v>
+      </c>
+      <c r="F76" s="41">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="41">
+        <v>13</v>
+      </c>
+      <c r="H76" s="41">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="42" t="s">
+        <v>42</v>
+      </c>
       <c r="J76" s="35"/>
       <c r="K76" s="35"/>
       <c r="L76" s="35"/>
     </row>
-    <row r="77" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
-      <c r="A77" s="51">
-        <v>1</v>
-      </c>
-      <c r="B77" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="E77" s="51">
-        <v>28</v>
-      </c>
-      <c r="F77" s="51">
-        <f t="shared" ref="F77:F83" si="17">C77*E77</f>
-        <v>0</v>
-      </c>
-      <c r="G77" s="51">
-        <v>32</v>
-      </c>
-      <c r="H77" s="51">
+    <row r="77" ht="27" customHeight="1" spans="1:12">
+      <c r="A77" s="50">
+        <v>9</v>
+      </c>
+      <c r="B77" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="41">
+        <v>12</v>
+      </c>
+      <c r="F77" s="41">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G77" s="41">
+        <v>7</v>
+      </c>
+      <c r="H77" s="41">
+        <f t="shared" ref="H77:H84" si="16">SUM(G77*C77)</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="J77" s="35"/>
+      <c r="K77" s="35"/>
+      <c r="L77" s="35"/>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:12">
+      <c r="A78" s="50">
+        <v>10</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="41">
+        <v>12</v>
+      </c>
+      <c r="F78" s="41">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G78" s="41">
+        <v>5</v>
+      </c>
+      <c r="H78" s="41">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I77" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J77" s="60"/>
-      <c r="K77" s="60"/>
-      <c r="L77" s="60"/>
-    </row>
-    <row r="78" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
-      <c r="A78" s="51">
-        <v>2</v>
-      </c>
-      <c r="B78" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" s="42"/>
-      <c r="D78" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="42">
-        <v>2.5</v>
-      </c>
-      <c r="H78" s="42">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="43" t="s">
-        <v>62</v>
+      <c r="I78" s="42" t="s">
+        <v>51</v>
       </c>
       <c r="J78" s="35"/>
       <c r="K78" s="35"/>
       <c r="L78" s="35"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A79" s="51">
-        <v>3</v>
-      </c>
-      <c r="B79" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" s="42">
-        <v>65</v>
-      </c>
-      <c r="F79" s="42">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G79" s="42">
-        <v>85</v>
-      </c>
-      <c r="H79" s="42">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
-      <c r="L79" s="35"/>
-    </row>
-    <row r="80" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A80" s="51">
-        <v>4</v>
-      </c>
-      <c r="B80" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="C80" s="42"/>
-      <c r="D80" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E80" s="42">
-        <v>2</v>
-      </c>
-      <c r="F80" s="42">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="42">
-        <v>4</v>
-      </c>
-      <c r="H80" s="42">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I80" s="43" t="s">
-        <v>40</v>
-      </c>
+    <row r="79" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A79" s="61"/>
+      <c r="B79" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="61">
+        <f>SUM(F69:F78)</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="61"/>
+      <c r="H79" s="61">
+        <f>SUM(H69:H78)</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="63"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="64"/>
+      <c r="L79" s="64"/>
+    </row>
+    <row r="80" ht="18" customHeight="1" spans="1:12">
+      <c r="A80" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="42"/>
       <c r="J80" s="35"/>
       <c r="K80" s="35"/>
       <c r="L80" s="35"/>
     </row>
-    <row r="81" ht="26.25" customHeight="1" spans="1:12">
-      <c r="A81" s="51">
-        <v>5</v>
-      </c>
-      <c r="B81" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C81" s="42"/>
-      <c r="D81" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E81" s="42">
-        <v>19</v>
-      </c>
-      <c r="F81" s="42">
+    <row r="81" s="6" customFormat="1" ht="24" customHeight="1" spans="1:12">
+      <c r="A81" s="50">
+        <v>1</v>
+      </c>
+      <c r="B81" s="66" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="50"/>
+      <c r="D81" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" s="50">
+        <v>28</v>
+      </c>
+      <c r="F81" s="50">
+        <f t="shared" ref="F81:F84" si="17">C81*E81</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="50">
+        <v>32</v>
+      </c>
+      <c r="H81" s="50">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I81" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="J81" s="59"/>
+      <c r="K81" s="59"/>
+      <c r="L81" s="59"/>
+    </row>
+    <row r="82" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A82" s="50">
+        <v>2</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="41"/>
+      <c r="D82" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="41">
+        <v>70</v>
+      </c>
+      <c r="F82" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G81" s="42">
-        <v>13</v>
-      </c>
-      <c r="H81" s="42">
+      <c r="G82" s="45">
+        <v>25</v>
+      </c>
+      <c r="H82" s="41">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I81" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="J81" s="35"/>
-      <c r="K81" s="35"/>
-      <c r="L81" s="35"/>
-    </row>
-    <row r="82" ht="27" customHeight="1" spans="1:12">
-      <c r="A82" s="51">
-        <v>6</v>
-      </c>
-      <c r="B82" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="C82" s="42"/>
-      <c r="D82" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="42">
-        <v>12</v>
-      </c>
-      <c r="F82" s="42">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G82" s="42">
-        <v>7</v>
-      </c>
-      <c r="H82" s="42">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I82" s="43" t="s">
-        <v>44</v>
+      <c r="I82" s="46" t="s">
+        <v>16</v>
       </c>
       <c r="J82" s="35"/>
       <c r="K82" s="35"/>
       <c r="L82" s="35"/>
     </row>
-    <row r="83" ht="15" customHeight="1" spans="1:12">
-      <c r="A83" s="51">
-        <v>7</v>
-      </c>
-      <c r="B83" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C83" s="42"/>
-      <c r="D83" s="42" t="s">
+    <row r="83" s="4" customFormat="1" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A83" s="50">
+        <v>3</v>
+      </c>
+      <c r="B83" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="49"/>
+      <c r="D83" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" s="50">
+        <v>125</v>
+      </c>
+      <c r="F83" s="50">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="G83" s="50">
+        <v>65</v>
+      </c>
+      <c r="H83" s="50">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" s="52"/>
+      <c r="K83" s="53"/>
+      <c r="L83" s="53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" s="6" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A84" s="50">
+        <v>4</v>
+      </c>
+      <c r="B84" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="43"/>
+      <c r="D84" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E83" s="42">
-        <v>12</v>
-      </c>
-      <c r="F83" s="42">
+      <c r="E84" s="43">
+        <v>95</v>
+      </c>
+      <c r="F84" s="41">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G83" s="42">
+      <c r="G84" s="43">
+        <v>55</v>
+      </c>
+      <c r="H84" s="41">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" s="23"/>
+      <c r="K84" s="23"/>
+      <c r="L84" s="23"/>
+    </row>
+    <row r="85" s="6" customFormat="1" ht="14" customHeight="1" spans="1:12">
+      <c r="A85" s="50">
         <v>5</v>
       </c>
-      <c r="H83" s="42">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I83" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="J83" s="35"/>
-      <c r="K83" s="35"/>
-      <c r="L83" s="35"/>
-    </row>
-    <row r="84" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A84" s="62"/>
-      <c r="B84" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C84" s="62"/>
-      <c r="D84" s="62"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62">
-        <f>SUM(F77:F83)</f>
-        <v>0</v>
-      </c>
-      <c r="G84" s="62"/>
-      <c r="H84" s="62">
-        <f>SUM(H77:H83)</f>
-        <v>0</v>
-      </c>
-      <c r="I84" s="64"/>
-      <c r="J84" s="65"/>
-      <c r="K84" s="65"/>
-      <c r="L84" s="65"/>
-    </row>
-    <row r="85" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A85" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B85" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C85" s="42"/>
-      <c r="D85" s="42"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="42"/>
-      <c r="G85" s="42"/>
-      <c r="H85" s="42"/>
-      <c r="I85" s="43"/>
+      <c r="B85" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="41"/>
+      <c r="F85" s="41">
+        <f t="shared" ref="F85:F90" si="18">C85*E85</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H85" s="41">
+        <f t="shared" ref="H85:H90" si="19">SUM(G85*C85)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="42" t="s">
+        <v>62</v>
+      </c>
       <c r="J85" s="35"/>
       <c r="K85" s="35"/>
       <c r="L85" s="35"/>
     </row>
-    <row r="86" ht="18" customHeight="1" spans="1:12">
-      <c r="A86" s="42" t="s">
+    <row r="86" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A86" s="50">
+        <v>6</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="41">
+        <v>65</v>
+      </c>
+      <c r="F86" s="41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="41">
         <v>85</v>
       </c>
-      <c r="B86" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" s="80"/>
-      <c r="D86" s="80"/>
-      <c r="E86" s="81"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="42"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="43"/>
+      <c r="H86" s="41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="42" t="s">
+        <v>80</v>
+      </c>
       <c r="J86" s="35"/>
       <c r="K86" s="35"/>
       <c r="L86" s="35"/>
     </row>
-    <row r="87" s="6" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A87" s="51">
-        <v>1</v>
-      </c>
-      <c r="B87" s="67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E87" s="51">
-        <v>14</v>
-      </c>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51">
+    <row r="87" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A87" s="50">
+        <v>7</v>
+      </c>
+      <c r="B87" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" s="41"/>
+      <c r="D87" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E87" s="41">
+        <v>2</v>
+      </c>
+      <c r="F87" s="41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="41">
+        <v>4</v>
+      </c>
+      <c r="H87" s="41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="J87" s="35"/>
+      <c r="K87" s="35"/>
+      <c r="L87" s="35"/>
+    </row>
+    <row r="88" ht="26.25" customHeight="1" spans="1:12">
+      <c r="A88" s="50">
+        <v>8</v>
+      </c>
+      <c r="B88" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="41">
+        <v>19</v>
+      </c>
+      <c r="F88" s="41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="41">
+        <v>13</v>
+      </c>
+      <c r="H88" s="41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="J88" s="35"/>
+      <c r="K88" s="35"/>
+      <c r="L88" s="35"/>
+    </row>
+    <row r="89" ht="27" customHeight="1" spans="1:12">
+      <c r="A89" s="50">
+        <v>9</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" s="41"/>
+      <c r="D89" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" s="41">
         <v>12</v>
       </c>
-      <c r="H87" s="51"/>
-      <c r="I87" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="J87" s="60"/>
-      <c r="K87" s="60"/>
-      <c r="L87" s="60"/>
-    </row>
-    <row r="88" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A88" s="51">
-        <v>2</v>
-      </c>
-      <c r="B88" s="67" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" s="51">
-        <v>6</v>
-      </c>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51">
-        <v>11</v>
-      </c>
-      <c r="H88" s="51"/>
-      <c r="I88" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="J88" s="60"/>
-      <c r="K88" s="60"/>
-      <c r="L88" s="60"/>
-    </row>
-    <row r="89" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A89" s="51">
-        <v>3</v>
-      </c>
-      <c r="B89" s="67" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" s="51">
-        <v>6</v>
-      </c>
-      <c r="F89" s="51"/>
-      <c r="G89" s="51">
-        <v>11</v>
-      </c>
-      <c r="H89" s="51"/>
-      <c r="I89" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="J89" s="60"/>
-      <c r="K89" s="60"/>
-      <c r="L89" s="60"/>
-    </row>
-    <row r="90" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A90" s="51">
-        <v>4</v>
-      </c>
-      <c r="B90" s="67" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E90" s="51">
-        <v>6</v>
-      </c>
-      <c r="F90" s="51"/>
-      <c r="G90" s="51">
-        <v>11</v>
-      </c>
-      <c r="H90" s="51"/>
-      <c r="I90" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="J90" s="60"/>
-      <c r="K90" s="60"/>
-      <c r="L90" s="60"/>
-    </row>
-    <row r="91" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A91" s="51">
+      <c r="F89" s="41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="41">
+        <v>7</v>
+      </c>
+      <c r="H89" s="41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="J89" s="35"/>
+      <c r="K89" s="35"/>
+      <c r="L89" s="35"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" spans="1:12">
+      <c r="A90" s="50">
+        <v>10</v>
+      </c>
+      <c r="B90" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90" s="41"/>
+      <c r="D90" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="41">
+        <v>12</v>
+      </c>
+      <c r="F90" s="41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="41">
         <v>5</v>
       </c>
-      <c r="B91" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E91" s="51">
-        <v>6</v>
-      </c>
-      <c r="F91" s="51"/>
-      <c r="G91" s="51">
-        <v>11</v>
-      </c>
-      <c r="H91" s="51"/>
-      <c r="I91" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="J91" s="60"/>
-      <c r="K91" s="60"/>
-      <c r="L91" s="60"/>
-    </row>
-    <row r="92" ht="15" customHeight="1" spans="1:12">
-      <c r="A92" s="42">
-        <v>6</v>
-      </c>
-      <c r="B92" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C92" s="42"/>
-      <c r="D92" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="42">
-        <v>10</v>
-      </c>
-      <c r="F92" s="42"/>
-      <c r="G92" s="42">
-        <v>6</v>
-      </c>
-      <c r="H92" s="42"/>
-      <c r="I92" s="43" t="s">
-        <v>96</v>
-      </c>
+      <c r="H90" s="41">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J90" s="35"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="35"/>
+    </row>
+    <row r="91" s="7" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A91" s="61"/>
+      <c r="B91" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C91" s="61"/>
+      <c r="D91" s="61"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="61">
+        <f>SUM(F81:F90)</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="61"/>
+      <c r="H91" s="61">
+        <f>SUM(H81:H90)</f>
+        <v>0</v>
+      </c>
+      <c r="I91" s="63"/>
+      <c r="J91" s="64"/>
+      <c r="K91" s="64"/>
+      <c r="L91" s="64"/>
+    </row>
+    <row r="92" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A92" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="41"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="41"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
+      <c r="H92" s="41"/>
+      <c r="I92" s="42"/>
       <c r="J92" s="35"/>
       <c r="K92" s="35"/>
       <c r="L92" s="35"/>
     </row>
-    <row r="93" ht="15" customHeight="1" spans="1:12">
-      <c r="A93" s="42">
-        <v>7</v>
-      </c>
-      <c r="B93" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C93" s="42"/>
-      <c r="D93" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E93" s="42">
-        <v>75</v>
-      </c>
-      <c r="F93" s="42"/>
-      <c r="G93" s="42">
-        <v>45</v>
-      </c>
-      <c r="H93" s="46"/>
-      <c r="I93" s="43" t="s">
-        <v>98</v>
-      </c>
+    <row r="93" ht="18" customHeight="1" spans="1:12">
+      <c r="A93" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" s="79"/>
+      <c r="D93" s="79"/>
+      <c r="E93" s="80"/>
+      <c r="F93" s="41"/>
+      <c r="G93" s="41"/>
+      <c r="H93" s="41"/>
+      <c r="I93" s="42"/>
       <c r="J93" s="35"/>
       <c r="K93" s="35"/>
       <c r="L93" s="35"/>
     </row>
-    <row r="94" ht="15" customHeight="1" spans="1:12">
-      <c r="A94" s="42">
-        <v>8</v>
-      </c>
-      <c r="B94" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="C94" s="42"/>
-      <c r="D94" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="E94" s="42">
+    <row r="94" s="6" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
+      <c r="A94" s="50">
+        <v>1</v>
+      </c>
+      <c r="B94" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="C94" s="50"/>
+      <c r="D94" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="50">
+        <v>14</v>
+      </c>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50">
+        <v>12</v>
+      </c>
+      <c r="H94" s="50"/>
+      <c r="I94" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="J94" s="59"/>
+      <c r="K94" s="59"/>
+      <c r="L94" s="59"/>
+    </row>
+    <row r="95" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A95" s="50">
         <v>2</v>
       </c>
-      <c r="F94" s="42"/>
-      <c r="G94" s="42">
+      <c r="B95" s="66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" s="50"/>
+      <c r="D95" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" s="50">
+        <v>6</v>
+      </c>
+      <c r="F95" s="50"/>
+      <c r="G95" s="50">
+        <v>11</v>
+      </c>
+      <c r="H95" s="50"/>
+      <c r="I95" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="J95" s="59"/>
+      <c r="K95" s="59"/>
+      <c r="L95" s="59"/>
+    </row>
+    <row r="96" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A96" s="50">
+        <v>3</v>
+      </c>
+      <c r="B96" s="66" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" s="50"/>
+      <c r="D96" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" s="50">
+        <v>6</v>
+      </c>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50">
+        <v>11</v>
+      </c>
+      <c r="H96" s="50"/>
+      <c r="I96" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="J96" s="59"/>
+      <c r="K96" s="59"/>
+      <c r="L96" s="59"/>
+    </row>
+    <row r="97" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A97" s="50">
         <v>4</v>
       </c>
-      <c r="H94" s="42"/>
-      <c r="I94" s="43" t="s">
-        <v>101</v>
-      </c>
-      <c r="J94" s="35"/>
-      <c r="K94" s="35"/>
-      <c r="L94" s="35"/>
-    </row>
-    <row r="95" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A95" s="51">
-        <v>9</v>
-      </c>
-      <c r="B95" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51" t="s">
+      <c r="B97" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="50"/>
+      <c r="D97" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="51">
-        <v>18</v>
-      </c>
-      <c r="F95" s="51"/>
-      <c r="G95" s="51">
-        <v>13</v>
-      </c>
-      <c r="H95" s="51"/>
-      <c r="I95" s="82" t="s">
-        <v>103</v>
-      </c>
-      <c r="J95" s="60"/>
-      <c r="K95" s="60"/>
-      <c r="L95" s="60"/>
-    </row>
-    <row r="96" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A96" s="51">
+      <c r="E97" s="50">
+        <v>6</v>
+      </c>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50">
+        <v>11</v>
+      </c>
+      <c r="H97" s="50"/>
+      <c r="I97" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="J97" s="59"/>
+      <c r="K97" s="59"/>
+      <c r="L97" s="59"/>
+    </row>
+    <row r="98" s="6" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A98" s="50">
+        <v>5</v>
+      </c>
+      <c r="B98" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C98" s="50"/>
+      <c r="D98" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="50">
+        <v>6</v>
+      </c>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50">
+        <v>11</v>
+      </c>
+      <c r="H98" s="50"/>
+      <c r="I98" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="J98" s="59"/>
+      <c r="K98" s="59"/>
+      <c r="L98" s="59"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" spans="1:12">
+      <c r="A99" s="41">
+        <v>6</v>
+      </c>
+      <c r="B99" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="41">
         <v>10</v>
       </c>
-      <c r="B96" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" s="51">
-        <v>25</v>
-      </c>
-      <c r="F96" s="51"/>
-      <c r="G96" s="51">
-        <v>15</v>
-      </c>
-      <c r="H96" s="83"/>
-      <c r="I96" s="82" t="s">
-        <v>105</v>
-      </c>
-      <c r="J96" s="60"/>
-      <c r="K96" s="60"/>
-      <c r="L96" s="60"/>
-    </row>
-    <row r="97" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A97" s="51">
-        <v>11</v>
-      </c>
-      <c r="B97" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E97" s="51">
-        <v>55</v>
-      </c>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51">
-        <v>20</v>
-      </c>
-      <c r="H97" s="83"/>
-      <c r="I97" s="82" t="s">
-        <v>107</v>
-      </c>
-      <c r="J97" s="60"/>
-      <c r="K97" s="60"/>
-      <c r="L97" s="60"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A98" s="42">
-        <v>12</v>
-      </c>
-      <c r="B98" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C98" s="42"/>
-      <c r="D98" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E98" s="42">
-        <v>150</v>
-      </c>
-      <c r="F98" s="42"/>
-      <c r="G98" s="42">
-        <v>180</v>
-      </c>
-      <c r="H98" s="42"/>
-      <c r="I98" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="J98" s="35"/>
-      <c r="K98" s="35"/>
-      <c r="L98" s="35"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A99" s="42">
-        <v>13</v>
-      </c>
-      <c r="B99" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="C99" s="42"/>
-      <c r="D99" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E99" s="42">
-        <v>240</v>
-      </c>
-      <c r="F99" s="42"/>
-      <c r="G99" s="42">
-        <v>160</v>
-      </c>
-      <c r="H99" s="42"/>
-      <c r="I99" s="43" t="s">
-        <v>109</v>
+      <c r="F99" s="41"/>
+      <c r="G99" s="41">
+        <v>6</v>
+      </c>
+      <c r="H99" s="41"/>
+      <c r="I99" s="42" t="s">
+        <v>96</v>
       </c>
       <c r="J99" s="35"/>
       <c r="K99" s="35"/>
       <c r="L99" s="35"/>
     </row>
-    <row r="100" ht="22.5" customHeight="1" spans="1:12">
-      <c r="A100" s="42">
-        <v>14</v>
-      </c>
-      <c r="B100" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" s="42"/>
-      <c r="D100" s="42" t="s">
+    <row r="100" ht="15" customHeight="1" spans="1:12">
+      <c r="A100" s="41">
+        <v>7</v>
+      </c>
+      <c r="B100" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="41"/>
+      <c r="D100" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E100" s="42">
-        <v>120</v>
-      </c>
-      <c r="F100" s="42"/>
-      <c r="G100" s="42">
-        <v>380</v>
-      </c>
-      <c r="H100" s="42"/>
-      <c r="I100" s="43" t="s">
-        <v>112</v>
+      <c r="E100" s="41">
+        <v>75</v>
+      </c>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41">
+        <v>45</v>
+      </c>
+      <c r="H100" s="45"/>
+      <c r="I100" s="42" t="s">
+        <v>98</v>
       </c>
       <c r="J100" s="35"/>
       <c r="K100" s="35"/>
       <c r="L100" s="35"/>
     </row>
-    <row r="101" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A101" s="42">
+    <row r="101" ht="15" customHeight="1" spans="1:12">
+      <c r="A101" s="41">
+        <v>8</v>
+      </c>
+      <c r="B101" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" s="41"/>
+      <c r="D101" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="E101" s="41">
+        <v>2</v>
+      </c>
+      <c r="F101" s="41"/>
+      <c r="G101" s="41">
+        <v>4</v>
+      </c>
+      <c r="H101" s="41"/>
+      <c r="I101" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="J101" s="35"/>
+      <c r="K101" s="35"/>
+      <c r="L101" s="35"/>
+    </row>
+    <row r="102" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
+      <c r="A102" s="50">
+        <v>9</v>
+      </c>
+      <c r="B102" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C102" s="50"/>
+      <c r="D102" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B101" s="68" t="s">
-        <v>113</v>
-      </c>
-      <c r="C101" s="84"/>
-      <c r="D101" s="42" t="s">
+      <c r="E102" s="50">
         <v>18</v>
       </c>
-      <c r="E101" s="84"/>
-      <c r="F101" s="42"/>
-      <c r="G101" s="42">
-        <v>5</v>
-      </c>
-      <c r="H101" s="46"/>
-      <c r="I101" s="85" t="s">
-        <v>114</v>
-      </c>
-      <c r="J101" s="35"/>
-      <c r="K101" s="86"/>
-      <c r="L101" s="86"/>
-    </row>
-    <row r="102" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A102" s="62"/>
-      <c r="B102" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C102" s="62"/>
-      <c r="D102" s="62"/>
-      <c r="E102" s="62"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="62"/>
-      <c r="H102" s="62"/>
-      <c r="I102" s="64"/>
-      <c r="J102" s="65"/>
-      <c r="K102" s="65"/>
-      <c r="L102" s="65"/>
-    </row>
-    <row r="103" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A103" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="B103" s="76" t="s">
-        <v>116</v>
-      </c>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
-      <c r="E103" s="78"/>
-      <c r="F103" s="42"/>
-      <c r="G103" s="42"/>
-      <c r="H103" s="42"/>
-      <c r="I103" s="43"/>
-      <c r="J103" s="35"/>
-      <c r="K103" s="35"/>
-      <c r="L103" s="35"/>
-    </row>
-    <row r="104" s="6" customFormat="1" ht="24.75" customHeight="1" spans="1:12">
-      <c r="A104" s="51">
-        <v>1</v>
-      </c>
-      <c r="B104" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51" t="s">
+      <c r="F102" s="50"/>
+      <c r="G102" s="50">
+        <v>13</v>
+      </c>
+      <c r="H102" s="50"/>
+      <c r="I102" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="J102" s="59"/>
+      <c r="K102" s="59"/>
+      <c r="L102" s="59"/>
+    </row>
+    <row r="103" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
+      <c r="A103" s="50">
+        <v>10</v>
+      </c>
+      <c r="B103" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103" s="50"/>
+      <c r="D103" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="51">
-        <v>36</v>
-      </c>
-      <c r="F104" s="51"/>
-      <c r="G104" s="51">
-        <v>33</v>
-      </c>
-      <c r="H104" s="51"/>
-      <c r="I104" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="J104" s="60"/>
-      <c r="K104" s="60"/>
-      <c r="L104" s="60"/>
-    </row>
-    <row r="105" ht="25.5" customHeight="1" spans="1:12">
-      <c r="A105" s="42">
-        <v>2</v>
-      </c>
-      <c r="B105" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42" t="s">
+      <c r="E103" s="50">
+        <v>25</v>
+      </c>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50">
         <v>15</v>
       </c>
-      <c r="E105" s="42">
-        <v>38</v>
-      </c>
-      <c r="F105" s="42"/>
-      <c r="G105" s="42">
-        <v>40</v>
-      </c>
-      <c r="H105" s="42"/>
-      <c r="I105" s="43" t="s">
-        <v>120</v>
+      <c r="H103" s="82"/>
+      <c r="I103" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="J103" s="59"/>
+      <c r="K103" s="59"/>
+      <c r="L103" s="59"/>
+    </row>
+    <row r="104" s="6" customFormat="1" ht="22.5" customHeight="1" spans="1:12">
+      <c r="A104" s="50">
+        <v>11</v>
+      </c>
+      <c r="B104" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="50"/>
+      <c r="D104" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="50">
+        <v>55</v>
+      </c>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50">
+        <v>20</v>
+      </c>
+      <c r="H104" s="82"/>
+      <c r="I104" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="J104" s="59"/>
+      <c r="K104" s="59"/>
+      <c r="L104" s="59"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A105" s="41">
+        <v>12</v>
+      </c>
+      <c r="B105" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="C105" s="41"/>
+      <c r="D105" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E105" s="41">
+        <v>150</v>
+      </c>
+      <c r="F105" s="41"/>
+      <c r="G105" s="41">
+        <v>180</v>
+      </c>
+      <c r="H105" s="41"/>
+      <c r="I105" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="J105" s="35"/>
       <c r="K105" s="35"/>
       <c r="L105" s="35"/>
     </row>
-    <row r="106" ht="24.5" customHeight="1" spans="1:12">
-      <c r="A106" s="42">
-        <v>3</v>
-      </c>
-      <c r="B106" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C106" s="42"/>
-      <c r="D106" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" s="42">
-        <v>48</v>
-      </c>
-      <c r="F106" s="42"/>
-      <c r="G106" s="42">
-        <v>70</v>
-      </c>
-      <c r="H106" s="42"/>
-      <c r="I106" s="43" t="s">
-        <v>120</v>
+    <row r="106" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A106" s="41">
+        <v>13</v>
+      </c>
+      <c r="B106" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" s="41"/>
+      <c r="D106" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E106" s="41">
+        <v>240</v>
+      </c>
+      <c r="F106" s="41"/>
+      <c r="G106" s="41">
+        <v>160</v>
+      </c>
+      <c r="H106" s="41"/>
+      <c r="I106" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="J106" s="35"/>
       <c r="K106" s="35"/>
       <c r="L106" s="35"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:12">
-      <c r="A107" s="42">
-        <v>4</v>
-      </c>
-      <c r="B107" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C107" s="42"/>
-      <c r="D107" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E107" s="42">
-        <v>20</v>
-      </c>
-      <c r="F107" s="42"/>
-      <c r="G107" s="42">
-        <v>15</v>
-      </c>
-      <c r="H107" s="42"/>
-      <c r="I107" s="43" t="s">
-        <v>123</v>
+    <row r="107" ht="22.5" customHeight="1" spans="1:12">
+      <c r="A107" s="41">
+        <v>14</v>
+      </c>
+      <c r="B107" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E107" s="41">
+        <v>120</v>
+      </c>
+      <c r="F107" s="41"/>
+      <c r="G107" s="41">
+        <v>380</v>
+      </c>
+      <c r="H107" s="41"/>
+      <c r="I107" s="42" t="s">
+        <v>112</v>
       </c>
       <c r="J107" s="35"/>
       <c r="K107" s="35"/>
       <c r="L107" s="35"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:12">
-      <c r="A108" s="42">
+    <row r="108" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A108" s="41">
+        <v>15</v>
+      </c>
+      <c r="B108" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" s="83"/>
+      <c r="D108" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="83"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="41">
         <v>5</v>
       </c>
-      <c r="B108" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="C108" s="42"/>
-      <c r="D108" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="E108" s="42">
-        <v>135</v>
-      </c>
-      <c r="F108" s="42"/>
-      <c r="G108" s="42">
-        <v>35</v>
-      </c>
-      <c r="H108" s="42"/>
-      <c r="I108" s="43" t="s">
-        <v>125</v>
+      <c r="H108" s="45"/>
+      <c r="I108" s="84" t="s">
+        <v>114</v>
       </c>
       <c r="J108" s="35"/>
-      <c r="K108" s="35"/>
-      <c r="L108" s="35"/>
-    </row>
-    <row r="109" s="7" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A109" s="62"/>
-      <c r="B109" s="63" t="s">
+      <c r="K108" s="85"/>
+      <c r="L108" s="85"/>
+    </row>
+    <row r="109" s="7" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A109" s="61"/>
+      <c r="B109" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="C109" s="62"/>
-      <c r="D109" s="62"/>
-      <c r="E109" s="62"/>
-      <c r="F109" s="62"/>
-      <c r="G109" s="62"/>
-      <c r="H109" s="62"/>
-      <c r="I109" s="64"/>
-      <c r="J109" s="65"/>
-      <c r="K109" s="65"/>
-      <c r="L109" s="65"/>
-    </row>
-    <row r="110" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A110" s="87" t="s">
-        <v>126</v>
-      </c>
-      <c r="B110" s="41" t="s">
-        <v>127</v>
-      </c>
-      <c r="C110" s="42"/>
-      <c r="D110" s="42"/>
-      <c r="E110" s="42"/>
-      <c r="F110" s="42"/>
-      <c r="G110" s="42"/>
-      <c r="H110" s="42"/>
-      <c r="I110" s="43"/>
+      <c r="C109" s="61"/>
+      <c r="D109" s="61"/>
+      <c r="E109" s="61"/>
+      <c r="F109" s="61"/>
+      <c r="G109" s="61"/>
+      <c r="H109" s="61"/>
+      <c r="I109" s="63"/>
+      <c r="J109" s="64"/>
+      <c r="K109" s="64"/>
+      <c r="L109" s="64"/>
+    </row>
+    <row r="110" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A110" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B110" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C110" s="76"/>
+      <c r="D110" s="76"/>
+      <c r="E110" s="77"/>
+      <c r="F110" s="41"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="41"/>
+      <c r="I110" s="42"/>
       <c r="J110" s="35"/>
       <c r="K110" s="35"/>
       <c r="L110" s="35"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A111" s="42">
+    <row r="111" s="6" customFormat="1" ht="24.75" customHeight="1" spans="1:12">
+      <c r="A111" s="50">
         <v>1</v>
       </c>
-      <c r="B111" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="C111" s="42"/>
-      <c r="D111" s="42" t="s">
+      <c r="B111" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="C111" s="50"/>
+      <c r="D111" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="42">
-        <v>22</v>
-      </c>
-      <c r="F111" s="42">
-        <f>C111*E111</f>
-        <v>0</v>
-      </c>
-      <c r="G111" s="42">
-        <v>25</v>
-      </c>
-      <c r="H111" s="42">
-        <f>SUM(G111*C111)</f>
-        <v>0</v>
-      </c>
-      <c r="I111" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="J111" s="35"/>
-      <c r="K111" s="35"/>
-      <c r="L111" s="35"/>
-    </row>
-    <row r="112" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A112" s="42">
+      <c r="E111" s="50">
+        <v>36</v>
+      </c>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50">
+        <v>33</v>
+      </c>
+      <c r="H111" s="50"/>
+      <c r="I111" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="J111" s="59"/>
+      <c r="K111" s="59"/>
+      <c r="L111" s="59"/>
+    </row>
+    <row r="112" ht="25.5" customHeight="1" spans="1:12">
+      <c r="A112" s="41">
         <v>2</v>
       </c>
-      <c r="B112" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="C112" s="42"/>
-      <c r="D112" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E112" s="42">
-        <v>160</v>
-      </c>
-      <c r="F112" s="42">
-        <f t="shared" ref="F112:F131" si="18">C112*E112</f>
-        <v>0</v>
-      </c>
-      <c r="G112" s="42">
-        <v>125</v>
-      </c>
-      <c r="H112" s="42">
-        <f t="shared" ref="H112:H131" si="19">SUM(G112*C112)</f>
-        <v>0</v>
-      </c>
-      <c r="I112" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="J112" s="88"/>
-      <c r="K112" s="88"/>
-      <c r="L112" s="88"/>
-    </row>
-    <row r="113" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A113" s="42">
+      <c r="B112" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" s="41"/>
+      <c r="D112" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="41">
+        <v>38</v>
+      </c>
+      <c r="F112" s="41"/>
+      <c r="G112" s="41">
+        <v>40</v>
+      </c>
+      <c r="H112" s="41"/>
+      <c r="I112" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="J112" s="35"/>
+      <c r="K112" s="35"/>
+      <c r="L112" s="35"/>
+    </row>
+    <row r="113" ht="24.5" customHeight="1" spans="1:12">
+      <c r="A113" s="41">
         <v>3</v>
       </c>
-      <c r="B113" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="C113" s="42"/>
-      <c r="D113" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E113" s="42">
-        <v>95</v>
-      </c>
-      <c r="F113" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G113" s="42">
-        <v>75</v>
-      </c>
-      <c r="H113" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="43" t="s">
-        <v>133</v>
+      <c r="B113" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" s="41">
+        <v>48</v>
+      </c>
+      <c r="F113" s="41"/>
+      <c r="G113" s="41">
+        <v>70</v>
+      </c>
+      <c r="H113" s="41"/>
+      <c r="I113" s="42" t="s">
+        <v>120</v>
       </c>
       <c r="J113" s="35"/>
       <c r="K113" s="35"/>
       <c r="L113" s="35"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A114" s="42">
+    <row r="114" ht="15" customHeight="1" spans="1:12">
+      <c r="A114" s="41">
         <v>4</v>
       </c>
-      <c r="B114" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C114" s="42"/>
-      <c r="D114" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E114" s="42">
-        <v>120</v>
-      </c>
-      <c r="F114" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G114" s="42">
-        <v>90</v>
-      </c>
-      <c r="H114" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="43" t="s">
-        <v>136</v>
+      <c r="B114" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114" s="41"/>
+      <c r="D114" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="41">
+        <v>20</v>
+      </c>
+      <c r="F114" s="41"/>
+      <c r="G114" s="41">
+        <v>15</v>
+      </c>
+      <c r="H114" s="41"/>
+      <c r="I114" s="42" t="s">
+        <v>123</v>
       </c>
       <c r="J114" s="35"/>
       <c r="K114" s="35"/>
       <c r="L114" s="35"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A115" s="42">
+    <row r="115" ht="15" customHeight="1" spans="1:12">
+      <c r="A115" s="41">
         <v>5</v>
       </c>
-      <c r="B115" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="C115" s="42"/>
-      <c r="D115" s="42" t="s">
+      <c r="B115" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C115" s="41"/>
+      <c r="D115" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="E115" s="41">
         <v>135</v>
       </c>
-      <c r="E115" s="42">
-        <v>150</v>
-      </c>
-      <c r="F115" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G115" s="42">
-        <v>100</v>
-      </c>
-      <c r="H115" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="43" t="s">
-        <v>136</v>
+      <c r="F115" s="41"/>
+      <c r="G115" s="41">
+        <v>35</v>
+      </c>
+      <c r="H115" s="41"/>
+      <c r="I115" s="42" t="s">
+        <v>125</v>
       </c>
       <c r="J115" s="35"/>
       <c r="K115" s="35"/>
       <c r="L115" s="35"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A116" s="42">
-        <v>6</v>
-      </c>
-      <c r="B116" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="C116" s="42"/>
-      <c r="D116" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E116" s="42">
-        <v>120</v>
-      </c>
-      <c r="F116" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G116" s="42">
-        <v>320</v>
-      </c>
-      <c r="H116" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="J116" s="35"/>
-      <c r="K116" s="35"/>
-      <c r="L116" s="35"/>
-    </row>
-    <row r="117" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A117" s="42">
-        <v>7</v>
-      </c>
-      <c r="B117" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="C117" s="42"/>
-      <c r="D117" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E117" s="42">
-        <v>10</v>
-      </c>
-      <c r="F117" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G117" s="42">
-        <v>15</v>
-      </c>
-      <c r="H117" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="43" t="s">
-        <v>141</v>
-      </c>
+    <row r="116" s="7" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
+      <c r="A116" s="61"/>
+      <c r="B116" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C116" s="61"/>
+      <c r="D116" s="61"/>
+      <c r="E116" s="61"/>
+      <c r="F116" s="61"/>
+      <c r="G116" s="61"/>
+      <c r="H116" s="61"/>
+      <c r="I116" s="63"/>
+      <c r="J116" s="64"/>
+      <c r="K116" s="64"/>
+      <c r="L116" s="64"/>
+    </row>
+    <row r="117" ht="17.15" customHeight="1" spans="1:12">
+      <c r="A117" s="86" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="41"/>
+      <c r="I117" s="42"/>
       <c r="J117" s="35"/>
       <c r="K117" s="35"/>
       <c r="L117" s="35"/>
     </row>
-    <row r="118" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A118" s="42">
-        <v>8</v>
-      </c>
-      <c r="B118" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="C118" s="42"/>
-      <c r="D118" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E118" s="42">
-        <v>280</v>
-      </c>
-      <c r="F118" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G118" s="42">
-        <v>380</v>
-      </c>
-      <c r="H118" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="J118" s="89"/>
-      <c r="K118" s="89"/>
-      <c r="L118" s="89"/>
-    </row>
-    <row r="119" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A119" s="42">
-        <v>9</v>
-      </c>
-      <c r="B119" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C119" s="42"/>
-      <c r="D119" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E119" s="42">
-        <v>105</v>
-      </c>
-      <c r="F119" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G119" s="42">
-        <v>70</v>
-      </c>
-      <c r="H119" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="J119" s="89"/>
-      <c r="K119" s="89"/>
-      <c r="L119" s="89"/>
-    </row>
-    <row r="120" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A120" s="42">
-        <v>10</v>
-      </c>
-      <c r="B120" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="C120" s="51"/>
-      <c r="D120" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E120" s="42">
+    <row r="118" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A118" s="41">
+        <v>1</v>
+      </c>
+      <c r="B118" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="41"/>
+      <c r="D118" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" s="41">
+        <v>22</v>
+      </c>
+      <c r="F118" s="41">
+        <f>C118*E118</f>
+        <v>0</v>
+      </c>
+      <c r="G118" s="41">
         <v>25</v>
       </c>
-      <c r="F120" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G120" s="83">
-        <v>45</v>
-      </c>
-      <c r="H120" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="J120" s="60"/>
-      <c r="K120" s="60"/>
-      <c r="L120" s="60"/>
-    </row>
-    <row r="121" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A121" s="42">
-        <v>11</v>
-      </c>
-      <c r="B121" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="C121" s="42"/>
-      <c r="D121" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E121" s="42">
-        <v>45</v>
-      </c>
-      <c r="F121" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G121" s="42">
+      <c r="H118" s="41">
+        <f>SUM(G118*C118)</f>
+        <v>0</v>
+      </c>
+      <c r="I118" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="J118" s="35"/>
+      <c r="K118" s="35"/>
+      <c r="L118" s="35"/>
+    </row>
+    <row r="119" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A119" s="41">
+        <v>2</v>
+      </c>
+      <c r="B119" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C119" s="41"/>
+      <c r="D119" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" s="41">
+        <v>160</v>
+      </c>
+      <c r="F119" s="41">
+        <f t="shared" ref="F119:F138" si="20">C119*E119</f>
+        <v>0</v>
+      </c>
+      <c r="G119" s="41">
+        <v>125</v>
+      </c>
+      <c r="H119" s="41">
+        <f t="shared" ref="H119:H138" si="21">SUM(G119*C119)</f>
+        <v>0</v>
+      </c>
+      <c r="I119" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="J119" s="87"/>
+      <c r="K119" s="87"/>
+      <c r="L119" s="87"/>
+    </row>
+    <row r="120" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A120" s="41">
+        <v>3</v>
+      </c>
+      <c r="B120" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="C120" s="41"/>
+      <c r="D120" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120" s="41">
+        <v>95</v>
+      </c>
+      <c r="F120" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="41">
+        <v>75</v>
+      </c>
+      <c r="H120" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I120" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="J120" s="35"/>
+      <c r="K120" s="35"/>
+      <c r="L120" s="35"/>
+    </row>
+    <row r="121" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A121" s="41">
+        <v>4</v>
+      </c>
+      <c r="B121" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="C121" s="41"/>
+      <c r="D121" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E121" s="41">
+        <v>120</v>
+      </c>
+      <c r="F121" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G121" s="41">
         <v>90</v>
       </c>
-      <c r="H121" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="43" t="s">
-        <v>149</v>
+      <c r="H121" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="42" t="s">
+        <v>136</v>
       </c>
       <c r="J121" s="35"/>
       <c r="K121" s="35"/>
       <c r="L121" s="35"/>
     </row>
-    <row r="122" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A122" s="42">
-        <v>12</v>
-      </c>
-      <c r="B122" s="45" t="s">
+    <row r="122" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A122" s="41">
+        <v>5</v>
+      </c>
+      <c r="B122" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" s="41"/>
+      <c r="D122" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E122" s="41">
         <v>150</v>
       </c>
-      <c r="C122" s="42"/>
-      <c r="D122" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="42">
-        <v>65</v>
-      </c>
-      <c r="F122" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G122" s="42">
+      <c r="F122" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G122" s="41">
         <v>100</v>
       </c>
-      <c r="H122" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="J122"/>
-      <c r="K122"/>
-      <c r="L122"/>
-    </row>
-    <row r="123" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A123" s="42">
-        <v>13</v>
-      </c>
-      <c r="B123" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C123" s="42"/>
-      <c r="D123" s="51" t="s">
+      <c r="H122" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I122" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="J122" s="35"/>
+      <c r="K122" s="35"/>
+      <c r="L122" s="35"/>
+    </row>
+    <row r="123" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A123" s="41">
+        <v>6</v>
+      </c>
+      <c r="B123" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="41"/>
+      <c r="D123" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E123" s="42">
-        <v>180</v>
-      </c>
-      <c r="F123" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G123" s="42">
+      <c r="E123" s="41">
+        <v>120</v>
+      </c>
+      <c r="F123" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="41">
         <v>320</v>
       </c>
-      <c r="H123" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="43" t="s">
-        <v>153</v>
+      <c r="H123" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="42" t="s">
+        <v>139</v>
       </c>
       <c r="J123" s="35"/>
       <c r="K123" s="35"/>
       <c r="L123" s="35"/>
     </row>
-    <row r="124" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A124" s="42">
-        <v>14</v>
-      </c>
-      <c r="B124" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="C124" s="42"/>
-      <c r="D124" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="E124" s="42">
-        <v>4</v>
-      </c>
-      <c r="F124" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G124" s="42">
-        <v>2.5</v>
-      </c>
-      <c r="H124" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="43" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="125" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A125" s="42">
+    <row r="124" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A124" s="41">
+        <v>7</v>
+      </c>
+      <c r="B124" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124" s="41"/>
+      <c r="D124" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E124" s="41">
+        <v>10</v>
+      </c>
+      <c r="F124" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G124" s="41">
         <v>15</v>
       </c>
-      <c r="B125" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C125" s="42"/>
-      <c r="D125" s="51" t="s">
+      <c r="H124" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="J124" s="35"/>
+      <c r="K124" s="35"/>
+      <c r="L124" s="35"/>
+    </row>
+    <row r="125" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A125" s="41">
+        <v>8</v>
+      </c>
+      <c r="B125" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C125" s="41"/>
+      <c r="D125" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E125" s="41">
+        <v>280</v>
+      </c>
+      <c r="F125" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G125" s="41">
+        <v>380</v>
+      </c>
+      <c r="H125" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I125" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="J125" s="88"/>
+      <c r="K125" s="88"/>
+      <c r="L125" s="88"/>
+    </row>
+    <row r="126" s="12" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A126" s="41">
+        <v>9</v>
+      </c>
+      <c r="B126" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C126" s="41"/>
+      <c r="D126" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E126" s="41">
+        <v>105</v>
+      </c>
+      <c r="F126" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G126" s="41">
+        <v>70</v>
+      </c>
+      <c r="H126" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I126" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="J126" s="88"/>
+      <c r="K126" s="88"/>
+      <c r="L126" s="88"/>
+    </row>
+    <row r="127" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A127" s="41">
+        <v>10</v>
+      </c>
+      <c r="B127" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C127" s="50"/>
+      <c r="D127" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E127" s="41">
+        <v>25</v>
+      </c>
+      <c r="F127" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="82">
+        <v>45</v>
+      </c>
+      <c r="H127" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="J127" s="59"/>
+      <c r="K127" s="59"/>
+      <c r="L127" s="59"/>
+    </row>
+    <row r="128" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A128" s="41">
+        <v>11</v>
+      </c>
+      <c r="B128" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="C128" s="41"/>
+      <c r="D128" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E128" s="41">
+        <v>45</v>
+      </c>
+      <c r="F128" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G128" s="41">
+        <v>90</v>
+      </c>
+      <c r="H128" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I128" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="J128" s="35"/>
+      <c r="K128" s="35"/>
+      <c r="L128" s="35"/>
+    </row>
+    <row r="129" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="A129" s="41">
+        <v>12</v>
+      </c>
+      <c r="B129" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="C129" s="41"/>
+      <c r="D129" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="42">
-        <v>25</v>
-      </c>
-      <c r="F125" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G125" s="42">
-        <v>48</v>
-      </c>
-      <c r="H125" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I125" s="43" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="126" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A126" s="42">
-        <v>16</v>
-      </c>
-      <c r="B126" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C126" s="42"/>
-      <c r="D126" s="42" t="s">
+      <c r="E129" s="41">
+        <v>65</v>
+      </c>
+      <c r="F129" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G129" s="41">
+        <v>100</v>
+      </c>
+      <c r="H129" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="J129"/>
+      <c r="K129"/>
+      <c r="L129"/>
+    </row>
+    <row r="130" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A130" s="41">
+        <v>13</v>
+      </c>
+      <c r="B130" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C130" s="41"/>
+      <c r="D130" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="E126" s="42">
-        <v>160</v>
-      </c>
-      <c r="F126" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G126" s="42">
-        <v>125</v>
-      </c>
-      <c r="H126" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I126" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="J126" s="35"/>
-      <c r="K126" s="35"/>
-      <c r="L126" s="35"/>
-    </row>
-    <row r="127" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A127" s="42">
-        <v>17</v>
-      </c>
-      <c r="B127" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="C127" s="42"/>
-      <c r="D127" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" s="42">
-        <v>0</v>
-      </c>
-      <c r="F127" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G127" s="42">
-        <v>75</v>
-      </c>
-      <c r="H127" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="J127" s="35"/>
-      <c r="K127" s="35"/>
-      <c r="L127" s="35"/>
-    </row>
-    <row r="128" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A128" s="42">
-        <v>18</v>
-      </c>
-      <c r="B128" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="C128" s="42"/>
-      <c r="D128" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E128" s="42"/>
-      <c r="F128" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G128" s="42">
-        <v>5</v>
-      </c>
-      <c r="H128" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I128" s="43" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="129" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A129" s="42">
-        <v>19</v>
-      </c>
-      <c r="B129" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="C129" s="42"/>
-      <c r="D129" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E129" s="42">
-        <v>80</v>
-      </c>
-      <c r="F129" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G129" s="42">
-        <v>75</v>
-      </c>
-      <c r="H129" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I129" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="J129" s="35"/>
-      <c r="K129" s="35"/>
-      <c r="L129" s="35"/>
-    </row>
-    <row r="130" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A130" s="42">
-        <v>20</v>
-      </c>
-      <c r="B130" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="C130" s="42"/>
-      <c r="D130" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" s="42">
-        <v>15</v>
-      </c>
-      <c r="F130" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G130" s="42">
-        <v>13</v>
-      </c>
-      <c r="H130" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I130" s="43" t="s">
-        <v>168</v>
+      <c r="E130" s="41">
+        <v>180</v>
+      </c>
+      <c r="F130" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G130" s="41">
+        <v>320</v>
+      </c>
+      <c r="H130" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="42" t="s">
+        <v>153</v>
       </c>
       <c r="J130" s="35"/>
       <c r="K130" s="35"/>
       <c r="L130" s="35"/>
     </row>
-    <row r="131" s="8" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A131" s="42">
-        <v>21</v>
-      </c>
-      <c r="B131" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C131" s="42"/>
-      <c r="D131" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E131" s="42">
-        <v>2</v>
-      </c>
-      <c r="F131" s="42">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="G131" s="42">
-        <v>6</v>
-      </c>
-      <c r="H131" s="42">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I131" s="43" t="s">
-        <v>170</v>
-      </c>
-      <c r="J131" s="69"/>
-      <c r="K131" s="69"/>
-      <c r="L131" s="69"/>
-    </row>
-    <row r="132" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A132" s="62"/>
-      <c r="B132" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="C132" s="62"/>
-      <c r="D132" s="62"/>
-      <c r="E132" s="62"/>
-      <c r="F132" s="62">
-        <f>SUM(F111:F131)</f>
-        <v>0</v>
-      </c>
-      <c r="G132" s="62"/>
-      <c r="H132" s="62">
-        <f>SUM(H111:H131)</f>
-        <v>0</v>
-      </c>
-      <c r="I132" s="64"/>
-      <c r="J132" s="65"/>
-      <c r="K132" s="65"/>
-      <c r="L132" s="65"/>
-    </row>
-    <row r="133" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A133" s="42"/>
-      <c r="B133" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="C133" s="42"/>
-      <c r="D133" s="42"/>
-      <c r="E133" s="42"/>
-      <c r="F133" s="90">
-        <f>F132+F84+F75+F65+F54+F45+F34+F25</f>
-        <v>0</v>
-      </c>
-      <c r="G133" s="90"/>
-      <c r="H133" s="90">
-        <f>H132+H84+H75+H65+H54+H45+H34+H25</f>
-        <v>0</v>
-      </c>
-      <c r="I133" s="43"/>
+    <row r="131" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A131" s="41">
+        <v>14</v>
+      </c>
+      <c r="B131" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="C131" s="41"/>
+      <c r="D131" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E131" s="41">
+        <v>4</v>
+      </c>
+      <c r="F131" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G131" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="H131" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="132" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A132" s="41">
+        <v>15</v>
+      </c>
+      <c r="B132" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C132" s="41"/>
+      <c r="D132" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E132" s="41">
+        <v>25</v>
+      </c>
+      <c r="F132" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="41">
+        <v>48</v>
+      </c>
+      <c r="H132" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I132" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="133" s="8" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A133" s="41">
+        <v>16</v>
+      </c>
+      <c r="B133" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C133" s="41"/>
+      <c r="D133" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E133" s="41">
+        <v>160</v>
+      </c>
+      <c r="F133" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G133" s="41">
+        <v>125</v>
+      </c>
+      <c r="H133" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I133" s="42" t="s">
+        <v>160</v>
+      </c>
       <c r="J133" s="35"/>
       <c r="K133" s="35"/>
       <c r="L133" s="35"/>
     </row>
-    <row r="134" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A134" s="62"/>
-      <c r="B134" s="63" t="s">
-        <v>172</v>
-      </c>
-      <c r="C134" s="62"/>
-      <c r="D134" s="62"/>
-      <c r="E134" s="62"/>
-      <c r="F134" s="62"/>
-      <c r="G134" s="62"/>
-      <c r="H134" s="91">
-        <f>F133+H133</f>
-        <v>0</v>
-      </c>
-      <c r="I134" s="92"/>
-      <c r="J134" s="65"/>
-      <c r="K134" s="65"/>
-      <c r="L134" s="65"/>
-    </row>
-    <row r="135" s="15" customFormat="1" ht="18" customHeight="1" spans="1:12">
-      <c r="A135" s="93"/>
-      <c r="B135" s="94" t="s">
-        <v>173</v>
-      </c>
-      <c r="C135" s="95"/>
-      <c r="D135" s="95"/>
-      <c r="E135" s="95"/>
-      <c r="F135" s="95"/>
-      <c r="G135" s="95"/>
-      <c r="H135" s="95"/>
-      <c r="I135" s="96"/>
-      <c r="J135" s="97"/>
-      <c r="K135" s="97"/>
-      <c r="L135" s="97"/>
-    </row>
-    <row r="136" ht="14.25" customHeight="1" spans="1:12">
-      <c r="A136" s="42"/>
-      <c r="B136" s="98" t="s">
-        <v>174</v>
-      </c>
-      <c r="C136" s="42"/>
-      <c r="D136" s="42"/>
-      <c r="E136" s="42"/>
-      <c r="F136" s="42"/>
-      <c r="G136" s="99"/>
-      <c r="H136" s="90">
-        <f>H134*3.5%</f>
-        <v>0</v>
-      </c>
-      <c r="I136" s="43" t="s">
-        <v>175</v>
+    <row r="134" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A134" s="41">
+        <v>17</v>
+      </c>
+      <c r="B134" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C134" s="41"/>
+      <c r="D134" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" s="41">
+        <v>0</v>
+      </c>
+      <c r="F134" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G134" s="41">
+        <v>75</v>
+      </c>
+      <c r="H134" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I134" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="J134" s="35"/>
+      <c r="K134" s="35"/>
+      <c r="L134" s="35"/>
+    </row>
+    <row r="135" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A135" s="41">
+        <v>18</v>
+      </c>
+      <c r="B135" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C135" s="41"/>
+      <c r="D135" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" s="41"/>
+      <c r="F135" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G135" s="41">
+        <v>5</v>
+      </c>
+      <c r="H135" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I135" s="42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="136" s="11" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A136" s="41">
+        <v>19</v>
+      </c>
+      <c r="B136" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C136" s="41"/>
+      <c r="D136" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" s="41">
+        <v>80</v>
+      </c>
+      <c r="F136" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G136" s="41">
+        <v>75</v>
+      </c>
+      <c r="H136" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I136" s="42" t="s">
+        <v>166</v>
       </c>
       <c r="J136" s="35"/>
       <c r="K136" s="35"/>
       <c r="L136" s="35"/>
     </row>
-    <row r="137" ht="24" customHeight="1" spans="1:12">
-      <c r="A137" s="42"/>
-      <c r="B137" s="66" t="s">
-        <v>176</v>
-      </c>
-      <c r="C137" s="42"/>
-      <c r="D137" s="42"/>
-      <c r="E137" s="42"/>
-      <c r="F137" s="42"/>
-      <c r="G137" s="99"/>
-      <c r="H137" s="90">
-        <f>H134*3%</f>
-        <v>0</v>
-      </c>
-      <c r="I137" s="43" t="s">
-        <v>177</v>
+    <row r="137" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A137" s="41">
+        <v>20</v>
+      </c>
+      <c r="B137" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="C137" s="41"/>
+      <c r="D137" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" s="41">
+        <v>15</v>
+      </c>
+      <c r="F137" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G137" s="41">
+        <v>13</v>
+      </c>
+      <c r="H137" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I137" s="42" t="s">
+        <v>168</v>
       </c>
       <c r="J137" s="35"/>
       <c r="K137" s="35"/>
       <c r="L137" s="35"/>
     </row>
-    <row r="138" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A138" s="42"/>
-      <c r="B138" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="C138" s="42"/>
-      <c r="D138" s="42"/>
-      <c r="E138" s="42"/>
-      <c r="F138" s="100"/>
-      <c r="G138" s="42"/>
-      <c r="H138" s="90">
-        <f>H134*8%</f>
-        <v>0</v>
-      </c>
-      <c r="I138" s="43" t="s">
-        <v>179</v>
-      </c>
-      <c r="J138" s="101"/>
-      <c r="K138" s="102"/>
-      <c r="L138" s="102"/>
-    </row>
-    <row r="139" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A139" s="42"/>
-      <c r="B139" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="100"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="90">
-        <f>H134*5%</f>
-        <v>0</v>
-      </c>
-      <c r="I139" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="J139" s="101"/>
-      <c r="K139" s="102"/>
-      <c r="L139" s="102"/>
-    </row>
-    <row r="140" s="16" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A140" s="93"/>
-      <c r="B140" s="103" t="s">
-        <v>182</v>
-      </c>
-      <c r="C140" s="93"/>
-      <c r="D140" s="93"/>
-      <c r="E140" s="93"/>
-      <c r="F140" s="104"/>
-      <c r="G140" s="93"/>
-      <c r="H140" s="105">
-        <f>H139+H138+H137+H136+H134</f>
-        <v>0</v>
-      </c>
-      <c r="I140" s="106"/>
-      <c r="J140" s="107"/>
-      <c r="K140" s="108"/>
-      <c r="L140" s="108"/>
-    </row>
-    <row r="141" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A141" s="42"/>
-      <c r="B141" s="109" t="s">
-        <v>183</v>
-      </c>
-      <c r="C141" s="110"/>
-      <c r="D141" s="110"/>
-      <c r="E141" s="110"/>
-      <c r="F141" s="110"/>
-      <c r="G141" s="110"/>
-      <c r="H141" s="111"/>
-      <c r="I141" s="112" t="s">
-        <v>184</v>
-      </c>
-      <c r="J141" s="101"/>
-      <c r="K141" s="102"/>
-      <c r="L141" s="102"/>
-    </row>
-    <row r="142" s="16" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A142" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B142" s="103" t="s">
-        <v>185</v>
-      </c>
-      <c r="C142" s="93"/>
-      <c r="D142" s="93"/>
-      <c r="E142" s="93"/>
-      <c r="F142" s="104"/>
-      <c r="G142" s="93"/>
-      <c r="H142" s="104"/>
-      <c r="J142" s="107"/>
-      <c r="K142" s="108"/>
-      <c r="L142" s="108"/>
-    </row>
-    <row r="143" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A143" s="42">
-        <v>1</v>
-      </c>
-      <c r="B143" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="C143" s="42"/>
-      <c r="D143" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="E143" s="46">
-        <v>95</v>
-      </c>
-      <c r="F143" s="42"/>
-      <c r="G143" s="46">
-        <v>45</v>
-      </c>
-      <c r="H143" s="46"/>
-      <c r="I143" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="J143" s="101"/>
-      <c r="K143" s="102"/>
-      <c r="L143" s="102"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" spans="1:12">
-      <c r="A144" s="42">
+    <row r="138" s="8" customFormat="1" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A138" s="41">
+        <v>21</v>
+      </c>
+      <c r="B138" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C138" s="41"/>
+      <c r="D138" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" s="41">
         <v>2</v>
       </c>
-      <c r="B144" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="C144" s="42"/>
-      <c r="D144" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E144" s="46">
-        <v>2</v>
-      </c>
-      <c r="F144" s="42"/>
-      <c r="G144" s="46">
+      <c r="F138" s="41">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G138" s="41">
         <v>6</v>
       </c>
-      <c r="H144" s="42"/>
-      <c r="I144" s="43" t="s">
-        <v>190</v>
+      <c r="H138" s="41">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I138" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="J138" s="68"/>
+      <c r="K138" s="68"/>
+      <c r="L138" s="68"/>
+    </row>
+    <row r="139" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
+      <c r="A139" s="61"/>
+      <c r="B139" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C139" s="61"/>
+      <c r="D139" s="61"/>
+      <c r="E139" s="61"/>
+      <c r="F139" s="61">
+        <f>SUM(F118:F138)</f>
+        <v>0</v>
+      </c>
+      <c r="G139" s="61"/>
+      <c r="H139" s="61">
+        <f>SUM(H118:H138)</f>
+        <v>0</v>
+      </c>
+      <c r="I139" s="63"/>
+      <c r="J139" s="64"/>
+      <c r="K139" s="64"/>
+      <c r="L139" s="64"/>
+    </row>
+    <row r="140" ht="17.25" customHeight="1" spans="1:12">
+      <c r="A140" s="41"/>
+      <c r="B140" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C140" s="41"/>
+      <c r="D140" s="41"/>
+      <c r="E140" s="41"/>
+      <c r="F140" s="89">
+        <f>F139+F91+F79+F67+F56+F45+F34+F25</f>
+        <v>0</v>
+      </c>
+      <c r="G140" s="89"/>
+      <c r="H140" s="89">
+        <f>H139+H91+H79+H67+H56+H45+H34+H25</f>
+        <v>0</v>
+      </c>
+      <c r="I140" s="42"/>
+      <c r="J140" s="35"/>
+      <c r="K140" s="35"/>
+      <c r="L140" s="35"/>
+    </row>
+    <row r="141" s="7" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
+      <c r="A141" s="61"/>
+      <c r="B141" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="C141" s="61"/>
+      <c r="D141" s="61"/>
+      <c r="E141" s="61"/>
+      <c r="F141" s="61"/>
+      <c r="G141" s="61"/>
+      <c r="H141" s="90">
+        <f>F140+H140</f>
+        <v>0</v>
+      </c>
+      <c r="I141" s="91"/>
+      <c r="J141" s="64"/>
+      <c r="K141" s="64"/>
+      <c r="L141" s="64"/>
+    </row>
+    <row r="142" s="15" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A142" s="92"/>
+      <c r="B142" s="93" t="s">
+        <v>173</v>
+      </c>
+      <c r="C142" s="94"/>
+      <c r="D142" s="94"/>
+      <c r="E142" s="94"/>
+      <c r="F142" s="94"/>
+      <c r="G142" s="94"/>
+      <c r="H142" s="94"/>
+      <c r="I142" s="95"/>
+      <c r="J142" s="96"/>
+      <c r="K142" s="96"/>
+      <c r="L142" s="96"/>
+    </row>
+    <row r="143" ht="14.25" customHeight="1" spans="1:12">
+      <c r="A143" s="41"/>
+      <c r="B143" s="97" t="s">
+        <v>174</v>
+      </c>
+      <c r="C143" s="41"/>
+      <c r="D143" s="41"/>
+      <c r="E143" s="41"/>
+      <c r="F143" s="41"/>
+      <c r="G143" s="98"/>
+      <c r="H143" s="89">
+        <f>H141*3.5%</f>
+        <v>0</v>
+      </c>
+      <c r="I143" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="J143" s="35"/>
+      <c r="K143" s="35"/>
+      <c r="L143" s="35"/>
+    </row>
+    <row r="144" ht="24" customHeight="1" spans="1:12">
+      <c r="A144" s="41"/>
+      <c r="B144" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C144" s="41"/>
+      <c r="D144" s="41"/>
+      <c r="E144" s="41"/>
+      <c r="F144" s="41"/>
+      <c r="G144" s="98"/>
+      <c r="H144" s="89">
+        <f>H141*3%</f>
+        <v>0</v>
+      </c>
+      <c r="I144" s="42" t="s">
+        <v>177</v>
       </c>
       <c r="J144" s="35"/>
       <c r="K144" s="35"/>
       <c r="L144" s="35"/>
     </row>
-    <row r="145" ht="15" customHeight="1" spans="1:12">
-      <c r="A145" s="42">
+    <row r="145" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A145" s="41"/>
+      <c r="B145" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="C145" s="41"/>
+      <c r="D145" s="41"/>
+      <c r="E145" s="41"/>
+      <c r="F145" s="99"/>
+      <c r="G145" s="41"/>
+      <c r="H145" s="89">
+        <f>H141*8%</f>
+        <v>0</v>
+      </c>
+      <c r="I145" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="J145" s="100"/>
+      <c r="K145" s="101"/>
+      <c r="L145" s="101"/>
+    </row>
+    <row r="146" s="5" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A146" s="41"/>
+      <c r="B146" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="C146" s="41"/>
+      <c r="D146" s="41"/>
+      <c r="E146" s="41"/>
+      <c r="F146" s="99"/>
+      <c r="G146" s="41"/>
+      <c r="H146" s="89">
+        <f>H141*5%</f>
+        <v>0</v>
+      </c>
+      <c r="I146" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="J146" s="100"/>
+      <c r="K146" s="101"/>
+      <c r="L146" s="101"/>
+    </row>
+    <row r="147" s="16" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A147" s="92"/>
+      <c r="B147" s="102" t="s">
+        <v>182</v>
+      </c>
+      <c r="C147" s="92"/>
+      <c r="D147" s="92"/>
+      <c r="E147" s="92"/>
+      <c r="F147" s="103"/>
+      <c r="G147" s="92"/>
+      <c r="H147" s="104">
+        <f>H146+H145+H144+H143+H141</f>
+        <v>0</v>
+      </c>
+      <c r="I147" s="105"/>
+      <c r="J147" s="106"/>
+      <c r="K147" s="107"/>
+      <c r="L147" s="107"/>
+    </row>
+    <row r="148" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A148" s="41"/>
+      <c r="B148" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="C148" s="109"/>
+      <c r="D148" s="109"/>
+      <c r="E148" s="109"/>
+      <c r="F148" s="109"/>
+      <c r="G148" s="109"/>
+      <c r="H148" s="110"/>
+      <c r="I148" s="111" t="s">
+        <v>184</v>
+      </c>
+      <c r="J148" s="100"/>
+      <c r="K148" s="101"/>
+      <c r="L148" s="101"/>
+    </row>
+    <row r="149" s="16" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
+      <c r="A149" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" s="102" t="s">
+        <v>185</v>
+      </c>
+      <c r="C149" s="92"/>
+      <c r="D149" s="92"/>
+      <c r="E149" s="92"/>
+      <c r="F149" s="103"/>
+      <c r="G149" s="92"/>
+      <c r="H149" s="103"/>
+      <c r="J149" s="106"/>
+      <c r="K149" s="107"/>
+      <c r="L149" s="107"/>
+    </row>
+    <row r="150" s="5" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A150" s="41">
+        <v>1</v>
+      </c>
+      <c r="B150" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C150" s="41"/>
+      <c r="D150" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="E150" s="45">
+        <v>95</v>
+      </c>
+      <c r="F150" s="41"/>
+      <c r="G150" s="45">
+        <v>45</v>
+      </c>
+      <c r="H150" s="45"/>
+      <c r="I150" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="J150" s="100"/>
+      <c r="K150" s="101"/>
+      <c r="L150" s="101"/>
+    </row>
+    <row r="151" ht="15" customHeight="1" spans="1:12">
+      <c r="A151" s="41">
+        <v>2</v>
+      </c>
+      <c r="B151" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="C151" s="41"/>
+      <c r="D151" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151" s="45">
+        <v>2</v>
+      </c>
+      <c r="F151" s="41"/>
+      <c r="G151" s="45">
+        <v>6</v>
+      </c>
+      <c r="H151" s="41"/>
+      <c r="I151" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="J151" s="35"/>
+      <c r="K151" s="35"/>
+      <c r="L151" s="35"/>
+    </row>
+    <row r="152" ht="15" customHeight="1" spans="1:12">
+      <c r="A152" s="41">
         <v>3</v>
       </c>
-      <c r="B145" s="45" t="s">
+      <c r="B152" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C145" s="42"/>
-      <c r="D145" s="42" t="s">
+      <c r="C152" s="41"/>
+      <c r="D152" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E145" s="46">
+      <c r="E152" s="45">
         <v>20</v>
       </c>
-      <c r="F145" s="42"/>
-      <c r="G145" s="46">
+      <c r="F152" s="41"/>
+      <c r="G152" s="45">
         <v>45</v>
       </c>
-      <c r="H145" s="42"/>
-      <c r="I145" s="113" t="s">
+      <c r="H152" s="41"/>
+      <c r="I152" s="112" t="s">
         <v>192</v>
       </c>
-      <c r="J145" s="35"/>
-      <c r="K145" s="35"/>
-      <c r="L145" s="35"/>
-    </row>
-    <row r="146" ht="15" customHeight="1" spans="1:12">
-      <c r="A146" s="42">
+      <c r="J152" s="35"/>
+      <c r="K152" s="35"/>
+      <c r="L152" s="35"/>
+    </row>
+    <row r="153" ht="15" customHeight="1" spans="1:12">
+      <c r="A153" s="41">
         <v>4</v>
       </c>
-      <c r="B146" s="45" t="s">
+      <c r="B153" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="C146" s="42"/>
-      <c r="D146" s="42" t="s">
+      <c r="C153" s="41"/>
+      <c r="D153" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E146" s="46">
+      <c r="E153" s="45">
         <v>20</v>
       </c>
-      <c r="F146" s="42"/>
-      <c r="G146" s="46">
+      <c r="F153" s="41"/>
+      <c r="G153" s="45">
         <v>60</v>
       </c>
-      <c r="H146" s="42"/>
-      <c r="I146" s="113" t="s">
+      <c r="H153" s="41"/>
+      <c r="I153" s="112" t="s">
         <v>194</v>
-      </c>
-      <c r="J146" s="35"/>
-      <c r="K146" s="35"/>
-      <c r="L146" s="35"/>
-    </row>
-    <row r="147" ht="15" customHeight="1" spans="1:12">
-      <c r="A147" s="42">
-        <v>5</v>
-      </c>
-      <c r="B147" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="C147" s="42"/>
-      <c r="D147" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E147" s="46">
-        <v>20</v>
-      </c>
-      <c r="F147" s="42"/>
-      <c r="G147" s="46">
-        <v>85</v>
-      </c>
-      <c r="H147" s="42"/>
-      <c r="I147" s="113" t="s">
-        <v>196</v>
-      </c>
-      <c r="J147" s="35"/>
-      <c r="K147" s="35"/>
-      <c r="L147" s="35"/>
-    </row>
-    <row r="148" ht="15" customHeight="1" spans="1:12">
-      <c r="A148" s="42">
-        <v>6</v>
-      </c>
-      <c r="B148" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="C148" s="42"/>
-      <c r="D148" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E148" s="46">
-        <v>45</v>
-      </c>
-      <c r="F148" s="42"/>
-      <c r="G148" s="46">
-        <v>90</v>
-      </c>
-      <c r="H148" s="42"/>
-      <c r="I148" s="113" t="s">
-        <v>149</v>
-      </c>
-      <c r="J148" s="35"/>
-      <c r="K148" s="35"/>
-      <c r="L148" s="35"/>
-    </row>
-    <row r="149" ht="15" customHeight="1" spans="1:12">
-      <c r="A149" s="42">
-        <v>7</v>
-      </c>
-      <c r="B149" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C149" s="42"/>
-      <c r="D149" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E149" s="46">
-        <v>180</v>
-      </c>
-      <c r="F149" s="42"/>
-      <c r="G149" s="46">
-        <v>120</v>
-      </c>
-      <c r="H149" s="46"/>
-      <c r="I149" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="J149" s="35"/>
-      <c r="K149" s="35"/>
-      <c r="L149" s="35"/>
-    </row>
-    <row r="150" ht="15" customHeight="1" spans="1:12">
-      <c r="A150" s="42">
-        <v>8</v>
-      </c>
-      <c r="B150" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C150" s="42"/>
-      <c r="D150" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="E150" s="46">
-        <v>70</v>
-      </c>
-      <c r="F150" s="42"/>
-      <c r="G150" s="46">
-        <v>25</v>
-      </c>
-      <c r="H150" s="46"/>
-      <c r="I150" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="J150" s="35"/>
-      <c r="K150" s="35"/>
-      <c r="L150" s="35"/>
-    </row>
-    <row r="151" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A151" s="42">
-        <v>9</v>
-      </c>
-      <c r="B151" s="68" t="s">
-        <v>199</v>
-      </c>
-      <c r="C151" s="42"/>
-      <c r="D151" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E151" s="84">
-        <v>0</v>
-      </c>
-      <c r="F151" s="42"/>
-      <c r="G151" s="42">
-        <v>50</v>
-      </c>
-      <c r="H151" s="42"/>
-      <c r="I151" s="114" t="s">
-        <v>200</v>
-      </c>
-      <c r="J151" s="89"/>
-      <c r="K151" s="89"/>
-      <c r="L151" s="89"/>
-    </row>
-    <row r="152" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A152" s="42">
-        <v>10</v>
-      </c>
-      <c r="B152" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="C152" s="42"/>
-      <c r="D152" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E152" s="84">
-        <v>50</v>
-      </c>
-      <c r="F152" s="42"/>
-      <c r="G152" s="42">
-        <v>100</v>
-      </c>
-      <c r="H152" s="42"/>
-      <c r="I152" s="114" t="s">
-        <v>202</v>
-      </c>
-      <c r="J152" s="89"/>
-      <c r="K152" s="89"/>
-      <c r="L152" s="89"/>
-    </row>
-    <row r="153" ht="15" customHeight="1" spans="1:12">
-      <c r="A153" s="42">
-        <v>11</v>
-      </c>
-      <c r="B153" s="115" t="s">
-        <v>203</v>
-      </c>
-      <c r="C153" s="42"/>
-      <c r="D153" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E153" s="46">
-        <v>120</v>
-      </c>
-      <c r="F153" s="42"/>
-      <c r="G153" s="46">
-        <v>160</v>
-      </c>
-      <c r="H153" s="46"/>
-      <c r="I153" s="47" t="s">
-        <v>198</v>
       </c>
       <c r="J153" s="35"/>
       <c r="K153" s="35"/>
       <c r="L153" s="35"/>
     </row>
-    <row r="154" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A154" s="42">
-        <v>12</v>
-      </c>
-      <c r="B154" s="116" t="s">
-        <v>146</v>
-      </c>
-      <c r="C154" s="51"/>
-      <c r="D154" s="51" t="s">
+    <row r="154" ht="15" customHeight="1" spans="1:12">
+      <c r="A154" s="41">
+        <v>5</v>
+      </c>
+      <c r="B154" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="C154" s="41"/>
+      <c r="D154" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E154" s="83">
+      <c r="E154" s="45">
+        <v>20</v>
+      </c>
+      <c r="F154" s="41"/>
+      <c r="G154" s="45">
+        <v>85</v>
+      </c>
+      <c r="H154" s="41"/>
+      <c r="I154" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="J154" s="35"/>
+      <c r="K154" s="35"/>
+      <c r="L154" s="35"/>
+    </row>
+    <row r="155" ht="15" customHeight="1" spans="1:12">
+      <c r="A155" s="41">
+        <v>6</v>
+      </c>
+      <c r="B155" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="C155" s="41"/>
+      <c r="D155" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155" s="45">
+        <v>45</v>
+      </c>
+      <c r="F155" s="41"/>
+      <c r="G155" s="45">
+        <v>90</v>
+      </c>
+      <c r="H155" s="41"/>
+      <c r="I155" s="112" t="s">
+        <v>149</v>
+      </c>
+      <c r="J155" s="35"/>
+      <c r="K155" s="35"/>
+      <c r="L155" s="35"/>
+    </row>
+    <row r="156" ht="15" customHeight="1" spans="1:12">
+      <c r="A156" s="41">
+        <v>7</v>
+      </c>
+      <c r="B156" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="C156" s="41"/>
+      <c r="D156" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E156" s="45">
+        <v>180</v>
+      </c>
+      <c r="F156" s="41"/>
+      <c r="G156" s="45">
+        <v>120</v>
+      </c>
+      <c r="H156" s="45"/>
+      <c r="I156" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="J156" s="35"/>
+      <c r="K156" s="35"/>
+      <c r="L156" s="35"/>
+    </row>
+    <row r="157" ht="15" customHeight="1" spans="1:12">
+      <c r="A157" s="41">
+        <v>8</v>
+      </c>
+      <c r="B157" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C157" s="41"/>
+      <c r="D157" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" s="45">
+        <v>70</v>
+      </c>
+      <c r="F157" s="41"/>
+      <c r="G157" s="45">
         <v>25</v>
       </c>
-      <c r="F154" s="51"/>
-      <c r="G154" s="83">
-        <v>45</v>
-      </c>
-      <c r="H154" s="83"/>
-      <c r="I154" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="J154" s="60"/>
-      <c r="K154" s="60"/>
-      <c r="L154" s="60"/>
-    </row>
-    <row r="155" s="17" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A155" s="42">
-        <v>13</v>
-      </c>
-      <c r="B155" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="C155" s="51"/>
-      <c r="D155" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="E155" s="83">
-        <v>23</v>
-      </c>
-      <c r="F155" s="51"/>
-      <c r="G155" s="83">
+      <c r="H157" s="45"/>
+      <c r="I157" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H155" s="51"/>
-      <c r="I155" s="52" t="s">
-        <v>205</v>
-      </c>
-      <c r="J155" s="117"/>
-      <c r="K155" s="117"/>
-      <c r="L155" s="117"/>
-    </row>
-    <row r="156" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A156" s="42">
-        <v>14</v>
-      </c>
-      <c r="B156" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="C156" s="42"/>
-      <c r="D156" s="42" t="s">
+      <c r="J157" s="35"/>
+      <c r="K157" s="35"/>
+      <c r="L157" s="35"/>
+    </row>
+    <row r="158" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A158" s="41">
+        <v>9</v>
+      </c>
+      <c r="B158" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C158" s="41"/>
+      <c r="D158" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E156" s="46">
+      <c r="E158" s="83">
+        <v>0</v>
+      </c>
+      <c r="F158" s="41"/>
+      <c r="G158" s="41">
+        <v>50</v>
+      </c>
+      <c r="H158" s="41"/>
+      <c r="I158" s="113" t="s">
+        <v>200</v>
+      </c>
+      <c r="J158" s="88"/>
+      <c r="K158" s="88"/>
+      <c r="L158" s="88"/>
+    </row>
+    <row r="159" s="12" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A159" s="41">
+        <v>10</v>
+      </c>
+      <c r="B159" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C159" s="41"/>
+      <c r="D159" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E159" s="83">
+        <v>50</v>
+      </c>
+      <c r="F159" s="41"/>
+      <c r="G159" s="41">
+        <v>100</v>
+      </c>
+      <c r="H159" s="41"/>
+      <c r="I159" s="113" t="s">
+        <v>202</v>
+      </c>
+      <c r="J159" s="88"/>
+      <c r="K159" s="88"/>
+      <c r="L159" s="88"/>
+    </row>
+    <row r="160" ht="15" customHeight="1" spans="1:12">
+      <c r="A160" s="41">
+        <v>11</v>
+      </c>
+      <c r="B160" s="114" t="s">
+        <v>203</v>
+      </c>
+      <c r="C160" s="41"/>
+      <c r="D160" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E160" s="45">
         <v>120</v>
       </c>
-      <c r="F156" s="42"/>
-      <c r="G156" s="46">
-        <v>180</v>
-      </c>
-      <c r="H156" s="42"/>
-      <c r="I156" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="J156" s="69"/>
-      <c r="K156" s="69"/>
-      <c r="L156" s="69"/>
-    </row>
-    <row r="157" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A157" s="42">
-        <v>15</v>
-      </c>
-      <c r="B157" s="118" t="s">
-        <v>150</v>
-      </c>
-      <c r="C157" s="119"/>
-      <c r="D157" s="119" t="s">
-        <v>15</v>
-      </c>
-      <c r="E157" s="120">
-        <v>65</v>
-      </c>
-      <c r="F157" s="42"/>
-      <c r="G157" s="120">
-        <v>100</v>
-      </c>
-      <c r="H157" s="42"/>
-      <c r="I157" s="121" t="s">
-        <v>151</v>
-      </c>
-      <c r="J157"/>
-      <c r="K157"/>
-      <c r="L157"/>
-    </row>
-    <row r="158" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A158" s="42">
-        <v>16</v>
-      </c>
-      <c r="B158" s="122" t="s">
-        <v>163</v>
-      </c>
-      <c r="C158" s="42"/>
-      <c r="D158" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" s="123"/>
-      <c r="F158" s="42"/>
-      <c r="G158" s="123">
-        <v>5</v>
-      </c>
-      <c r="H158" s="42"/>
-      <c r="I158" s="124" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="159" ht="15" customHeight="1" spans="1:12">
-      <c r="A159" s="42">
-        <v>17</v>
-      </c>
-      <c r="B159" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C159" s="42"/>
-      <c r="D159" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E159" s="46">
-        <v>180</v>
-      </c>
-      <c r="F159" s="42"/>
-      <c r="G159" s="46">
-        <v>320</v>
-      </c>
-      <c r="H159" s="42"/>
-      <c r="I159" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="J159" s="35"/>
-      <c r="K159" s="35"/>
-      <c r="L159" s="35"/>
-    </row>
-    <row r="160" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A160" s="42">
-        <v>18</v>
-      </c>
-      <c r="B160" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="C160" s="42"/>
-      <c r="D160" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E160" s="46">
-        <v>200</v>
-      </c>
-      <c r="F160" s="42"/>
-      <c r="G160" s="46">
-        <v>150</v>
-      </c>
-      <c r="H160" s="42"/>
-      <c r="I160" s="43" t="s">
-        <v>209</v>
+      <c r="F160" s="41"/>
+      <c r="G160" s="45">
+        <v>160</v>
+      </c>
+      <c r="H160" s="45"/>
+      <c r="I160" s="46" t="s">
+        <v>198</v>
       </c>
       <c r="J160" s="35"/>
       <c r="K160" s="35"/>
       <c r="L160" s="35"/>
     </row>
-    <row r="161" customFormat="1" ht="15" customHeight="1" spans="1:12">
-      <c r="A161" s="42">
+    <row r="161" s="13" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A161" s="41">
+        <v>12</v>
+      </c>
+      <c r="B161" s="115" t="s">
+        <v>146</v>
+      </c>
+      <c r="C161" s="50"/>
+      <c r="D161" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E161" s="82">
+        <v>25</v>
+      </c>
+      <c r="F161" s="50"/>
+      <c r="G161" s="82">
+        <v>45</v>
+      </c>
+      <c r="H161" s="82"/>
+      <c r="I161" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="J161" s="59"/>
+      <c r="K161" s="59"/>
+      <c r="L161" s="59"/>
+    </row>
+    <row r="162" s="17" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="A162" s="41">
+        <v>13</v>
+      </c>
+      <c r="B162" s="58" t="s">
+        <v>204</v>
+      </c>
+      <c r="C162" s="50"/>
+      <c r="D162" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E162" s="82">
+        <v>23</v>
+      </c>
+      <c r="F162" s="50"/>
+      <c r="G162" s="82">
+        <v>16</v>
+      </c>
+      <c r="H162" s="50"/>
+      <c r="I162" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="J162" s="116"/>
+      <c r="K162" s="116"/>
+      <c r="L162" s="116"/>
+    </row>
+    <row r="163" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="A163" s="41">
+        <v>14</v>
+      </c>
+      <c r="B163" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="C163" s="41"/>
+      <c r="D163" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E163" s="45">
+        <v>120</v>
+      </c>
+      <c r="F163" s="41"/>
+      <c r="G163" s="45">
+        <v>180</v>
+      </c>
+      <c r="H163" s="41"/>
+      <c r="I163" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="J163" s="68"/>
+      <c r="K163" s="68"/>
+      <c r="L163" s="68"/>
+    </row>
+    <row r="164" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="A164" s="41">
+        <v>15</v>
+      </c>
+      <c r="B164" s="117" t="s">
+        <v>150</v>
+      </c>
+      <c r="C164" s="118"/>
+      <c r="D164" s="118" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" s="119">
+        <v>65</v>
+      </c>
+      <c r="F164" s="41"/>
+      <c r="G164" s="119">
+        <v>100</v>
+      </c>
+      <c r="H164" s="41"/>
+      <c r="I164" s="120" t="s">
+        <v>151</v>
+      </c>
+      <c r="J164"/>
+      <c r="K164"/>
+      <c r="L164"/>
+    </row>
+    <row r="165" s="14" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A165" s="41">
+        <v>16</v>
+      </c>
+      <c r="B165" s="121" t="s">
+        <v>163</v>
+      </c>
+      <c r="C165" s="41"/>
+      <c r="D165" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" s="122"/>
+      <c r="F165" s="41"/>
+      <c r="G165" s="122">
+        <v>5</v>
+      </c>
+      <c r="H165" s="41"/>
+      <c r="I165" s="123" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" ht="15" customHeight="1" spans="1:12">
+      <c r="A166" s="41">
+        <v>17</v>
+      </c>
+      <c r="B166" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C166" s="41"/>
+      <c r="D166" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E166" s="45">
+        <v>180</v>
+      </c>
+      <c r="F166" s="41"/>
+      <c r="G166" s="45">
+        <v>320</v>
+      </c>
+      <c r="H166" s="41"/>
+      <c r="I166" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="J166" s="35"/>
+      <c r="K166" s="35"/>
+      <c r="L166" s="35"/>
+    </row>
+    <row r="167" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A167" s="41">
+        <v>18</v>
+      </c>
+      <c r="B167" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C167" s="41"/>
+      <c r="D167" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E167" s="45">
+        <v>200</v>
+      </c>
+      <c r="F167" s="41"/>
+      <c r="G167" s="45">
+        <v>150</v>
+      </c>
+      <c r="H167" s="41"/>
+      <c r="I167" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="J167" s="35"/>
+      <c r="K167" s="35"/>
+      <c r="L167" s="35"/>
+    </row>
+    <row r="168" customFormat="1" ht="15" customHeight="1" spans="1:12">
+      <c r="A168" s="41">
         <v>19</v>
       </c>
-      <c r="B161" s="45" t="s">
+      <c r="B168" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="C161" s="42"/>
-      <c r="D161" s="42" t="s">
+      <c r="C168" s="41"/>
+      <c r="D168" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E161" s="46">
+      <c r="E168" s="45">
         <v>130</v>
       </c>
-      <c r="F161" s="42"/>
-      <c r="G161" s="46">
+      <c r="F168" s="41"/>
+      <c r="G168" s="45">
         <v>70</v>
       </c>
-      <c r="H161" s="42"/>
-      <c r="I161" s="43" t="s">
+      <c r="H168" s="41"/>
+      <c r="I168" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="J161" s="35"/>
-      <c r="K161" s="35"/>
-      <c r="L161" s="35"/>
-    </row>
-    <row r="162" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A162" s="42">
+      <c r="J168" s="35"/>
+      <c r="K168" s="35"/>
+      <c r="L168" s="35"/>
+    </row>
+    <row r="169" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A169" s="41">
         <v>20</v>
       </c>
-      <c r="B162" s="125" t="s">
+      <c r="B169" s="124" t="s">
         <v>154</v>
       </c>
-      <c r="C162" s="42"/>
-      <c r="D162" s="119" t="s">
+      <c r="C169" s="41"/>
+      <c r="D169" s="118" t="s">
         <v>155</v>
       </c>
-      <c r="E162" s="120">
+      <c r="E169" s="119">
         <v>4</v>
       </c>
-      <c r="F162" s="119"/>
-      <c r="G162" s="120">
+      <c r="F169" s="118"/>
+      <c r="G169" s="119">
         <v>2.5</v>
       </c>
-      <c r="H162" s="42"/>
-      <c r="I162" s="121" t="s">
+      <c r="H169" s="41"/>
+      <c r="I169" s="120" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="163" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A163" s="42">
+    <row r="170" s="11" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A170" s="41">
         <v>21</v>
       </c>
-      <c r="B163" s="118" t="s">
+      <c r="B170" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="C163" s="42"/>
-      <c r="D163" s="119" t="s">
+      <c r="C170" s="41"/>
+      <c r="D170" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="E163" s="120">
+      <c r="E170" s="119">
         <v>25</v>
       </c>
-      <c r="F163" s="42"/>
-      <c r="G163" s="120">
+      <c r="F170" s="41"/>
+      <c r="G170" s="119">
         <v>48</v>
       </c>
-      <c r="H163" s="42"/>
-      <c r="I163" s="121" t="s">
+      <c r="H170" s="41"/>
+      <c r="I170" s="120" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1" spans="1:12">
-      <c r="A164" s="42">
+    <row r="171" ht="15" customHeight="1" spans="1:12">
+      <c r="A171" s="41">
         <v>22</v>
       </c>
-      <c r="B164" s="115" t="s">
+      <c r="B171" s="114" t="s">
         <v>159</v>
       </c>
-      <c r="C164" s="42"/>
-      <c r="D164" s="42" t="s">
+      <c r="C171" s="41"/>
+      <c r="D171" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E164" s="46">
+      <c r="E171" s="45">
         <v>160</v>
       </c>
-      <c r="F164" s="42"/>
-      <c r="G164" s="46">
+      <c r="F171" s="41"/>
+      <c r="G171" s="45">
         <v>125</v>
       </c>
-      <c r="H164" s="42"/>
-      <c r="I164" s="43" t="s">
+      <c r="H171" s="41"/>
+      <c r="I171" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="J164" s="35"/>
-      <c r="K164" s="35"/>
-      <c r="L164" s="35"/>
-    </row>
-    <row r="165" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
-      <c r="A165" s="42">
+      <c r="J171" s="35"/>
+      <c r="K171" s="35"/>
+      <c r="L171" s="35"/>
+    </row>
+    <row r="172" s="8" customFormat="1" ht="14.15" customHeight="1" spans="1:12">
+      <c r="A172" s="41">
         <v>23</v>
       </c>
-      <c r="B165" s="118" t="s">
+      <c r="B172" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="C165" s="119"/>
-      <c r="D165" s="119" t="s">
+      <c r="C172" s="118"/>
+      <c r="D172" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="120"/>
-      <c r="F165" s="42">
-        <f>C165*E165</f>
-        <v>0</v>
-      </c>
-      <c r="G165" s="120">
+      <c r="E172" s="119"/>
+      <c r="F172" s="41">
+        <f>C172*E172</f>
+        <v>0</v>
+      </c>
+      <c r="G172" s="119">
         <v>85</v>
       </c>
-      <c r="H165" s="42">
-        <f>SUM(G165*C165)</f>
-        <v>0</v>
-      </c>
-      <c r="I165" s="43" t="s">
+      <c r="H172" s="41">
+        <f>SUM(G172*C172)</f>
+        <v>0</v>
+      </c>
+      <c r="I172" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="J165"/>
-    </row>
-    <row r="166" s="5" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
-      <c r="A166" s="42" t="s">
+      <c r="J172"/>
+    </row>
+    <row r="173" s="5" customFormat="1" ht="17.15" customHeight="1" spans="1:12">
+      <c r="A173" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B166" s="66" t="s">
+      <c r="B173" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="C166" s="126"/>
-      <c r="D166" s="126"/>
-      <c r="E166" s="126"/>
-      <c r="F166" s="126"/>
-      <c r="G166" s="126"/>
-      <c r="H166" s="126"/>
-      <c r="I166" s="126"/>
-      <c r="J166" s="101"/>
-      <c r="K166" s="102"/>
-      <c r="L166" s="102"/>
-    </row>
-    <row r="167" s="5" customFormat="1" ht="27" customHeight="1" spans="1:12">
-      <c r="A167" s="42">
+      <c r="C173" s="125"/>
+      <c r="D173" s="125"/>
+      <c r="E173" s="125"/>
+      <c r="F173" s="125"/>
+      <c r="G173" s="125"/>
+      <c r="H173" s="125"/>
+      <c r="I173" s="125"/>
+      <c r="J173" s="100"/>
+      <c r="K173" s="101"/>
+      <c r="L173" s="101"/>
+    </row>
+    <row r="174" s="5" customFormat="1" ht="27" customHeight="1" spans="1:12">
+      <c r="A174" s="41">
         <v>1</v>
       </c>
-      <c r="B167" s="127" t="s">
+      <c r="B174" s="126" t="s">
         <v>215</v>
       </c>
-      <c r="C167" s="127"/>
-      <c r="D167" s="127"/>
-      <c r="E167" s="127"/>
-      <c r="F167" s="127"/>
-      <c r="G167" s="127"/>
-      <c r="H167" s="127"/>
-      <c r="I167" s="127"/>
-      <c r="J167" s="101"/>
-      <c r="K167" s="102"/>
-      <c r="L167" s="102"/>
-    </row>
-    <row r="168" s="5" customFormat="1" ht="29" customHeight="1" spans="1:12">
-      <c r="A168" s="42">
+      <c r="C174" s="126"/>
+      <c r="D174" s="126"/>
+      <c r="E174" s="126"/>
+      <c r="F174" s="126"/>
+      <c r="G174" s="126"/>
+      <c r="H174" s="126"/>
+      <c r="I174" s="126"/>
+      <c r="J174" s="100"/>
+      <c r="K174" s="101"/>
+      <c r="L174" s="101"/>
+    </row>
+    <row r="175" s="5" customFormat="1" ht="29" customHeight="1" spans="1:12">
+      <c r="A175" s="41">
         <v>2</v>
       </c>
-      <c r="B168" s="45" t="s">
+      <c r="B175" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="C168" s="45"/>
-      <c r="D168" s="45"/>
-      <c r="E168" s="45"/>
-      <c r="F168" s="45"/>
-      <c r="G168" s="45"/>
-      <c r="H168" s="45"/>
-      <c r="I168" s="45"/>
-      <c r="J168" s="101"/>
-      <c r="K168" s="102"/>
-      <c r="L168" s="102"/>
-    </row>
-    <row r="169" s="5" customFormat="1" ht="29.25" customHeight="1" spans="1:12">
-      <c r="A169" s="42">
+      <c r="C175" s="44"/>
+      <c r="D175" s="44"/>
+      <c r="E175" s="44"/>
+      <c r="F175" s="44"/>
+      <c r="G175" s="44"/>
+      <c r="H175" s="44"/>
+      <c r="I175" s="44"/>
+      <c r="J175" s="100"/>
+      <c r="K175" s="101"/>
+      <c r="L175" s="101"/>
+    </row>
+    <row r="176" s="5" customFormat="1" ht="29.25" customHeight="1" spans="1:12">
+      <c r="A176" s="41">
         <v>3</v>
       </c>
-      <c r="B169" s="127" t="s">
+      <c r="B176" s="126" t="s">
         <v>217</v>
       </c>
-      <c r="C169" s="127"/>
-      <c r="D169" s="127"/>
-      <c r="E169" s="127"/>
-      <c r="F169" s="127"/>
-      <c r="G169" s="127"/>
-      <c r="H169" s="127"/>
-      <c r="I169" s="127"/>
-      <c r="J169" s="101"/>
-      <c r="K169" s="102"/>
-      <c r="L169" s="102"/>
-    </row>
-    <row r="170" s="5" customFormat="1" ht="27.75" customHeight="1" spans="1:12">
-      <c r="A170" s="42">
+      <c r="C176" s="126"/>
+      <c r="D176" s="126"/>
+      <c r="E176" s="126"/>
+      <c r="F176" s="126"/>
+      <c r="G176" s="126"/>
+      <c r="H176" s="126"/>
+      <c r="I176" s="126"/>
+      <c r="J176" s="100"/>
+      <c r="K176" s="101"/>
+      <c r="L176" s="101"/>
+    </row>
+    <row r="177" s="5" customFormat="1" ht="27.75" customHeight="1" spans="1:12">
+      <c r="A177" s="41">
         <v>4</v>
       </c>
-      <c r="B170" s="127" t="s">
+      <c r="B177" s="126" t="s">
         <v>218</v>
       </c>
-      <c r="C170" s="127"/>
-      <c r="D170" s="127"/>
-      <c r="E170" s="127"/>
-      <c r="F170" s="127"/>
-      <c r="G170" s="127"/>
-      <c r="H170" s="127"/>
-      <c r="I170" s="127"/>
-      <c r="J170" s="101"/>
-      <c r="K170" s="102"/>
-      <c r="L170" s="102"/>
-    </row>
-    <row r="171" s="5" customFormat="1" ht="58" customHeight="1" spans="1:12">
-      <c r="A171" s="42">
+      <c r="C177" s="126"/>
+      <c r="D177" s="126"/>
+      <c r="E177" s="126"/>
+      <c r="F177" s="126"/>
+      <c r="G177" s="126"/>
+      <c r="H177" s="126"/>
+      <c r="I177" s="126"/>
+      <c r="J177" s="100"/>
+      <c r="K177" s="101"/>
+      <c r="L177" s="101"/>
+    </row>
+    <row r="178" s="5" customFormat="1" ht="58" customHeight="1" spans="1:12">
+      <c r="A178" s="41">
         <v>5</v>
       </c>
-      <c r="B171" s="127" t="s">
+      <c r="B178" s="126" t="s">
         <v>219</v>
       </c>
-      <c r="C171" s="127"/>
-      <c r="D171" s="127"/>
-      <c r="E171" s="127"/>
-      <c r="F171" s="127"/>
-      <c r="G171" s="127"/>
-      <c r="H171" s="127"/>
-      <c r="I171" s="127"/>
-      <c r="J171" s="101"/>
-      <c r="K171" s="102"/>
-      <c r="L171" s="102"/>
-    </row>
-    <row r="172" s="5" customFormat="1" ht="31.5" customHeight="1" spans="1:12">
-      <c r="A172" s="42">
+      <c r="C178" s="126"/>
+      <c r="D178" s="126"/>
+      <c r="E178" s="126"/>
+      <c r="F178" s="126"/>
+      <c r="G178" s="126"/>
+      <c r="H178" s="126"/>
+      <c r="I178" s="126"/>
+      <c r="J178" s="100"/>
+      <c r="K178" s="101"/>
+      <c r="L178" s="101"/>
+    </row>
+    <row r="179" s="5" customFormat="1" ht="31.5" customHeight="1" spans="1:12">
+      <c r="A179" s="41">
         <v>6</v>
       </c>
-      <c r="B172" s="45" t="s">
+      <c r="B179" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="C172" s="45"/>
-      <c r="D172" s="45"/>
-      <c r="E172" s="45"/>
-      <c r="F172" s="45"/>
-      <c r="G172" s="45"/>
-      <c r="H172" s="45"/>
-      <c r="I172" s="45"/>
-      <c r="J172" s="101"/>
-      <c r="K172" s="102"/>
-      <c r="L172" s="102"/>
-    </row>
-    <row r="173" s="5" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
-      <c r="A173" s="42">
+      <c r="C179" s="44"/>
+      <c r="D179" s="44"/>
+      <c r="E179" s="44"/>
+      <c r="F179" s="44"/>
+      <c r="G179" s="44"/>
+      <c r="H179" s="44"/>
+      <c r="I179" s="44"/>
+      <c r="J179" s="100"/>
+      <c r="K179" s="101"/>
+      <c r="L179" s="101"/>
+    </row>
+    <row r="180" s="5" customFormat="1" ht="16.5" customHeight="1" spans="1:12">
+      <c r="A180" s="41">
         <v>7</v>
       </c>
-      <c r="B173" s="127" t="s">
+      <c r="B180" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="C173" s="127"/>
-      <c r="D173" s="127"/>
-      <c r="E173" s="127"/>
-      <c r="F173" s="127"/>
-      <c r="G173" s="127"/>
-      <c r="H173" s="127"/>
-      <c r="I173" s="127"/>
-      <c r="J173" s="101"/>
-      <c r="K173" s="102"/>
-      <c r="L173" s="102"/>
-    </row>
-    <row r="174" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
-      <c r="A174" s="42">
+      <c r="C180" s="126"/>
+      <c r="D180" s="126"/>
+      <c r="E180" s="126"/>
+      <c r="F180" s="126"/>
+      <c r="G180" s="126"/>
+      <c r="H180" s="126"/>
+      <c r="I180" s="126"/>
+      <c r="J180" s="100"/>
+      <c r="K180" s="101"/>
+      <c r="L180" s="101"/>
+    </row>
+    <row r="181" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
+      <c r="A181" s="41">
         <v>8</v>
       </c>
-      <c r="B174" s="127" t="s">
+      <c r="B181" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="C174" s="127"/>
-      <c r="D174" s="127"/>
-      <c r="E174" s="127"/>
-      <c r="F174" s="127"/>
-      <c r="G174" s="127"/>
-      <c r="H174" s="127"/>
-      <c r="I174" s="127"/>
-      <c r="J174" s="101"/>
-      <c r="K174" s="102"/>
-      <c r="L174" s="102"/>
-    </row>
-    <row r="175" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
-      <c r="A175" s="42">
+      <c r="C181" s="126"/>
+      <c r="D181" s="126"/>
+      <c r="E181" s="126"/>
+      <c r="F181" s="126"/>
+      <c r="G181" s="126"/>
+      <c r="H181" s="126"/>
+      <c r="I181" s="126"/>
+      <c r="J181" s="100"/>
+      <c r="K181" s="101"/>
+      <c r="L181" s="101"/>
+    </row>
+    <row r="182" s="5" customFormat="1" ht="16" customHeight="1" spans="1:12">
+      <c r="A182" s="41">
         <v>9</v>
       </c>
-      <c r="B175" s="127" t="s">
+      <c r="B182" s="126" t="s">
         <v>223</v>
       </c>
-      <c r="C175" s="127"/>
-      <c r="D175" s="127"/>
-      <c r="E175" s="127"/>
-      <c r="F175" s="127"/>
-      <c r="G175" s="127"/>
-      <c r="H175" s="127"/>
-      <c r="I175" s="127"/>
-      <c r="J175" s="101"/>
-      <c r="K175" s="102"/>
-      <c r="L175" s="102"/>
-    </row>
-    <row r="176" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
-      <c r="A176" s="128"/>
-      <c r="B176" s="129" t="s">
+      <c r="C182" s="126"/>
+      <c r="D182" s="126"/>
+      <c r="E182" s="126"/>
+      <c r="F182" s="126"/>
+      <c r="G182" s="126"/>
+      <c r="H182" s="126"/>
+      <c r="I182" s="126"/>
+      <c r="J182" s="100"/>
+      <c r="K182" s="101"/>
+      <c r="L182" s="101"/>
+    </row>
+    <row r="183" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:12">
+      <c r="A183" s="127"/>
+      <c r="B183" s="128" t="s">
         <v>224</v>
       </c>
-      <c r="C176" s="129"/>
-      <c r="D176" s="129"/>
-      <c r="E176" s="129"/>
-      <c r="F176" s="129"/>
-      <c r="G176" s="129"/>
-      <c r="H176" s="129"/>
-      <c r="I176" s="129"/>
-      <c r="J176" s="130"/>
-      <c r="K176" s="130"/>
-      <c r="L176" s="130"/>
+      <c r="C183" s="128"/>
+      <c r="D183" s="128"/>
+      <c r="E183" s="128"/>
+      <c r="F183" s="128"/>
+      <c r="G183" s="128"/>
+      <c r="H183" s="128"/>
+      <c r="I183" s="128"/>
+      <c r="J183" s="129"/>
+      <c r="K183" s="129"/>
+      <c r="L183" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -7903,21 +8130,21 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B135:I135"/>
-    <mergeCell ref="B141:G141"/>
-    <mergeCell ref="C166:I166"/>
-    <mergeCell ref="B167:I167"/>
-    <mergeCell ref="B168:I168"/>
-    <mergeCell ref="B169:I169"/>
-    <mergeCell ref="B170:I170"/>
-    <mergeCell ref="B171:I171"/>
-    <mergeCell ref="B172:I172"/>
-    <mergeCell ref="B173:I173"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B142:I142"/>
+    <mergeCell ref="B148:G148"/>
+    <mergeCell ref="C173:I173"/>
     <mergeCell ref="B174:I174"/>
     <mergeCell ref="B175:I175"/>
     <mergeCell ref="B176:I176"/>
+    <mergeCell ref="B177:I177"/>
+    <mergeCell ref="B178:I178"/>
+    <mergeCell ref="B179:I179"/>
+    <mergeCell ref="B180:I180"/>
+    <mergeCell ref="B181:I181"/>
+    <mergeCell ref="B182:I182"/>
+    <mergeCell ref="B183:I183"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="C4:C7"/>
